--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77F0F4C-3227-4039-B16A-105F00E45DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AAEC29-491F-4894-A600-8989C5149F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Transcripts!$A$1:$D$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WOOM Archive'!$A$1:$E$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WOOM Archive'!$A$1:$E$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="268">
   <si>
     <t>youtube_link</t>
   </si>
@@ -9349,6 +9349,9 @@
   <si>
     <t>2026-09-08</t>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=M4_pR6sS5zM&amp;t=1s</t>
+  </si>
 </sst>
 </file>
 
@@ -9472,10 +9475,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10454,7 +10453,9 @@
       <c r="D39" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="E39" s="5"/>
+      <c r="E39" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="40" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
@@ -10487,7 +10488,7 @@
       <c r="E41" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E40" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}"/>
+  <autoFilter ref="A1:E41" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}"/>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" xr:uid="{B375DB27-E1B7-490E-9D8C-9444D796161B}"/>
   </hyperlinks>

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AAEC29-491F-4894-A600-8989C5149F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1A510D-F22A-4F63-8BD8-73489D1F3FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="271">
   <si>
     <t>youtube_link</t>
   </si>
@@ -9352,11 +9352,421 @@
   <si>
     <t>https://www.youtube.com/watch?v=M4_pR6sS5zM&amp;t=1s</t>
   </si>
+  <si>
+    <t>What Are People Pretending to Like</t>
+  </si>
+  <si>
+    <t>Transcript
+00:00:00 Darius
+about to make the joke that you did the internet thing where you said unpopular opinion and then stated very common practices. It's like habits that I don't want to admit. I pray before a long drive. I decompress after bad days. It's hard for me to go to sleep when I'm anxious. But driving back and forth to Durham is genuinely weird.
+00:00:21 Jordan
+Yeah, I'll be like, **** this. Yeah, I just. I just jump up and down the road. U-turn after U-turn. I don't know what's weird about me.
+00:00:27 Darius
+After a hard day, I watch a comedy. That's. That's me.
+00:00:32 Jordan
+Well, I'm very like, specific.
+00:00:33 Darius
+Out trunk with Jordan and Darius. My name is Darius. That's these all up in the area on all socials.
+00:00:38 Jordan
+And I'm Jordan. That's Jordan to be writing on all socials.
+00:00:41 Darius
+This is our What's On Our Mind segment where we let you guys know what's on our mind, what we've seen on the internet, things that we want to talk about. Do a little engagement bait, starting it off. We got, I'm going to put the graphic up on the screen here. We're picking one per row. Just a way to let you guys get to know us. What you got for, we're good. Just going to number the rows one, two, three. Just pick, just pick one for each row. And then we'll just go and go from there. So what you got for the first row, A, B, C, D, or E?
+00:01:12 Jordan
+I'm going with the breakfast burrito for row C. I love, you know, breakfast food. Anytime I can get in sort of like an efficient way like that, you know, it's always nice. I love omelets, but I got to be in the mood for hash browns. Same thing with pancakes too. I'm kind of weird about that kind of stuff. And the red velvet fridge toast, that just feels like a Saturday thing. You know what I mean? I couldn't have that like on a weekday and work. I'd need like 4 hours of sleep after that, you know?
+00:01:38 Darius
+Yeah, I'm not big on red velvet anything.
+00:01:43 Jordan
+Really.
+00:01:44 Darius
+It's just not, doesn't really do it for me. Yeah, breakfast burrito as well. Like you said, it's efficient. It hits all the bases. I do love hash browns, so I would like hash browns in my breakfast burrito.
+00:01:57 Jordan
+I'm not mad at that.
+00:01:58 Darius
+Pancakes are really hit or miss. Really hit or miss.
+00:02:01 Jordan
+I got to I got to really be. I feel like there's a weekend thing because you just who has time to like Sydney pancakes during the week, you know?
+00:02:07 Darius
+They're just and then when you do get them, they're so infrequently done right. And so omelets, I love an omelet, but if I can just put it all wrapped into a burrito, that's fine. Grand slam, which that's doing too much.
+00:02:19 Jordan
+Yeah.
+00:02:20 Darius
+And I love French toast, but stuffed red velvet, strawberry cream, fruit, that's doing a lot.
+00:02:28 Jordan
+So I'm sure it'd be good. I just, if you ask me like a day-to-day type thing, you know, that's more like a festival, a festive thing, you know, like if I had like a Christmas Eve brunch or something like that, that's like, would be on theme, To.
+00:02:43 Darius
+Be fair, nothing in their row is day-to-day.
+00:02:46 Jordan
+Well, that's true. close enough. I mean, every fast food place has a real.
+00:02:51 Darius
+Heavy, real heavy day-to-day, but I'm going with some as well. All right, row two, we got a club, chicken tenders, turkey melt, grilled cheese, or brisket melt. Where are we going with this one?
+00:03:03 Jordan
+I'm going with the brisket melt. I love brisket and anytime I can get that with some cheese or on some bread or in a nachos or whatever, pizza, whatever, I'll take that any day.
+00:03:15 Darius
+Turkey melt for me, same deal. I love turkey, little turkey sandwich. And then you got onion rings on there. So Basically the same gist that it is basically a grilled cheese with turkey, just like a brisket is a grilled cheese with brisket. So chicken tenders, I mean, I'm ambivalent about those. And a club is basically a turkey melt. You can do those anywhere. And Zod brother had it hot.
+00:03:39 Jordan
+Same.
+00:03:40 Darius
+So we're going with row. So we got, you got breakfast burrito, brisket melt and breakfast burrito, turkey melt. Row 3.
+00:03:51 Jordan
+Smothered gravy, yeah. Chicken fried steak, I think is basically what it is.
+00:03:54 Darius
+Yeah, that's what it looks like. Steak, cheeseburger, turkey, or lasagna. That is a really random roll. What you got?
+00:04:01 Jordan
+Yeah, it's a really random roll.
+00:04:03 Darius
+There's no thing to put it at all.
+00:04:05 Jordan
+Yeah, it's just giving like Golden Corral. ****** lower air food. Or K&amp;W on Sundays. I'm going to go with the first one. I'd go with the chicken fried steak.
+00:04:18 Darius
+Okay.
+00:04:18 Jordan
+Like some other gravy. It looks like mashed potatoes. Is that corn? I can't quite tell. Yeah, it's corn. Yeah, I'm cool with that. I'll take that. A good Sunday dinner type vibes.
+00:04:28 Darius
+White gravy or brown gravy? I know that's white gravy on the screen, but like which one would you prefer?
+00:04:35 Jordan
+For chicken fried steak, I'm going white.
+00:04:37 Darius
+Okay.
+00:04:37 Jordan
+Chicken fried steak, I'm going white.
+00:04:39 Darius
+I hate white gravy. I love brown gravy.
+00:04:41 Jordan
+Really.
+00:04:41 Darius
+But just as much as I hate white gravy, I love brown gravy.
+00:04:44 Jordan
+I also love sausage gravy.
+00:04:46 Darius
+Yeah, I could put brown gravy on anything and white gravy just reminds me of snot.
+00:04:53 Jordan
+So you might want to get that checked out.
+00:04:55 Darius
+It's really gross. Row 3 is tough.
+00:04:59 Jordan
+Yeah, there's a lot of good options.
+00:05:02 Darius
+But if I'm going with the best version of all of these, it's a lasagna.
+00:05:07 Jordan
+Okay.
+00:05:09 Darius
+Yeah, just. The best lasagna to me is better than the best version of the other four. And so that's the tiebreaker.
+00:05:16 Jordan
+I'm not mad at that.
+00:05:16 Darius
+I don't want the lasagna. If you get it with like a good, I don't like ricotta cheese, but if you just got a really cheesy one with some ground beef and some ground sausage and some good pasta sheets, it's tough to get that one. And we're going to head over to dessert, man. Brownie sundae, cheesecake, apple crumble, pumpkin pie, or cookie dough pie. Sweet potato pie. We're going to go ahead and sub that in a little bit.
+00:05:41 Jordan
+Yeah, okay, yeah, I thought about that.
+00:05:43 Darius
+I was like, oh. We're going to do that exchange. We're going to put sweet potato down there. So brownie sundae, cheesecake, crumble, sweet potato, or cookie dough.
+00:05:51 Jordan
+Yeah, although I do, I do, I don't have no beef with pumpkin pie. I do like pumpkin pie as well. I'm not going to lie. I'm a fan of all the winter vegetables.
+00:05:58 Darius
+Keep it in block. If you could blind tasted people, they wouldn't know the difference.
+00:06:01 Jordan
+It's not much difference.
+00:06:04 Darius
+Yeah.
+00:06:04 Jordan
+Well, I worked at a grid store when I was 16. It's like I had my own money. So I would just like buy those. So I actually am really good at tasting the difference because I just, that was like my, to me that was like buying a car type **** you know? Fair enough. You know, when you first get your own little money, you know, as a kid. So yeah, I think I'm going to go with the apple crumble. with the ice cream and the caramel looks like drizzled on top. Anytime I can get some sort of apple and ice cream or sweets together, I'm cool with that. But the brownie sundae looks good too, but you can kind of get that anywhere.
+00:06:40 Darius
+So yeah. the brownie sundae at any restaurant is almost certainly like just frozen. Yeah. Apple crumble for me too. Anytime I can get like a like a brown sugar cinnamon crust. I'm in.
+00:06:55 Jordan
+Yeah.
+00:06:56 Darius
+And so whatever you put in that crust is almost immaterial. So yeah, like that. There's a man, a good warm apple crumble with that scoop of that vanilla bean ice cream on top. It's smoking the field. The rest of those?
+00:07:10 Jordan
+Yeah. And to be honest, I'm really more of a pie person than a cake person. I got to be in the mood for cake or has to have like a certain like I prefer the Like the icing as opposed to like the whipped frosting, personally. And if they had had, if you saw about the cheesecake with like a key lime pie, I probably would have taken that because I do love a key lime pie.
+00:07:29 Darius
+I love a cheesecake, but like that cheesecake, like direct that. Yeah, the New York.
+00:07:34 Jordan
+Yeah.
+00:07:36 Darius
+But like, yeah, man, I just apple crumble is like, that's probably the My favorite dessert of them all. If I could pick any dessert, I think that one would win.
+00:07:46 Jordan
+Like any dessert of like in the world.
+00:07:48 Darius
+I think so. Yeah, I think so. Interesting. Like the best version of an apple crumble where like the apples are like in season and tender and it's like cinnamon and all spice and the crust is fresh and like crispy and buttery. I mean, what's beating that?
+00:08:06 Jordan
+I mean, I love banana pudding. with the Chessman cook cookies instead of the vanilla wafers. They're a little softer. I can **** ** some flan or some creme brulee any day. I'm a fan of the custards. All right, fair enough. Yeah, one of my old work moms, Puerto Ricans, she'd make those for us like in the holidays and stuff like that. So yeah, I love the custards. What else other good desserts do I like? I'm trying to think. I like ice cream cakes. What else, what else, what else? I'm trying to think. Yeah, like apple turnovers, anything like that, yeah.
+00:08:46 Darius
+Ice cream cake is a good one. I eat ice cream cake only on my birthday every year. Just growing up, it was like a. a special occasion. You got ice cream cake on your birthday because those cakes were quite pricey. And I've long since been able to just buy the cake whenever I want, but it's like a special birthday thing.
+00:09:05 Jordan
+That's how your brain is like conditioned it to.
+00:09:07 Darius
+It would feel like cheating to just like have it tonight, despite the fact that like it's $20. Like, you know, like, you can.
+00:09:14 Jordan
+Earn another year of life. So why should you have? Yeah.
+00:09:16 Darius
+But like, it's just with the Dairy Queen joint with the Crunchies in the middle and the gelatin on top. Man, listen, it's a birthday tradition. So rounding it up, you had the breakfast burrito, the brisket melt, the fried chicken, chicken fried steak, whatever you want to call it, apple crumble. And I went with breakfast burrito, turkey melt, lasagna, apple crumble. We are more unites us than divides us. So Yeah, write to us. Let us know what you guys picked on the thing and we'll put it up on the screen and yeah.
+00:09:53 Jordan
+What's your ideal menu of this four course situation?
+00:09:56 Darius
+And next week, if we don't have anything to start off with, we'll come up with another one. Heading into our first topic, it's you, man, habits and rituals.
+00:10:08 Jordan
+Yeah, so I think I actually found this online. What's a strange habit or ritual that you have that you rarely admit out loud?
+00:10:18 Darius
+You start.
+00:10:20 Jordan
+All right. Okay, I got a few. Whenever I go like on a long drive or like a long trip, I would say like a quick prayer just for like safety, you know, safe travels, you know, all that. That's one for sure.
+00:10:33 Darius
+I don't admit like that's.
+00:10:35 Jordan
+I mean, not that I don't admit it. I guess I just, I don't like, I'm not like a big like church person, and it's more private thing. I don't really do it. I do it silently. I don't really do it like out loud or, you know, so I guess that's more so the, it's more personal thing, I guess. Yeah, let's see. If I have a really bad day, I have to consume some sort of comedy entertainment. I have to be like, I can't just end the day and not like, I'll have to watch like a comedy movie or like a sitcom episode or I'll YouTube like a favorite scene from a movie or something that makes me laugh, whatever, something like that. Like I have to like make sure I laugh or smile at some point if I have a bad day. Like it could be the worst day ever and I'm like, you know, I need to YouTube ******* the office bloopers or some **** like that, whatever. I just like, no matter how bad the day is, I refuse to let the entire day be bad.
+00:11:28 Darius
+Okay.
+00:11:29 Jordan
+All right.
+00:11:30 Darius
+What else you got?
+00:11:35 Jordan
+As you know, you hear me pretty well. I can be pretty high strung, especially mostly when I'm in an irritated state. So you said it on me. I'm just nodding here. So I like I literally cannot sleep when I'm when I'm mad, like when I'm like fuming. So I will just like stay up. I'll do whatever I do to like to get that energy out before I can like get some rest. Like I will It could be 3 in the morning. I'd be like, **** it. I gotta go to the gym. And I'll think about whatever I'm mad at, wherever I'm mad at and just into the weights or whatever. If I gotta take a walk and walk 5 miles, then that's what I have to do. If I gotta drive to Durham and back three times, just straight up and down 70, then that's just what the **** I gotta do.
+00:12:24 Darius
+We got some, okay. So I was about to make the joke that you did the internet thing where you said unpopular opinion and then stated very common practices. Okay. Habits that I don't want to admit. I pray before a long drive. I decompress after bad days. It's hard for me to go to sleep when I'm anxious. But driving back and forth to Durham is genuinely weird.
+00:12:47 Jordan
+Yeah, no, I'll be like, **** this. I'll just drive up and down the road, U-turn after U-turn. I want to know what's weird about me.
+00:12:53 Darius
+After a hard day, I watch a comedy. That's me.
+00:12:58 Jordan
+Well, I have very like specific things that I watch. Like I have like my comfort movies are probably like a little unusual or not maybe standard, whatever. The awkward moment is one of my comfort movies, like when I'm upset. Or like, what if we reviewed that one with Daniel Radcliffe? Yeah, that's one of my comfort movies. Prisoner of Azkaban. I'm trying to think. What else? What else? What else? Maybe like Prince of Persia?
+00:13:21 Darius
+That's a deep cut.
+00:13:23 Jordan
+No, Prisoner of Azkaban. It's the third Harry Potter.
+00:13:26 Darius
+Oh, there's a Prince of Persia gayness movie with Jake Gyllenhaal.
+00:13:31 Jordan
+Jake Gyllenhaal. Yeah.
+00:13:33 Darius
+Titled similarly, I think.
+00:13:34 Jordan
+Yeah, I've seen that. I've seen that. Yeah. something. Yeah. I mean, I guess they're very, it's the way I cope. That's probably a little more niche than the coping itself.
+00:13:45 Darius
+All right. I'll get weird for us.
+00:13:48 Jordan
+Okay.
+00:13:49 Darius
+I no longer write it, but I usually write like Madden fan fiction. So like last week I said that we do franchise modes, but I don't do actual like, it's like in my head, they're characters like, and so It's not just like I will keep a guy on the team past his the time when I should come because of in my head what he means to the city in the video game and I used to like.
+00:14:19 Jordan
+Imaginary community service and stuff.
+00:14:21 Darius
+Correct. And so I would write, I would flesh these characters out and write them down. And I no longer write them down, but in my head, there was last year I was Vikings in the franchise mode and no, it happened twice. I was the Vikings in the franchise mode and TJ Hawkinson was like the tight end. He's a real tight end for the Vikings. And it was like year 10 of it. And we had won a bunch of Super Bowls together and it was like, it was time to let him go. And in our last Super Bowl, he scored a touchdown and I paused the game and like gave him his moment with the crowd. But that's like fake. Like that's not in the game. That was just me in my living room giving him his moment.
+00:14:58 Jordan
+Did you stand up and applaud?
+00:15:00 Darius
+Yes. That is something very weird that I do that I don't like anything out loud.
+00:15:09 Jordan
+Okay. When I.
+00:15:10 Darius
+Jog, depending on the song, I pretend I am having a concert and I'm on stage performing that song when I jog. And so it's very like, if you ever watch Save by the Bell, like the Zack attack type thing, when you like imagine, it helps me push through and like keep pace. Okay. Like I'm performing a song on stage. And so, Yeah, I write, used to write Madden fan fiction. Now it's mostly in my head. And yeah, I hold basically in imaginary concerts when I jog. So.
+00:15:44 Jordan
+Okay. I have a, okay, I got a couple more then. So I'm obviously very outgoing, but I actually do have an extremely introverted side that no one really believes or notices, I guess. I guess I camouflage it well. So before like big social events, especially if it's like booked in advance, I've like mentally prepared and done visualization exercises pretty much up until the moment I walk it through the door for a set event. You know, like I've thought about what I'm gonna wear, who I'm gonna see when I'm in the room, what we're gonna talk about or what I want to talk about with them, what I'm gonna bring to the function, you know, whatever. If I have songs I like, which ones am I gonna request on the aux or the Bluetooth, whatever, **** like that. I don't know if that's weird or not. A little different.
+00:16:32 Darius
+I have stop bits that like.
+00:16:35 Jordan
+You go to stores.
+00:16:36 Darius
+If I don't force them into the conversation, but if it gets there, I have it's almost just like a comedian has routine jokes that just when the sets dry, he can just lean on them. I have like four or five of those.
+00:16:49 Jordan
+Same.
+00:16:50 Darius
+If I just have to, you know, drive the social conversation for a little bit, which I don't particularly enjoy doing. But So mapping out the social interaction, that's we got one that actually counts.
+00:17:04 Jordan
+So I love making playlists. So I have a, when I perform poetry, I have a playlist called Performing, which a lot of songs just like get me like hype for performing, just get me in that mode to like be on, you know, and be, you know, at full capacity. A lot of them are about like just, you know, superstardom and pursuing dreams and, you know, being at the pinnacle, things of that nature. And so I play that on a loop while I'm getting dressed, while I'm driving to the venue, whatever case may be. I also will like visualize the crowd and visualize the pauses and the possible rewinds when I'm doing my lines and stuff like that. I practice like my hand gestures almost to a T for certain lines and stuff. I don't know if that's strange or not. I don't picture all these naked. I put everyone in their clothes.
+00:17:58 Darius
+I've never understood why that's supposed to work.
+00:18:01 Jordan
+Yeah, I don't get that either. I'd rather just not picture them. Yeah, enjoying the performance.
+00:18:10 Darius
+The few times I've had to publicly. Well, I'm not bad at publicly speaking when it's like as long as there's not like a stage. But the whole being elevated, just it's nerve-wracking.
+00:18:25 Jordan
+That is true.
+00:18:26 Darius
+Yeah.
+00:18:27 Jordan
+Especially with the lights, you can't see.
+00:18:30 Darius
+Yeah, man, it's like when I was, so I have siblings, but the gap is so large, it almost resets. Like my brother is 11 years older than me and my sister's 8 years older than me. So it's like, funks, like I'm not an only child, but like my upbringing was very solitary because like, I'm 10, they're 18 and 21. They not trying to kick it with me. like they out doing 18 and 21 year old ****. So I had my action figures and I had like, I would build out like wrestling storylines with the action figures. And I say all this to say, I have, you develop an extraordinary imagination when you have to entertain yourself before Netflix and smartphones. And so like I would, you know, take each each action figure had his own backstory and his own character, and then you would build out all of that. And yeah, I guess it's it's travel with me into Madden. So yeah, and other video games, but mostly the ones that sports games are easier because like, yeah, you stay with these characters year to year and, you know, watch them succeed and fail. So.
+00:19:40 Jordan
+Okay. I think I thought of another one. Whenever, especially over text, if I had a conversation with someone, I didn't like how that conversation went or I just didn't like the energy or the vibe and I don't want to harp on it, I will delete the text thread or delete those texts specifically. And if I'm really, really mad, then I'll just delete the text thread and delete their number altogether. And if they want to reconcile or if it's meant to be, then they will hit me back up and then I'll re-enter their name in my phone and resume the relationship. Dude, okay.
+00:20:17 Darius
+That's over the top. What are y'all falling out about? We gotta work on your conflict resolution skills.
+00:20:28 Jordan
+Yeah, I think that's my way of just like not cussing people out. It's just like, let me just act like the conversation didn't happen. And then if you can come back or I can get myself in a better headspace and you hit me up or something like that, then we can converse.
+00:20:40 Darius
+Makes sense?
+00:20:41 Jordan
+Nuke it.
+00:20:42 Darius
+If you can't see it, never happened.
+00:20:44 Jordan
+Correct.
+00:20:46 Darius
+All right. So we're heading into the next topic. So I got on here. What are some things you believe people are just pretending to like? Yeah, I have three food and artist and a movie, but you don't have to follow that structure at all. So you can let me have it, man. What you got?
+00:21:09 Jordan
+So the first one I have is adversity. I mean, it's a part of life and you do need to learn that skill. But it feels like sometimes people just glorify that **** all the time. And it's like, you know what? I'm not going to tell a homeless person that this is something good for them, that they'll come off stronger at the end of this. You know what I mean? Like, you know, that person whose life got fell apart because of a divorce, maybe their life won't get better after that. You know what I mean? I mean, hopefully it does. But you know what I'm saying? Like that whole thing of like trivializing and like toxic positivity, so to speak. It's like, some people die with broken hearts still. Meaning the storm did not end.
+00:21:48 Darius
+Toxic positivity is something I have a particular distaste for because like.
+00:21:54 Jordan
+Should be bad sometimes.
+00:21:55 Darius
+Should be bad. And like, it might not work out. Like that happens all the time. Like we've said this before, in particular about like Hollywood. It's like, there's a strong survivor bias. Like you only hear about John Ham, who got his first role when he was 40 and was waiting tables until then. But I promise you, there's 1000 people who went out there and it just didn't work. Like they just, yeah. It's like, they just don't get a TV show. They don't go, they don't win an Emmy to tell you it didn't work. Like they just never, ever hear their story. And it's like you only hear the rare survival stories. There's a strong survival bias when it comes to those Hollywood brags to riches stories. I know someone who moved to LA and he's fine, but it never, like he went there to act and it's been 10 years and I ain't seen him in no movies. He just lives there now. And that's what happens more often than not is that you just build a life out there and then just slowly give it up and just start working. And like you don't, move back home 'cause L.A. is still fun, but Right?
+00:22:57 Jordan
+But I say it's still a cool city.
+00:22:59 Darius
+It's still it's still no, but you still did something like it's still an accomplishment to move out there and build a new life, but yeah, absolutely. I moved out there to be an actor and I ain't seen no credits. You don't get a sack card? No, but that's the I mean. I don't want to be cheesy and say that's not a failure because the goal wasn't achieved. Yeah, because it's really not. He just moved in for work and the work just turned out to be a little differently than he expected. So yeah, I'm not mad at that. So artist MF Doom. We RIP.
+00:23:36 Jordan
+Rest in peace.
+00:23:37 Darius
+But I was not a hip. And then when he passed, People were clicking, sending, posting songs and I'm like, is there something wrong with my internet? This can't be the songs y'all are talking about.
+00:23:47 Jordan
+I'll be honest with you. I've never, I don't think I've ever heard one of these songs. I'm not gonna lie.
+00:23:51 Darius
+They're so bad. He's not good. I don't, get, I swear I don't get it. It's like, people like are hyped about it. And I'm just like, I don't understand it. You've heard the one line though. You've heard the one song that everyone talks about with the podcast, Chatty Patties. Rap snitches, tell them all their business, take them to court to be their own star witness. That's the MF Doom line when people quote that, that's MF Doom. So he was quite prescient with that line because these dudes be telling on themselves crazy. Movie, going to be a little controversial here because I understand why people pretend. Wakanda Forever was a mid pack. We can be honest. You do hate that movie. You do hate that movie. R.I.P. I get what I get. Yeah. The challenge at hand?
+00:24:41 Jordan
+The gist?
+00:24:41 Darius
+Yeah. But we are certainly not being honest. Like, yeah, you can't. I think the fever has tempered a little bit and you get people like if they if they make sure no one's listening, be honest about it. Yeah. I remember leaving that theater like that wasn't good. I was like, dude, I rip, but I didn't actually know him. And so, like, your job was to entertain me with a good movie, not throw a funeral for the cast. And you did not like, why? Why are we using the first hour of the movie to throw a funeral?
+00:25:21 Jordan
+Right.
+00:25:22 Darius
+On a multibillion dollar MCU project like you can we they recast it. It's time to move on. I get that. But like, As a consumer expecting a good movie, they did not deliver on that. And while I understand that it was under trying circumstances, I was not, I did not personally know Chadwick.
+00:25:40 Jordan
+And COVID too.
+00:25:41 Darius
+And COVID, but I did not personally know Chadwick, so I was not interested in attending his funeral and they made me. That's nuts.
+00:25:52 Jordan
+But I mean, it was a tough spot. it really was. I mean, they had no way to, they didn't know, they had no way to prepare. I mean, who knows how much time Coogler had to rewrite that whole script, Yeah, my big issue with that particular movie is I felt like the queen died for no reason. Like she just, they killed her and then there was, it was like, okay, you killed my mom, like I'm gonna try to kill you. Then it's like, oh, we need y'all. So let's piece it up.
+00:26:24 Darius
+The core tension is never resolved. It's like, they're in a blood feud and they just decide not to be and they only never explain why. And then it's like they introduce the little girl with the backpack and do nothing with her.
+00:26:36 Jordan
+Riri, yeah.
+00:26:38 Darius
+Lupita's in it for 10 minutes. I don't, like, she's the biggest star left.
+00:26:41 Jordan
+That was a waste of her.
+00:26:45 Darius
+And the movie just had no lead. That was the problem. But it just, you'd rather write a superhero movie without the superhero.
+00:26:52 Jordan
+With no superhero for the first two hours. It just didn't work. Yeah.
+00:26:58 Darius
+It was, you know, extraordinary circumstances, but I, the point of the prompt is what are things people, what are things people are pretending to like? We are 100% pretending to like that movie.
+00:27:09 Jordan
+Well, so, and it's like, it's funny you say that. I feel like that movie was, it's almost like as if you took The Lion King. And instead of focusing the movie on Simba, it was what happened to Pride Rock after Scar took over and Mufasa died. And but there's like no characters in that. Like, you know what I mean? Like, or like what happened when after Nala left to go find Simba. And it's like, okay, well, the mom's just there chilling, being abused by Scar. Everybody's surrendered. There's not much of a story there. You know what I'm saying?
+00:27:39 Darius
+I'm more interested in what's happening off screen and you're not showing me that. And I just, that was, I felt like I was taking crazy pills at the time because people were like. They did it though. Oh my God, it was so amazing.
+00:27:56 Jordan
+No, the scenery was beautiful. The cinematography was great. Obviously the water stuff was super awesome. Also, we spent the whole movie getting our ***** whipped by the blue people.
+00:28:05 Darius
+Yeah.
+00:28:06 Jordan
+So there was that too.
+00:28:08 Darius
+I saw it in IMAX and it was a beautifully shot movie.
+00:28:11 Jordan
+Yeah, absolutely. Stunning movie, great soundtrack.
+00:28:15 Darius
+We give him that. Neymar was a great villain.
+00:28:18 Jordan
+He was cold. He was awesome.
+00:28:20 Darius
+They just didn't do anything with him. And I don't think they have since, have they? I stopped watching after that one.
+00:28:26 Jordan
+Well, I'm pretty sure he's gonna be in Doomsday and probably Secret Wars. So we'll see what they do with that. Also, remember he caught, there was like some accusation against him. So I don't know if that's what caused him to not be in anything for a minute. I can't keep up.
+00:28:40 Darius
+What else you got for this one?
+00:28:44 Jordan
+I think that's all I had to be honest with you. I mean, you got two more if you, if you got those.
+00:28:48 Darius
+No, I mean, I've said it before. I'll hear sushi is something that.
+00:28:51 Jordan
+That's so crazy. I knew you were going to say that. I don't. You like rice, right?
+00:28:56 Darius
+Okay, but I like bland rice, under salted rice with a piece of fish on top that's raw. That only tastes like something. It's just a vehicle for soy sauce. And that's that yellow flap thing that just kind of tastes like I just don't. I don't understand it. It's.
+00:29:20 Jordan
+I love sushi.
+00:29:21 Darius
+You know, we have invented fire now. We like meat just tastes better when it's hot and it's like brought to have to be nuked, but like, you know, brought to a decent temperature. You know, every time I eat sushi, I think to myself, this would taste a lot better hot and cooked. So I think it's like people don't want to sound like simpletons by saying that they just, they want their food cooked. Yeah. Cause I guess that reads low class, but I'll be the one to say it. I will stand before history and say, stop. This **** is trash.
+00:29:54 Jordan
+You know what? Okay, I got one. I feel like people, a lot of people pretend to know how to use chopsticks. I think a lot of people are lying about knowing how to use chopsticks. There's A TikTok to a bar. This guy was holding chopsticks. He was showing how he fakes used them. So he literally is holding chopsticks and he grabs the food with his fingers and puts it like this and he's holding the chopsticks like this and he acts exactly like he just scooped it up with the chopsticks.
+00:30:18 Darius
+Yeah, it's like. It's a stupid way to eat food. You have forks and spoons. Why would we do this? It's like even like some cultures eat with their hands and like that's fine. I love finger food and I have no problem with that. You know, you wash your hands, that's cool. But like there's nothing chopsticks do better than a fork and a spoon and a knife. Not a single thing. It's just the dumbest way to use them though.
+00:30:42 Jordan
+Yeah, it's fine. But it is a flex. It's definitely flex.
+00:30:44 Darius
+You only got to use a typewriter. Like it's just useless now. Do you want to know how to eat like it's the 1400s and we don't haven't invented anything since then? All right, sure. But we have invented plastics and what are true? Silver.
+00:31:02 Jordan
+Utensils, silverware.
+00:31:04 Darius
+No, what is it made out of? I was thinking the metal, but it's definitely not silver. But anyways, we've invented a better way to do this and we should use it.
+00:31:11 Jordan
+I'm trying to think, what else do I think people are pretending to like? Work. I think a lot of people pretend to like work. I don't mean like their particular job. I mean like the whole like grinding culture, like don't ever ******* sleep. Wake up at 5 A.m. And if you know that this whole thing where it's like you got 8 hours of sleep, 8 hours to work, you still got 8 hours to make the rest of your life phenomenal. A</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Topics Covered&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Favorite four-course meals, dessert rankings, and why apple crumble deserves more respect.&lt;/li&gt;
+    &lt;li&gt;Strange personal habits and rituals people rarely admit out loud.&lt;/li&gt;
+    &lt;li&gt;Comfort movies, driving with no destination, and pre-event visualization.&lt;/li&gt;
+    &lt;li&gt;Creating fictional sports storylines and Madden fan fiction.&lt;/li&gt;
+    &lt;li&gt;Things people pretend to like, including adversity, sushi, chopsticks, grind culture, and certain forms of artistic prestige.&lt;/li&gt;
+    &lt;li&gt;Whether people genuinely enjoy struggling or simply enjoy the story that comes afterward.&lt;/li&gt;
+    &lt;li&gt;The difference between ignorance and stupidity.&lt;/li&gt;
+    &lt;li&gt;Bad advice that sounds good but produces terrible outcomes.&lt;/li&gt;
+    &lt;li&gt;&amp;quot;Live life to the fullest&amp;quot; versus making smart long-term decisions.&lt;/li&gt;
+    &lt;li&gt;What is genuinely better today than it has ever been.&lt;/li&gt;
+    &lt;li&gt;Modern technology, access to information, food variety, and consumer convenience.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Questions&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;What strange habit or ritual do you do that you rarely admit to other people?&lt;/li&gt;
+    &lt;li&gt;What is something people only pretend to like?&lt;/li&gt;
+    &lt;li&gt;Do people actually value adversity, or do they only value surviving it?&lt;/li&gt;
+    &lt;li&gt;What is the worst advice you&amp;#39;ve ever received?&lt;/li&gt;
+    &lt;li&gt;What common piece of wisdom sounds good but falls apart in practice?&lt;/li&gt;
+    &lt;li&gt;What is better today than it was for previous generations?&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Observations&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Most people do not enjoy adversity itself; they enjoy the growth, lessons, or stories that come after it.&lt;/li&gt;
+    &lt;li&gt;Comfort routines often exist because they provide stability during stressful periods of life.&lt;/li&gt;
+    &lt;li&gt;Prestige and popularity can pressure people into claiming they enjoy things they actually don&amp;#39;t.&lt;/li&gt;
+    &lt;li&gt;Ignorance can be corrected with information, but poor judgment is much harder to fix.&lt;/li&gt;
+    &lt;li&gt;Bad decisions often compound in ways that are invisible until years later.&lt;/li&gt;
+    &lt;li&gt;Modern life has dramatically improved access to information, education, food, and technology for curious people.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Debate&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Do People Pretend To Like Adversity?&lt;/strong&gt; Jordan argued that adversity is often romanticized and that many people claim to appreciate hardship only after surviving it. Darius agreed that struggle itself is unpleasant and pointed out that some storms never end, making the common &amp;quot;everything happens for a reason&amp;quot; narrative far less comforting than people pretend.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Personal Habits&lt;/li&gt;
+      &lt;li&gt;Self-Awareness&lt;/li&gt;
+      &lt;li&gt;Comfort Routines&lt;/li&gt;
+      &lt;li&gt;Adversity&lt;/li&gt;
+      &lt;li&gt;Personal Growth&lt;/li&gt;
+      &lt;li&gt;Bad Advice&lt;/li&gt;
+      &lt;li&gt;Decision Making&lt;/li&gt;
+      &lt;li&gt;Modern Technology&lt;/li&gt;
+      &lt;li&gt;Education&lt;/li&gt;
+      &lt;li&gt;Information Access&lt;/li&gt;
+      &lt;li&gt;Food Culture&lt;/li&gt;
+      &lt;li&gt;Everyday Philosophy&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="mm\.dd\.yy"/>
+  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -9437,7 +9847,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9459,6 +9869,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9475,6 +9887,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9794,7 +10210,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -10486,6 +10902,21 @@
         <v>265</v>
       </c>
       <c r="E41" s="5"/>
+    </row>
+    <row r="42" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>268</v>
+      </c>
+      <c r="B42" t="s">
+        <v>262</v>
+      </c>
+      <c r="C42" s="9">
+        <v>46297</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E42" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E41" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}"/>
@@ -10499,7 +10930,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -11082,6 +11513,20 @@
         <v>263</v>
       </c>
     </row>
+    <row r="42" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>268</v>
+      </c>
+      <c r="B42" t="s">
+        <v>262</v>
+      </c>
+      <c r="C42" s="10">
+        <v>46297</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D40" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
     <filterColumn colId="3">

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1A510D-F22A-4F63-8BD8-73489D1F3FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14BE534-751D-4A0A-9846-FCA901F72710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="268">
   <si>
     <t>youtube_link</t>
   </si>
@@ -9352,421 +9352,11 @@
   <si>
     <t>https://www.youtube.com/watch?v=M4_pR6sS5zM&amp;t=1s</t>
   </si>
-  <si>
-    <t>What Are People Pretending to Like</t>
-  </si>
-  <si>
-    <t>Transcript
-00:00:00 Darius
-about to make the joke that you did the internet thing where you said unpopular opinion and then stated very common practices. It's like habits that I don't want to admit. I pray before a long drive. I decompress after bad days. It's hard for me to go to sleep when I'm anxious. But driving back and forth to Durham is genuinely weird.
-00:00:21 Jordan
-Yeah, I'll be like, **** this. Yeah, I just. I just jump up and down the road. U-turn after U-turn. I don't know what's weird about me.
-00:00:27 Darius
-After a hard day, I watch a comedy. That's. That's me.
-00:00:32 Jordan
-Well, I'm very like, specific.
-00:00:33 Darius
-Out trunk with Jordan and Darius. My name is Darius. That's these all up in the area on all socials.
-00:00:38 Jordan
-And I'm Jordan. That's Jordan to be writing on all socials.
-00:00:41 Darius
-This is our What's On Our Mind segment where we let you guys know what's on our mind, what we've seen on the internet, things that we want to talk about. Do a little engagement bait, starting it off. We got, I'm going to put the graphic up on the screen here. We're picking one per row. Just a way to let you guys get to know us. What you got for, we're good. Just going to number the rows one, two, three. Just pick, just pick one for each row. And then we'll just go and go from there. So what you got for the first row, A, B, C, D, or E?
-00:01:12 Jordan
-I'm going with the breakfast burrito for row C. I love, you know, breakfast food. Anytime I can get in sort of like an efficient way like that, you know, it's always nice. I love omelets, but I got to be in the mood for hash browns. Same thing with pancakes too. I'm kind of weird about that kind of stuff. And the red velvet fridge toast, that just feels like a Saturday thing. You know what I mean? I couldn't have that like on a weekday and work. I'd need like 4 hours of sleep after that, you know?
-00:01:38 Darius
-Yeah, I'm not big on red velvet anything.
-00:01:43 Jordan
-Really.
-00:01:44 Darius
-It's just not, doesn't really do it for me. Yeah, breakfast burrito as well. Like you said, it's efficient. It hits all the bases. I do love hash browns, so I would like hash browns in my breakfast burrito.
-00:01:57 Jordan
-I'm not mad at that.
-00:01:58 Darius
-Pancakes are really hit or miss. Really hit or miss.
-00:02:01 Jordan
-I got to I got to really be. I feel like there's a weekend thing because you just who has time to like Sydney pancakes during the week, you know?
-00:02:07 Darius
-They're just and then when you do get them, they're so infrequently done right. And so omelets, I love an omelet, but if I can just put it all wrapped into a burrito, that's fine. Grand slam, which that's doing too much.
-00:02:19 Jordan
-Yeah.
-00:02:20 Darius
-And I love French toast, but stuffed red velvet, strawberry cream, fruit, that's doing a lot.
-00:02:28 Jordan
-So I'm sure it'd be good. I just, if you ask me like a day-to-day type thing, you know, that's more like a festival, a festive thing, you know, like if I had like a Christmas Eve brunch or something like that, that's like, would be on theme, To.
-00:02:43 Darius
-Be fair, nothing in their row is day-to-day.
-00:02:46 Jordan
-Well, that's true. close enough. I mean, every fast food place has a real.
-00:02:51 Darius
-Heavy, real heavy day-to-day, but I'm going with some as well. All right, row two, we got a club, chicken tenders, turkey melt, grilled cheese, or brisket melt. Where are we going with this one?
-00:03:03 Jordan
-I'm going with the brisket melt. I love brisket and anytime I can get that with some cheese or on some bread or in a nachos or whatever, pizza, whatever, I'll take that any day.
-00:03:15 Darius
-Turkey melt for me, same deal. I love turkey, little turkey sandwich. And then you got onion rings on there. So Basically the same gist that it is basically a grilled cheese with turkey, just like a brisket is a grilled cheese with brisket. So chicken tenders, I mean, I'm ambivalent about those. And a club is basically a turkey melt. You can do those anywhere. And Zod brother had it hot.
-00:03:39 Jordan
-Same.
-00:03:40 Darius
-So we're going with row. So we got, you got breakfast burrito, brisket melt and breakfast burrito, turkey melt. Row 3.
-00:03:51 Jordan
-Smothered gravy, yeah. Chicken fried steak, I think is basically what it is.
-00:03:54 Darius
-Yeah, that's what it looks like. Steak, cheeseburger, turkey, or lasagna. That is a really random roll. What you got?
-00:04:01 Jordan
-Yeah, it's a really random roll.
-00:04:03 Darius
-There's no thing to put it at all.
-00:04:05 Jordan
-Yeah, it's just giving like Golden Corral. ****** lower air food. Or K&amp;W on Sundays. I'm going to go with the first one. I'd go with the chicken fried steak.
-00:04:18 Darius
-Okay.
-00:04:18 Jordan
-Like some other gravy. It looks like mashed potatoes. Is that corn? I can't quite tell. Yeah, it's corn. Yeah, I'm cool with that. I'll take that. A good Sunday dinner type vibes.
-00:04:28 Darius
-White gravy or brown gravy? I know that's white gravy on the screen, but like which one would you prefer?
-00:04:35 Jordan
-For chicken fried steak, I'm going white.
-00:04:37 Darius
-Okay.
-00:04:37 Jordan
-Chicken fried steak, I'm going white.
-00:04:39 Darius
-I hate white gravy. I love brown gravy.
-00:04:41 Jordan
-Really.
-00:04:41 Darius
-But just as much as I hate white gravy, I love brown gravy.
-00:04:44 Jordan
-I also love sausage gravy.
-00:04:46 Darius
-Yeah, I could put brown gravy on anything and white gravy just reminds me of snot.
-00:04:53 Jordan
-So you might want to get that checked out.
-00:04:55 Darius
-It's really gross. Row 3 is tough.
-00:04:59 Jordan
-Yeah, there's a lot of good options.
-00:05:02 Darius
-But if I'm going with the best version of all of these, it's a lasagna.
-00:05:07 Jordan
-Okay.
-00:05:09 Darius
-Yeah, just. The best lasagna to me is better than the best version of the other four. And so that's the tiebreaker.
-00:05:16 Jordan
-I'm not mad at that.
-00:05:16 Darius
-I don't want the lasagna. If you get it with like a good, I don't like ricotta cheese, but if you just got a really cheesy one with some ground beef and some ground sausage and some good pasta sheets, it's tough to get that one. And we're going to head over to dessert, man. Brownie sundae, cheesecake, apple crumble, pumpkin pie, or cookie dough pie. Sweet potato pie. We're going to go ahead and sub that in a little bit.
-00:05:41 Jordan
-Yeah, okay, yeah, I thought about that.
-00:05:43 Darius
-I was like, oh. We're going to do that exchange. We're going to put sweet potato down there. So brownie sundae, cheesecake, crumble, sweet potato, or cookie dough.
-00:05:51 Jordan
-Yeah, although I do, I do, I don't have no beef with pumpkin pie. I do like pumpkin pie as well. I'm not going to lie. I'm a fan of all the winter vegetables.
-00:05:58 Darius
-Keep it in block. If you could blind tasted people, they wouldn't know the difference.
-00:06:01 Jordan
-It's not much difference.
-00:06:04 Darius
-Yeah.
-00:06:04 Jordan
-Well, I worked at a grid store when I was 16. It's like I had my own money. So I would just like buy those. So I actually am really good at tasting the difference because I just, that was like my, to me that was like buying a car type **** you know? Fair enough. You know, when you first get your own little money, you know, as a kid. So yeah, I think I'm going to go with the apple crumble. with the ice cream and the caramel looks like drizzled on top. Anytime I can get some sort of apple and ice cream or sweets together, I'm cool with that. But the brownie sundae looks good too, but you can kind of get that anywhere.
-00:06:40 Darius
-So yeah. the brownie sundae at any restaurant is almost certainly like just frozen. Yeah. Apple crumble for me too. Anytime I can get like a like a brown sugar cinnamon crust. I'm in.
-00:06:55 Jordan
-Yeah.
-00:06:56 Darius
-And so whatever you put in that crust is almost immaterial. So yeah, like that. There's a man, a good warm apple crumble with that scoop of that vanilla bean ice cream on top. It's smoking the field. The rest of those?
-00:07:10 Jordan
-Yeah. And to be honest, I'm really more of a pie person than a cake person. I got to be in the mood for cake or has to have like a certain like I prefer the Like the icing as opposed to like the whipped frosting, personally. And if they had had, if you saw about the cheesecake with like a key lime pie, I probably would have taken that because I do love a key lime pie.
-00:07:29 Darius
-I love a cheesecake, but like that cheesecake, like direct that. Yeah, the New York.
-00:07:34 Jordan
-Yeah.
-00:07:36 Darius
-But like, yeah, man, I just apple crumble is like, that's probably the My favorite dessert of them all. If I could pick any dessert, I think that one would win.
-00:07:46 Jordan
-Like any dessert of like in the world.
-00:07:48 Darius
-I think so. Yeah, I think so. Interesting. Like the best version of an apple crumble where like the apples are like in season and tender and it's like cinnamon and all spice and the crust is fresh and like crispy and buttery. I mean, what's beating that?
-00:08:06 Jordan
-I mean, I love banana pudding. with the Chessman cook cookies instead of the vanilla wafers. They're a little softer. I can **** ** some flan or some creme brulee any day. I'm a fan of the custards. All right, fair enough. Yeah, one of my old work moms, Puerto Ricans, she'd make those for us like in the holidays and stuff like that. So yeah, I love the custards. What else other good desserts do I like? I'm trying to think. I like ice cream cakes. What else, what else, what else? I'm trying to think. Yeah, like apple turnovers, anything like that, yeah.
-00:08:46 Darius
-Ice cream cake is a good one. I eat ice cream cake only on my birthday every year. Just growing up, it was like a. a special occasion. You got ice cream cake on your birthday because those cakes were quite pricey. And I've long since been able to just buy the cake whenever I want, but it's like a special birthday thing.
-00:09:05 Jordan
-That's how your brain is like conditioned it to.
-00:09:07 Darius
-It would feel like cheating to just like have it tonight, despite the fact that like it's $20. Like, you know, like, you can.
-00:09:14 Jordan
-Earn another year of life. So why should you have? Yeah.
-00:09:16 Darius
-But like, it's just with the Dairy Queen joint with the Crunchies in the middle and the gelatin on top. Man, listen, it's a birthday tradition. So rounding it up, you had the breakfast burrito, the brisket melt, the fried chicken, chicken fried steak, whatever you want to call it, apple crumble. And I went with breakfast burrito, turkey melt, lasagna, apple crumble. We are more unites us than divides us. So Yeah, write to us. Let us know what you guys picked on the thing and we'll put it up on the screen and yeah.
-00:09:53 Jordan
-What's your ideal menu of this four course situation?
-00:09:56 Darius
-And next week, if we don't have anything to start off with, we'll come up with another one. Heading into our first topic, it's you, man, habits and rituals.
-00:10:08 Jordan
-Yeah, so I think I actually found this online. What's a strange habit or ritual that you have that you rarely admit out loud?
-00:10:18 Darius
-You start.
-00:10:20 Jordan
-All right. Okay, I got a few. Whenever I go like on a long drive or like a long trip, I would say like a quick prayer just for like safety, you know, safe travels, you know, all that. That's one for sure.
-00:10:33 Darius
-I don't admit like that's.
-00:10:35 Jordan
-I mean, not that I don't admit it. I guess I just, I don't like, I'm not like a big like church person, and it's more private thing. I don't really do it. I do it silently. I don't really do it like out loud or, you know, so I guess that's more so the, it's more personal thing, I guess. Yeah, let's see. If I have a really bad day, I have to consume some sort of comedy entertainment. I have to be like, I can't just end the day and not like, I'll have to watch like a comedy movie or like a sitcom episode or I'll YouTube like a favorite scene from a movie or something that makes me laugh, whatever, something like that. Like I have to like make sure I laugh or smile at some point if I have a bad day. Like it could be the worst day ever and I'm like, you know, I need to YouTube ******* the office bloopers or some **** like that, whatever. I just like, no matter how bad the day is, I refuse to let the entire day be bad.
-00:11:28 Darius
-Okay.
-00:11:29 Jordan
-All right.
-00:11:30 Darius
-What else you got?
-00:11:35 Jordan
-As you know, you hear me pretty well. I can be pretty high strung, especially mostly when I'm in an irritated state. So you said it on me. I'm just nodding here. So I like I literally cannot sleep when I'm when I'm mad, like when I'm like fuming. So I will just like stay up. I'll do whatever I do to like to get that energy out before I can like get some rest. Like I will It could be 3 in the morning. I'd be like, **** it. I gotta go to the gym. And I'll think about whatever I'm mad at, wherever I'm mad at and just into the weights or whatever. If I gotta take a walk and walk 5 miles, then that's what I have to do. If I gotta drive to Durham and back three times, just straight up and down 70, then that's just what the **** I gotta do.
-00:12:24 Darius
-We got some, okay. So I was about to make the joke that you did the internet thing where you said unpopular opinion and then stated very common practices. Okay. Habits that I don't want to admit. I pray before a long drive. I decompress after bad days. It's hard for me to go to sleep when I'm anxious. But driving back and forth to Durham is genuinely weird.
-00:12:47 Jordan
-Yeah, no, I'll be like, **** this. I'll just drive up and down the road, U-turn after U-turn. I want to know what's weird about me.
-00:12:53 Darius
-After a hard day, I watch a comedy. That's me.
-00:12:58 Jordan
-Well, I have very like specific things that I watch. Like I have like my comfort movies are probably like a little unusual or not maybe standard, whatever. The awkward moment is one of my comfort movies, like when I'm upset. Or like, what if we reviewed that one with Daniel Radcliffe? Yeah, that's one of my comfort movies. Prisoner of Azkaban. I'm trying to think. What else? What else? What else? Maybe like Prince of Persia?
-00:13:21 Darius
-That's a deep cut.
-00:13:23 Jordan
-No, Prisoner of Azkaban. It's the third Harry Potter.
-00:13:26 Darius
-Oh, there's a Prince of Persia gayness movie with Jake Gyllenhaal.
-00:13:31 Jordan
-Jake Gyllenhaal. Yeah.
-00:13:33 Darius
-Titled similarly, I think.
-00:13:34 Jordan
-Yeah, I've seen that. I've seen that. Yeah. something. Yeah. I mean, I guess they're very, it's the way I cope. That's probably a little more niche than the coping itself.
-00:13:45 Darius
-All right. I'll get weird for us.
-00:13:48 Jordan
-Okay.
-00:13:49 Darius
-I no longer write it, but I usually write like Madden fan fiction. So like last week I said that we do franchise modes, but I don't do actual like, it's like in my head, they're characters like, and so It's not just like I will keep a guy on the team past his the time when I should come because of in my head what he means to the city in the video game and I used to like.
-00:14:19 Jordan
-Imaginary community service and stuff.
-00:14:21 Darius
-Correct. And so I would write, I would flesh these characters out and write them down. And I no longer write them down, but in my head, there was last year I was Vikings in the franchise mode and no, it happened twice. I was the Vikings in the franchise mode and TJ Hawkinson was like the tight end. He's a real tight end for the Vikings. And it was like year 10 of it. And we had won a bunch of Super Bowls together and it was like, it was time to let him go. And in our last Super Bowl, he scored a touchdown and I paused the game and like gave him his moment with the crowd. But that's like fake. Like that's not in the game. That was just me in my living room giving him his moment.
-00:14:58 Jordan
-Did you stand up and applaud?
-00:15:00 Darius
-Yes. That is something very weird that I do that I don't like anything out loud.
-00:15:09 Jordan
-Okay. When I.
-00:15:10 Darius
-Jog, depending on the song, I pretend I am having a concert and I'm on stage performing that song when I jog. And so it's very like, if you ever watch Save by the Bell, like the Zack attack type thing, when you like imagine, it helps me push through and like keep pace. Okay. Like I'm performing a song on stage. And so, Yeah, I write, used to write Madden fan fiction. Now it's mostly in my head. And yeah, I hold basically in imaginary concerts when I jog. So.
-00:15:44 Jordan
-Okay. I have a, okay, I got a couple more then. So I'm obviously very outgoing, but I actually do have an extremely introverted side that no one really believes or notices, I guess. I guess I camouflage it well. So before like big social events, especially if it's like booked in advance, I've like mentally prepared and done visualization exercises pretty much up until the moment I walk it through the door for a set event. You know, like I've thought about what I'm gonna wear, who I'm gonna see when I'm in the room, what we're gonna talk about or what I want to talk about with them, what I'm gonna bring to the function, you know, whatever. If I have songs I like, which ones am I gonna request on the aux or the Bluetooth, whatever, **** like that. I don't know if that's weird or not. A little different.
-00:16:32 Darius
-I have stop bits that like.
-00:16:35 Jordan
-You go to stores.
-00:16:36 Darius
-If I don't force them into the conversation, but if it gets there, I have it's almost just like a comedian has routine jokes that just when the sets dry, he can just lean on them. I have like four or five of those.
-00:16:49 Jordan
-Same.
-00:16:50 Darius
-If I just have to, you know, drive the social conversation for a little bit, which I don't particularly enjoy doing. But So mapping out the social interaction, that's we got one that actually counts.
-00:17:04 Jordan
-So I love making playlists. So I have a, when I perform poetry, I have a playlist called Performing, which a lot of songs just like get me like hype for performing, just get me in that mode to like be on, you know, and be, you know, at full capacity. A lot of them are about like just, you know, superstardom and pursuing dreams and, you know, being at the pinnacle, things of that nature. And so I play that on a loop while I'm getting dressed, while I'm driving to the venue, whatever case may be. I also will like visualize the crowd and visualize the pauses and the possible rewinds when I'm doing my lines and stuff like that. I practice like my hand gestures almost to a T for certain lines and stuff. I don't know if that's strange or not. I don't picture all these naked. I put everyone in their clothes.
-00:17:58 Darius
-I've never understood why that's supposed to work.
-00:18:01 Jordan
-Yeah, I don't get that either. I'd rather just not picture them. Yeah, enjoying the performance.
-00:18:10 Darius
-The few times I've had to publicly. Well, I'm not bad at publicly speaking when it's like as long as there's not like a stage. But the whole being elevated, just it's nerve-wracking.
-00:18:25 Jordan
-That is true.
-00:18:26 Darius
-Yeah.
-00:18:27 Jordan
-Especially with the lights, you can't see.
-00:18:30 Darius
-Yeah, man, it's like when I was, so I have siblings, but the gap is so large, it almost resets. Like my brother is 11 years older than me and my sister's 8 years older than me. So it's like, funks, like I'm not an only child, but like my upbringing was very solitary because like, I'm 10, they're 18 and 21. They not trying to kick it with me. like they out doing 18 and 21 year old ****. So I had my action figures and I had like, I would build out like wrestling storylines with the action figures. And I say all this to say, I have, you develop an extraordinary imagination when you have to entertain yourself before Netflix and smartphones. And so like I would, you know, take each each action figure had his own backstory and his own character, and then you would build out all of that. And yeah, I guess it's it's travel with me into Madden. So yeah, and other video games, but mostly the ones that sports games are easier because like, yeah, you stay with these characters year to year and, you know, watch them succeed and fail. So.
-00:19:40 Jordan
-Okay. I think I thought of another one. Whenever, especially over text, if I had a conversation with someone, I didn't like how that conversation went or I just didn't like the energy or the vibe and I don't want to harp on it, I will delete the text thread or delete those texts specifically. And if I'm really, really mad, then I'll just delete the text thread and delete their number altogether. And if they want to reconcile or if it's meant to be, then they will hit me back up and then I'll re-enter their name in my phone and resume the relationship. Dude, okay.
-00:20:17 Darius
-That's over the top. What are y'all falling out about? We gotta work on your conflict resolution skills.
-00:20:28 Jordan
-Yeah, I think that's my way of just like not cussing people out. It's just like, let me just act like the conversation didn't happen. And then if you can come back or I can get myself in a better headspace and you hit me up or something like that, then we can converse.
-00:20:40 Darius
-Makes sense?
-00:20:41 Jordan
-Nuke it.
-00:20:42 Darius
-If you can't see it, never happened.
-00:20:44 Jordan
-Correct.
-00:20:46 Darius
-All right. So we're heading into the next topic. So I got on here. What are some things you believe people are just pretending to like? Yeah, I have three food and artist and a movie, but you don't have to follow that structure at all. So you can let me have it, man. What you got?
-00:21:09 Jordan
-So the first one I have is adversity. I mean, it's a part of life and you do need to learn that skill. But it feels like sometimes people just glorify that **** all the time. And it's like, you know what? I'm not going to tell a homeless person that this is something good for them, that they'll come off stronger at the end of this. You know what I mean? Like, you know, that person whose life got fell apart because of a divorce, maybe their life won't get better after that. You know what I mean? I mean, hopefully it does. But you know what I'm saying? Like that whole thing of like trivializing and like toxic positivity, so to speak. It's like, some people die with broken hearts still. Meaning the storm did not end.
-00:21:48 Darius
-Toxic positivity is something I have a particular distaste for because like.
-00:21:54 Jordan
-Should be bad sometimes.
-00:21:55 Darius
-Should be bad. And like, it might not work out. Like that happens all the time. Like we've said this before, in particular about like Hollywood. It's like, there's a strong survivor bias. Like you only hear about John Ham, who got his first role when he was 40 and was waiting tables until then. But I promise you, there's 1000 people who went out there and it just didn't work. Like they just, yeah. It's like, they just don't get a TV show. They don't go, they don't win an Emmy to tell you it didn't work. Like they just never, ever hear their story. And it's like you only hear the rare survival stories. There's a strong survival bias when it comes to those Hollywood brags to riches stories. I know someone who moved to LA and he's fine, but it never, like he went there to act and it's been 10 years and I ain't seen him in no movies. He just lives there now. And that's what happens more often than not is that you just build a life out there and then just slowly give it up and just start working. And like you don't, move back home 'cause L.A. is still fun, but Right?
-00:22:57 Jordan
-But I say it's still a cool city.
-00:22:59 Darius
-It's still it's still no, but you still did something like it's still an accomplishment to move out there and build a new life, but yeah, absolutely. I moved out there to be an actor and I ain't seen no credits. You don't get a sack card? No, but that's the I mean. I don't want to be cheesy and say that's not a failure because the goal wasn't achieved. Yeah, because it's really not. He just moved in for work and the work just turned out to be a little differently than he expected. So yeah, I'm not mad at that. So artist MF Doom. We RIP.
-00:23:36 Jordan
-Rest in peace.
-00:23:37 Darius
-But I was not a hip. And then when he passed, People were clicking, sending, posting songs and I'm like, is there something wrong with my internet? This can't be the songs y'all are talking about.
-00:23:47 Jordan
-I'll be honest with you. I've never, I don't think I've ever heard one of these songs. I'm not gonna lie.
-00:23:51 Darius
-They're so bad. He's not good. I don't, get, I swear I don't get it. It's like, people like are hyped about it. And I'm just like, I don't understand it. You've heard the one line though. You've heard the one song that everyone talks about with the podcast, Chatty Patties. Rap snitches, tell them all their business, take them to court to be their own star witness. That's the MF Doom line when people quote that, that's MF Doom. So he was quite prescient with that line because these dudes be telling on themselves crazy. Movie, going to be a little controversial here because I understand why people pretend. Wakanda Forever was a mid pack. We can be honest. You do hate that movie. You do hate that movie. R.I.P. I get what I get. Yeah. The challenge at hand?
-00:24:41 Jordan
-The gist?
-00:24:41 Darius
-Yeah. But we are certainly not being honest. Like, yeah, you can't. I think the fever has tempered a little bit and you get people like if they if they make sure no one's listening, be honest about it. Yeah. I remember leaving that theater like that wasn't good. I was like, dude, I rip, but I didn't actually know him. And so, like, your job was to entertain me with a good movie, not throw a funeral for the cast. And you did not like, why? Why are we using the first hour of the movie to throw a funeral?
-00:25:21 Jordan
-Right.
-00:25:22 Darius
-On a multibillion dollar MCU project like you can we they recast it. It's time to move on. I get that. But like, As a consumer expecting a good movie, they did not deliver on that. And while I understand that it was under trying circumstances, I was not, I did not personally know Chadwick.
-00:25:40 Jordan
-And COVID too.
-00:25:41 Darius
-And COVID, but I did not personally know Chadwick, so I was not interested in attending his funeral and they made me. That's nuts.
-00:25:52 Jordan
-But I mean, it was a tough spot. it really was. I mean, they had no way to, they didn't know, they had no way to prepare. I mean, who knows how much time Coogler had to rewrite that whole script, Yeah, my big issue with that particular movie is I felt like the queen died for no reason. Like she just, they killed her and then there was, it was like, okay, you killed my mom, like I'm gonna try to kill you. Then it's like, oh, we need y'all. So let's piece it up.
-00:26:24 Darius
-The core tension is never resolved. It's like, they're in a blood feud and they just decide not to be and they only never explain why. And then it's like they introduce the little girl with the backpack and do nothing with her.
-00:26:36 Jordan
-Riri, yeah.
-00:26:38 Darius
-Lupita's in it for 10 minutes. I don't, like, she's the biggest star left.
-00:26:41 Jordan
-That was a waste of her.
-00:26:45 Darius
-And the movie just had no lead. That was the problem. But it just, you'd rather write a superhero movie without the superhero.
-00:26:52 Jordan
-With no superhero for the first two hours. It just didn't work. Yeah.
-00:26:58 Darius
-It was, you know, extraordinary circumstances, but I, the point of the prompt is what are things people, what are things people are pretending to like? We are 100% pretending to like that movie.
-00:27:09 Jordan
-Well, so, and it's like, it's funny you say that. I feel like that movie was, it's almost like as if you took The Lion King. And instead of focusing the movie on Simba, it was what happened to Pride Rock after Scar took over and Mufasa died. And but there's like no characters in that. Like, you know what I mean? Like, or like what happened when after Nala left to go find Simba. And it's like, okay, well, the mom's just there chilling, being abused by Scar. Everybody's surrendered. There's not much of a story there. You know what I'm saying?
-00:27:39 Darius
-I'm more interested in what's happening off screen and you're not showing me that. And I just, that was, I felt like I was taking crazy pills at the time because people were like. They did it though. Oh my God, it was so amazing.
-00:27:56 Jordan
-No, the scenery was beautiful. The cinematography was great. Obviously the water stuff was super awesome. Also, we spent the whole movie getting our ***** whipped by the blue people.
-00:28:05 Darius
-Yeah.
-00:28:06 Jordan
-So there was that too.
-00:28:08 Darius
-I saw it in IMAX and it was a beautifully shot movie.
-00:28:11 Jordan
-Yeah, absolutely. Stunning movie, great soundtrack.
-00:28:15 Darius
-We give him that. Neymar was a great villain.
-00:28:18 Jordan
-He was cold. He was awesome.
-00:28:20 Darius
-They just didn't do anything with him. And I don't think they have since, have they? I stopped watching after that one.
-00:28:26 Jordan
-Well, I'm pretty sure he's gonna be in Doomsday and probably Secret Wars. So we'll see what they do with that. Also, remember he caught, there was like some accusation against him. So I don't know if that's what caused him to not be in anything for a minute. I can't keep up.
-00:28:40 Darius
-What else you got for this one?
-00:28:44 Jordan
-I think that's all I had to be honest with you. I mean, you got two more if you, if you got those.
-00:28:48 Darius
-No, I mean, I've said it before. I'll hear sushi is something that.
-00:28:51 Jordan
-That's so crazy. I knew you were going to say that. I don't. You like rice, right?
-00:28:56 Darius
-Okay, but I like bland rice, under salted rice with a piece of fish on top that's raw. That only tastes like something. It's just a vehicle for soy sauce. And that's that yellow flap thing that just kind of tastes like I just don't. I don't understand it. It's.
-00:29:20 Jordan
-I love sushi.
-00:29:21 Darius
-You know, we have invented fire now. We like meat just tastes better when it's hot and it's like brought to have to be nuked, but like, you know, brought to a decent temperature. You know, every time I eat sushi, I think to myself, this would taste a lot better hot and cooked. So I think it's like people don't want to sound like simpletons by saying that they just, they want their food cooked. Yeah. Cause I guess that reads low class, but I'll be the one to say it. I will stand before history and say, stop. This **** is trash.
-00:29:54 Jordan
-You know what? Okay, I got one. I feel like people, a lot of people pretend to know how to use chopsticks. I think a lot of people are lying about knowing how to use chopsticks. There's A TikTok to a bar. This guy was holding chopsticks. He was showing how he fakes used them. So he literally is holding chopsticks and he grabs the food with his fingers and puts it like this and he's holding the chopsticks like this and he acts exactly like he just scooped it up with the chopsticks.
-00:30:18 Darius
-Yeah, it's like. It's a stupid way to eat food. You have forks and spoons. Why would we do this? It's like even like some cultures eat with their hands and like that's fine. I love finger food and I have no problem with that. You know, you wash your hands, that's cool. But like there's nothing chopsticks do better than a fork and a spoon and a knife. Not a single thing. It's just the dumbest way to use them though.
-00:30:42 Jordan
-Yeah, it's fine. But it is a flex. It's definitely flex.
-00:30:44 Darius
-You only got to use a typewriter. Like it's just useless now. Do you want to know how to eat like it's the 1400s and we don't haven't invented anything since then? All right, sure. But we have invented plastics and what are true? Silver.
-00:31:02 Jordan
-Utensils, silverware.
-00:31:04 Darius
-No, what is it made out of? I was thinking the metal, but it's definitely not silver. But anyways, we've invented a better way to do this and we should use it.
-00:31:11 Jordan
-I'm trying to think, what else do I think people are pretending to like? Work. I think a lot of people pretend to like work. I don't mean like their particular job. I mean like the whole like grinding culture, like don't ever ******* sleep. Wake up at 5 A.m. And if you know that this whole thing where it's like you got 8 hours of sleep, 8 hours to work, you still got 8 hours to make the rest of your life phenomenal. A</t>
-  </si>
-  <si>
-    <t>&lt;section class="show-notes-highlights"&gt;
-  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
-  &lt;h3&gt;Topics Covered&lt;/h3&gt;
-  &lt;ul&gt;
-    &lt;li&gt;Favorite four-course meals, dessert rankings, and why apple crumble deserves more respect.&lt;/li&gt;
-    &lt;li&gt;Strange personal habits and rituals people rarely admit out loud.&lt;/li&gt;
-    &lt;li&gt;Comfort movies, driving with no destination, and pre-event visualization.&lt;/li&gt;
-    &lt;li&gt;Creating fictional sports storylines and Madden fan fiction.&lt;/li&gt;
-    &lt;li&gt;Things people pretend to like, including adversity, sushi, chopsticks, grind culture, and certain forms of artistic prestige.&lt;/li&gt;
-    &lt;li&gt;Whether people genuinely enjoy struggling or simply enjoy the story that comes afterward.&lt;/li&gt;
-    &lt;li&gt;The difference between ignorance and stupidity.&lt;/li&gt;
-    &lt;li&gt;Bad advice that sounds good but produces terrible outcomes.&lt;/li&gt;
-    &lt;li&gt;&amp;quot;Live life to the fullest&amp;quot; versus making smart long-term decisions.&lt;/li&gt;
-    &lt;li&gt;What is genuinely better today than it has ever been.&lt;/li&gt;
-    &lt;li&gt;Modern technology, access to information, food variety, and consumer convenience.&lt;/li&gt;
-  &lt;/ul&gt;
-  &lt;h3&gt;Best Questions&lt;/h3&gt;
-  &lt;ul&gt;
-    &lt;li&gt;What strange habit or ritual do you do that you rarely admit to other people?&lt;/li&gt;
-    &lt;li&gt;What is something people only pretend to like?&lt;/li&gt;
-    &lt;li&gt;Do people actually value adversity, or do they only value surviving it?&lt;/li&gt;
-    &lt;li&gt;What is the worst advice you&amp;#39;ve ever received?&lt;/li&gt;
-    &lt;li&gt;What common piece of wisdom sounds good but falls apart in practice?&lt;/li&gt;
-    &lt;li&gt;What is better today than it was for previous generations?&lt;/li&gt;
-  &lt;/ul&gt;
-  &lt;h3&gt;Best Observations&lt;/h3&gt;
-  &lt;ul&gt;
-    &lt;li&gt;Most people do not enjoy adversity itself; they enjoy the growth, lessons, or stories that come after it.&lt;/li&gt;
-    &lt;li&gt;Comfort routines often exist because they provide stability during stressful periods of life.&lt;/li&gt;
-    &lt;li&gt;Prestige and popularity can pressure people into claiming they enjoy things they actually don&amp;#39;t.&lt;/li&gt;
-    &lt;li&gt;Ignorance can be corrected with information, but poor judgment is much harder to fix.&lt;/li&gt;
-    &lt;li&gt;Bad decisions often compound in ways that are invisible until years later.&lt;/li&gt;
-    &lt;li&gt;Modern life has dramatically improved access to information, education, food, and technology for curious people.&lt;/li&gt;
-  &lt;/ul&gt;
-  &lt;h3&gt;Best Debate&lt;/h3&gt;
-  &lt;p&gt;&lt;strong&gt;Do People Pretend To Like Adversity?&lt;/strong&gt; Jordan argued that adversity is often romanticized and that many people claim to appreciate hardship only after surviving it. Darius agreed that struggle itself is unpleasant and pointed out that some storms never end, making the common &amp;quot;everything happens for a reason&amp;quot; narrative far less comforting than people pretend.&lt;/p&gt;
-  &lt;div class="major-themes"&gt;
-    &lt;h3&gt;Major Themes&lt;/h3&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Personal Habits&lt;/li&gt;
-      &lt;li&gt;Self-Awareness&lt;/li&gt;
-      &lt;li&gt;Comfort Routines&lt;/li&gt;
-      &lt;li&gt;Adversity&lt;/li&gt;
-      &lt;li&gt;Personal Growth&lt;/li&gt;
-      &lt;li&gt;Bad Advice&lt;/li&gt;
-      &lt;li&gt;Decision Making&lt;/li&gt;
-      &lt;li&gt;Modern Technology&lt;/li&gt;
-      &lt;li&gt;Education&lt;/li&gt;
-      &lt;li&gt;Information Access&lt;/li&gt;
-      &lt;li&gt;Food Culture&lt;/li&gt;
-      &lt;li&gt;Everyday Philosophy&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/div&gt;
-&lt;/section&gt;</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="mm\.dd\.yy"/>
-  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -9847,7 +9437,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9869,8 +9459,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9887,10 +9475,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10210,7 +9794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -10902,21 +10486,6 @@
         <v>265</v>
       </c>
       <c r="E41" s="5"/>
-    </row>
-    <row r="42" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>268</v>
-      </c>
-      <c r="B42" t="s">
-        <v>262</v>
-      </c>
-      <c r="C42" s="9">
-        <v>46297</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="E42" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E41" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}"/>
@@ -10930,7 +10499,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -11513,20 +11082,6 @@
         <v>263</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>268</v>
-      </c>
-      <c r="B42" t="s">
-        <v>262</v>
-      </c>
-      <c r="C42" s="10">
-        <v>46297</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:D40" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
     <filterColumn colId="3">

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14BE534-751D-4A0A-9846-FCA901F72710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9B428F-EA29-412D-ACCE-800A6EBEFDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="272">
   <si>
     <t>youtube_link</t>
   </si>
@@ -9352,11 +9352,425 @@
   <si>
     <t>https://www.youtube.com/watch?v=M4_pR6sS5zM&amp;t=1s</t>
   </si>
+  <si>
+    <t>What Are People Pretending to Like</t>
+  </si>
+  <si>
+    <t>09.02.26</t>
+  </si>
+  <si>
+    <t>Transcript
+00:00:00 Darius
+about to make the joke that you did the internet thing where you said unpopular opinion and then stated very common practices. It's like habits that I don't want to admit. I pray before a long drive. I decompress after bad days. It's hard for me to go to sleep when I'm anxious. But driving back and forth to Durham is genuinely weird.
+00:00:21 Jordan
+Yeah, I'll be like, **** this. Yeah, I just. I just jump up and down the road. U-turn after U-turn. I don't know what's weird about me.
+00:00:27 Darius
+After a hard day, I watch a comedy. That's. That's me.
+00:00:32 Jordan
+Well, I'm very like, specific.
+00:00:33 Darius
+Out trunk with Jordan and Darius. My name is Darius. That's these all up in the area on all socials.
+00:00:38 Jordan
+And I'm Jordan. That's Jordan to be writing on all socials.
+00:00:41 Darius
+This is our What's On Our Mind segment where we let you guys know what's on our mind, what we've seen on the internet, things that we want to talk about. Do a little engagement bait, starting it off. We got, I'm going to put the graphic up on the screen here. We're picking one per row. Just a way to let you guys get to know us. What you got for, we're good. Just going to number the rows one, two, three. Just pick, just pick one for each row. And then we'll just go and go from there. So what you got for the first row, A, B, C, D, or E?
+00:01:12 Jordan
+I'm going with the breakfast burrito for row C. I love, you know, breakfast food. Anytime I can get in sort of like an efficient way like that, you know, it's always nice. I love omelets, but I got to be in the mood for hash browns. Same thing with pancakes too. I'm kind of weird about that kind of stuff. And the red velvet fridge toast, that just feels like a Saturday thing. You know what I mean? I couldn't have that like on a weekday and work. I'd need like 4 hours of sleep after that, you know?
+00:01:38 Darius
+Yeah, I'm not big on red velvet anything.
+00:01:43 Jordan
+Really.
+00:01:44 Darius
+It's just not, doesn't really do it for me. Yeah, breakfast burrito as well. Like you said, it's efficient. It hits all the bases. I do love hash browns, so I would like hash browns in my breakfast burrito.
+00:01:57 Jordan
+I'm not mad at that.
+00:01:58 Darius
+Pancakes are really hit or miss. Really hit or miss.
+00:02:01 Jordan
+I got to I got to really be. I feel like there's a weekend thing because you just who has time to like Sydney pancakes during the week, you know?
+00:02:07 Darius
+They're just and then when you do get them, they're so infrequently done right. And so omelets, I love an omelet, but if I can just put it all wrapped into a burrito, that's fine. Grand slam, which that's doing too much.
+00:02:19 Jordan
+Yeah.
+00:02:20 Darius
+And I love French toast, but stuffed red velvet, strawberry cream, fruit, that's doing a lot.
+00:02:28 Jordan
+So I'm sure it'd be good. I just, if you ask me like a day-to-day type thing, you know, that's more like a festival, a festive thing, you know, like if I had like a Christmas Eve brunch or something like that, that's like, would be on theme, To.
+00:02:43 Darius
+Be fair, nothing in their row is day-to-day.
+00:02:46 Jordan
+Well, that's true. close enough. I mean, every fast food place has a real.
+00:02:51 Darius
+Heavy, real heavy day-to-day, but I'm going with some as well. All right, row two, we got a club, chicken tenders, turkey melt, grilled cheese, or brisket melt. Where are we going with this one?
+00:03:03 Jordan
+I'm going with the brisket melt. I love brisket and anytime I can get that with some cheese or on some bread or in a nachos or whatever, pizza, whatever, I'll take that any day.
+00:03:15 Darius
+Turkey melt for me, same deal. I love turkey, little turkey sandwich. And then you got onion rings on there. So Basically the same gist that it is basically a grilled cheese with turkey, just like a brisket is a grilled cheese with brisket. So chicken tenders, I mean, I'm ambivalent about those. And a club is basically a turkey melt. You can do those anywhere. And Zod brother had it hot.
+00:03:39 Jordan
+Same.
+00:03:40 Darius
+So we're going with row. So we got, you got breakfast burrito, brisket melt and breakfast burrito, turkey melt. Row 3.
+00:03:51 Jordan
+Smothered gravy, yeah. Chicken fried steak, I think is basically what it is.
+00:03:54 Darius
+Yeah, that's what it looks like. Steak, cheeseburger, turkey, or lasagna. That is a really random roll. What you got?
+00:04:01 Jordan
+Yeah, it's a really random roll.
+00:04:03 Darius
+There's no thing to put it at all.
+00:04:05 Jordan
+Yeah, it's just giving like Golden Corral. ****** lower air food. Or K&amp;W on Sundays. I'm going to go with the first one. I'd go with the chicken fried steak.
+00:04:18 Darius
+Okay.
+00:04:18 Jordan
+Like some other gravy. It looks like mashed potatoes. Is that corn? I can't quite tell. Yeah, it's corn. Yeah, I'm cool with that. I'll take that. A good Sunday dinner type vibes.
+00:04:28 Darius
+White gravy or brown gravy? I know that's white gravy on the screen, but like which one would you prefer?
+00:04:35 Jordan
+For chicken fried steak, I'm going white.
+00:04:37 Darius
+Okay.
+00:04:37 Jordan
+Chicken fried steak, I'm going white.
+00:04:39 Darius
+I hate white gravy. I love brown gravy.
+00:04:41 Jordan
+Really.
+00:04:41 Darius
+But just as much as I hate white gravy, I love brown gravy.
+00:04:44 Jordan
+I also love sausage gravy.
+00:04:46 Darius
+Yeah, I could put brown gravy on anything and white gravy just reminds me of snot.
+00:04:53 Jordan
+So you might want to get that checked out.
+00:04:55 Darius
+It's really gross. Row 3 is tough.
+00:04:59 Jordan
+Yeah, there's a lot of good options.
+00:05:02 Darius
+But if I'm going with the best version of all of these, it's a lasagna.
+00:05:07 Jordan
+Okay.
+00:05:09 Darius
+Yeah, just. The best lasagna to me is better than the best version of the other four. And so that's the tiebreaker.
+00:05:16 Jordan
+I'm not mad at that.
+00:05:16 Darius
+I don't want the lasagna. If you get it with like a good, I don't like ricotta cheese, but if you just got a really cheesy one with some ground beef and some ground sausage and some good pasta sheets, it's tough to get that one. And we're going to head over to dessert, man. Brownie sundae, cheesecake, apple crumble, pumpkin pie, or cookie dough pie. Sweet potato pie. We're going to go ahead and sub that in a little bit.
+00:05:41 Jordan
+Yeah, okay, yeah, I thought about that.
+00:05:43 Darius
+I was like, oh. We're going to do that exchange. We're going to put sweet potato down there. So brownie sundae, cheesecake, crumble, sweet potato, or cookie dough.
+00:05:51 Jordan
+Yeah, although I do, I do, I don't have no beef with pumpkin pie. I do like pumpkin pie as well. I'm not going to lie. I'm a fan of all the winter vegetables.
+00:05:58 Darius
+Keep it in block. If you could blind tasted people, they wouldn't know the difference.
+00:06:01 Jordan
+It's not much difference.
+00:06:04 Darius
+Yeah.
+00:06:04 Jordan
+Well, I worked at a grid store when I was 16. It's like I had my own money. So I would just like buy those. So I actually am really good at tasting the difference because I just, that was like my, to me that was like buying a car type **** you know? Fair enough. You know, when you first get your own little money, you know, as a kid. So yeah, I think I'm going to go with the apple crumble. with the ice cream and the caramel looks like drizzled on top. Anytime I can get some sort of apple and ice cream or sweets together, I'm cool with that. But the brownie sundae looks good too, but you can kind of get that anywhere.
+00:06:40 Darius
+So yeah. the brownie sundae at any restaurant is almost certainly like just frozen. Yeah. Apple crumble for me too. Anytime I can get like a like a brown sugar cinnamon crust. I'm in.
+00:06:55 Jordan
+Yeah.
+00:06:56 Darius
+And so whatever you put in that crust is almost immaterial. So yeah, like that. There's a man, a good warm apple crumble with that scoop of that vanilla bean ice cream on top. It's smoking the field. The rest of those?
+00:07:10 Jordan
+Yeah. And to be honest, I'm really more of a pie person than a cake person. I got to be in the mood for cake or has to have like a certain like I prefer the Like the icing as opposed to like the whipped frosting, personally. And if they had had, if you saw about the cheesecake with like a key lime pie, I probably would have taken that because I do love a key lime pie.
+00:07:29 Darius
+I love a cheesecake, but like that cheesecake, like direct that. Yeah, the New York.
+00:07:34 Jordan
+Yeah.
+00:07:36 Darius
+But like, yeah, man, I just apple crumble is like, that's probably the My favorite dessert of them all. If I could pick any dessert, I think that one would win.
+00:07:46 Jordan
+Like any dessert of like in the world.
+00:07:48 Darius
+I think so. Yeah, I think so. Interesting. Like the best version of an apple crumble where like the apples are like in season and tender and it's like cinnamon and all spice and the crust is fresh and like crispy and buttery. I mean, what's beating that?
+00:08:06 Jordan
+I mean, I love banana pudding. with the Chessman cook cookies instead of the vanilla wafers. They're a little softer. I can **** ** some flan or some creme brulee any day. I'm a fan of the custards. All right, fair enough. Yeah, one of my old work moms, Puerto Ricans, she'd make those for us like in the holidays and stuff like that. So yeah, I love the custards. What else other good desserts do I like? I'm trying to think. I like ice cream cakes. What else, what else, what else? I'm trying to think. Yeah, like apple turnovers, anything like that, yeah.
+00:08:46 Darius
+Ice cream cake is a good one. I eat ice cream cake only on my birthday every year. Just growing up, it was like a. a special occasion. You got ice cream cake on your birthday because those cakes were quite pricey. And I've long since been able to just buy the cake whenever I want, but it's like a special birthday thing.
+00:09:05 Jordan
+That's how your brain is like conditioned it to.
+00:09:07 Darius
+It would feel like cheating to just like have it tonight, despite the fact that like it's $20. Like, you know, like, you can.
+00:09:14 Jordan
+Earn another year of life. So why should you have? Yeah.
+00:09:16 Darius
+But like, it's just with the Dairy Queen joint with the Crunchies in the middle and the gelatin on top. Man, listen, it's a birthday tradition. So rounding it up, you had the breakfast burrito, the brisket melt, the fried chicken, chicken fried steak, whatever you want to call it, apple crumble. And I went with breakfast burrito, turkey melt, lasagna, apple crumble. We are more unites us than divides us. So Yeah, write to us. Let us know what you guys picked on the thing and we'll put it up on the screen and yeah.
+00:09:53 Jordan
+What's your ideal menu of this four course situation?
+00:09:56 Darius
+And next week, if we don't have anything to start off with, we'll come up with another one. Heading into our first topic, it's you, man, habits and rituals.
+00:10:08 Jordan
+Yeah, so I think I actually found this online. What's a strange habit or ritual that you have that you rarely admit out loud?
+00:10:18 Darius
+You start.
+00:10:20 Jordan
+All right. Okay, I got a few. Whenever I go like on a long drive or like a long trip, I would say like a quick prayer just for like safety, you know, safe travels, you know, all that. That's one for sure.
+00:10:33 Darius
+I don't admit like that's.
+00:10:35 Jordan
+I mean, not that I don't admit it. I guess I just, I don't like, I'm not like a big like church person, and it's more private thing. I don't really do it. I do it silently. I don't really do it like out loud or, you know, so I guess that's more so the, it's more personal thing, I guess. Yeah, let's see. If I have a really bad day, I have to consume some sort of comedy entertainment. I have to be like, I can't just end the day and not like, I'll have to watch like a comedy movie or like a sitcom episode or I'll YouTube like a favorite scene from a movie or something that makes me laugh, whatever, something like that. Like I have to like make sure I laugh or smile at some point if I have a bad day. Like it could be the worst day ever and I'm like, you know, I need to YouTube ******* the office bloopers or some **** like that, whatever. I just like, no matter how bad the day is, I refuse to let the entire day be bad.
+00:11:28 Darius
+Okay.
+00:11:29 Jordan
+All right.
+00:11:30 Darius
+What else you got?
+00:11:35 Jordan
+As you know, you hear me pretty well. I can be pretty high strung, especially mostly when I'm in an irritated state. So you said it on me. I'm just nodding here. So I like I literally cannot sleep when I'm when I'm mad, like when I'm like fuming. So I will just like stay up. I'll do whatever I do to like to get that energy out before I can like get some rest. Like I will It could be 3 in the morning. I'd be like, **** it. I gotta go to the gym. And I'll think about whatever I'm mad at, wherever I'm mad at and just into the weights or whatever. If I gotta take a walk and walk 5 miles, then that's what I have to do. If I gotta drive to Durham and back three times, just straight up and down 70, then that's just what the **** I gotta do.
+00:12:24 Darius
+We got some, okay. So I was about to make the joke that you did the internet thing where you said unpopular opinion and then stated very common practices. Okay. Habits that I don't want to admit. I pray before a long drive. I decompress after bad days. It's hard for me to go to sleep when I'm anxious. But driving back and forth to Durham is genuinely weird.
+00:12:47 Jordan
+Yeah, no, I'll be like, **** this. I'll just drive up and down the road, U-turn after U-turn. I want to know what's weird about me.
+00:12:53 Darius
+After a hard day, I watch a comedy. That's me.
+00:12:58 Jordan
+Well, I have very like specific things that I watch. Like I have like my comfort movies are probably like a little unusual or not maybe standard, whatever. The awkward moment is one of my comfort movies, like when I'm upset. Or like, what if we reviewed that one with Daniel Radcliffe? Yeah, that's one of my comfort movies. Prisoner of Azkaban. I'm trying to think. What else? What else? What else? Maybe like Prince of Persia?
+00:13:21 Darius
+That's a deep cut.
+00:13:23 Jordan
+No, Prisoner of Azkaban. It's the third Harry Potter.
+00:13:26 Darius
+Oh, there's a Prince of Persia gayness movie with Jake Gyllenhaal.
+00:13:31 Jordan
+Jake Gyllenhaal. Yeah.
+00:13:33 Darius
+Titled similarly, I think.
+00:13:34 Jordan
+Yeah, I've seen that. I've seen that. Yeah. something. Yeah. I mean, I guess they're very, it's the way I cope. That's probably a little more niche than the coping itself.
+00:13:45 Darius
+All right. I'll get weird for us.
+00:13:48 Jordan
+Okay.
+00:13:49 Darius
+I no longer write it, but I usually write like Madden fan fiction. So like last week I said that we do franchise modes, but I don't do actual like, it's like in my head, they're characters like, and so It's not just like I will keep a guy on the team past his the time when I should come because of in my head what he means to the city in the video game and I used to like.
+00:14:19 Jordan
+Imaginary community service and stuff.
+00:14:21 Darius
+Correct. And so I would write, I would flesh these characters out and write them down. And I no longer write them down, but in my head, there was last year I was Vikings in the franchise mode and no, it happened twice. I was the Vikings in the franchise mode and TJ Hawkinson was like the tight end. He's a real tight end for the Vikings. And it was like year 10 of it. And we had won a bunch of Super Bowls together and it was like, it was time to let him go. And in our last Super Bowl, he scored a touchdown and I paused the game and like gave him his moment with the crowd. But that's like fake. Like that's not in the game. That was just me in my living room giving him his moment.
+00:14:58 Jordan
+Did you stand up and applaud?
+00:15:00 Darius
+Yes. That is something very weird that I do that I don't like anything out loud.
+00:15:09 Jordan
+Okay. When I.
+00:15:10 Darius
+Jog, depending on the song, I pretend I am having a concert and I'm on stage performing that song when I jog. And so it's very like, if you ever watch Save by the Bell, like the Zack attack type thing, when you like imagine, it helps me push through and like keep pace. Okay. Like I'm performing a song on stage. And so, Yeah, I write, used to write Madden fan fiction. Now it's mostly in my head. And yeah, I hold basically in imaginary concerts when I jog. So.
+00:15:44 Jordan
+Okay. I have a, okay, I got a couple more then. So I'm obviously very outgoing, but I actually do have an extremely introverted side that no one really believes or notices, I guess. I guess I camouflage it well. So before like big social events, especially if it's like booked in advance, I've like mentally prepared and done visualization exercises pretty much up until the moment I walk it through the door for a set event. You know, like I've thought about what I'm gonna wear, who I'm gonna see when I'm in the room, what we're gonna talk about or what I want to talk about with them, what I'm gonna bring to the function, you know, whatever. If I have songs I like, which ones am I gonna request on the aux or the Bluetooth, whatever, **** like that. I don't know if that's weird or not. A little different.
+00:16:32 Darius
+I have stop bits that like.
+00:16:35 Jordan
+You go to stores.
+00:16:36 Darius
+If I don't force them into the conversation, but if it gets there, I have it's almost just like a comedian has routine jokes that just when the sets dry, he can just lean on them. I have like four or five of those.
+00:16:49 Jordan
+Same.
+00:16:50 Darius
+If I just have to, you know, drive the social conversation for a little bit, which I don't particularly enjoy doing. But So mapping out the social interaction, that's we got one that actually counts.
+00:17:04 Jordan
+So I love making playlists. So I have a, when I perform poetry, I have a playlist called Performing, which a lot of songs just like get me like hype for performing, just get me in that mode to like be on, you know, and be, you know, at full capacity. A lot of them are about like just, you know, superstardom and pursuing dreams and, you know, being at the pinnacle, things of that nature. And so I play that on a loop while I'm getting dressed, while I'm driving to the venue, whatever case may be. I also will like visualize the crowd and visualize the pauses and the possible rewinds when I'm doing my lines and stuff like that. I practice like my hand gestures almost to a T for certain lines and stuff. I don't know if that's strange or not. I don't picture all these naked. I put everyone in their clothes.
+00:17:58 Darius
+I've never understood why that's supposed to work.
+00:18:01 Jordan
+Yeah, I don't get that either. I'd rather just not picture them. Yeah, enjoying the performance.
+00:18:10 Darius
+The few times I've had to publicly. Well, I'm not bad at publicly speaking when it's like as long as there's not like a stage. But the whole being elevated, just it's nerve-wracking.
+00:18:25 Jordan
+That is true.
+00:18:26 Darius
+Yeah.
+00:18:27 Jordan
+Especially with the lights, you can't see.
+00:18:30 Darius
+Yeah, man, it's like when I was, so I have siblings, but the gap is so large, it almost resets. Like my brother is 11 years older than me and my sister's 8 years older than me. So it's like, funks, like I'm not an only child, but like my upbringing was very solitary because like, I'm 10, they're 18 and 21. They not trying to kick it with me. like they out doing 18 and 21 year old ****. So I had my action figures and I had like, I would build out like wrestling storylines with the action figures. And I say all this to say, I have, you develop an extraordinary imagination when you have to entertain yourself before Netflix and smartphones. And so like I would, you know, take each each action figure had his own backstory and his own character, and then you would build out all of that. And yeah, I guess it's it's travel with me into Madden. So yeah, and other video games, but mostly the ones that sports games are easier because like, yeah, you stay with these characters year to year and, you know, watch them succeed and fail. So.
+00:19:40 Jordan
+Okay. I think I thought of another one. Whenever, especially over text, if I had a conversation with someone, I didn't like how that conversation went or I just didn't like the energy or the vibe and I don't want to harp on it, I will delete the text thread or delete those texts specifically. And if I'm really, really mad, then I'll just delete the text thread and delete their number altogether. And if they want to reconcile or if it's meant to be, then they will hit me back up and then I'll re-enter their name in my phone and resume the relationship. Dude, okay.
+00:20:17 Darius
+That's over the top. What are y'all falling out about? We gotta work on your conflict resolution skills.
+00:20:28 Jordan
+Yeah, I think that's my way of just like not cussing people out. It's just like, let me just act like the conversation didn't happen. And then if you can come back or I can get myself in a better headspace and you hit me up or something like that, then we can converse.
+00:20:40 Darius
+Makes sense?
+00:20:41 Jordan
+Nuke it.
+00:20:42 Darius
+If you can't see it, never happened.
+00:20:44 Jordan
+Correct.
+00:20:46 Darius
+All right. So we're heading into the next topic. So I got on here. What are some things you believe people are just pretending to like? Yeah, I have three food and artist and a movie, but you don't have to follow that structure at all. So you can let me have it, man. What you got?
+00:21:09 Jordan
+So the first one I have is adversity. I mean, it's a part of life and you do need to learn that skill. But it feels like sometimes people just glorify that **** all the time. And it's like, you know what? I'm not going to tell a homeless person that this is something good for them, that they'll come off stronger at the end of this. You know what I mean? Like, you know, that person whose life got fell apart because of a divorce, maybe their life won't get better after that. You know what I mean? I mean, hopefully it does. But you know what I'm saying? Like that whole thing of like trivializing and like toxic positivity, so to speak. It's like, some people die with broken hearts still. Meaning the storm did not end.
+00:21:48 Darius
+Toxic positivity is something I have a particular distaste for because like.
+00:21:54 Jordan
+Should be bad sometimes.
+00:21:55 Darius
+Should be bad. And like, it might not work out. Like that happens all the time. Like we've said this before, in particular about like Hollywood. It's like, there's a strong survivor bias. Like you only hear about John Ham, who got his first role when he was 40 and was waiting tables until then. But I promise you, there's 1000 people who went out there and it just didn't work. Like they just, yeah. It's like, they just don't get a TV show. They don't go, they don't win an Emmy to tell you it didn't work. Like they just never, ever hear their story. And it's like you only hear the rare survival stories. There's a strong survival bias when it comes to those Hollywood brags to riches stories. I know someone who moved to LA and he's fine, but it never, like he went there to act and it's been 10 years and I ain't seen him in no movies. He just lives there now. And that's what happens more often than not is that you just build a life out there and then just slowly give it up and just start working. And like you don't, move back home 'cause L.A. is still fun, but Right?
+00:22:57 Jordan
+But I say it's still a cool city.
+00:22:59 Darius
+It's still it's still no, but you still did something like it's still an accomplishment to move out there and build a new life, but yeah, absolutely. I moved out there to be an actor and I ain't seen no credits. You don't get a sack card? No, but that's the I mean. I don't want to be cheesy and say that's not a failure because the goal wasn't achieved. Yeah, because it's really not. He just moved in for work and the work just turned out to be a little differently than he expected. So yeah, I'm not mad at that. So artist MF Doom. We RIP.
+00:23:36 Jordan
+Rest in peace.
+00:23:37 Darius
+But I was not a hip. And then when he passed, People were clicking, sending, posting songs and I'm like, is there something wrong with my internet? This can't be the songs y'all are talking about.
+00:23:47 Jordan
+I'll be honest with you. I've never, I don't think I've ever heard one of these songs. I'm not gonna lie.
+00:23:51 Darius
+They're so bad. He's not good. I don't, get, I swear I don't get it. It's like, people like are hyped about it. And I'm just like, I don't understand it. You've heard the one line though. You've heard the one song that everyone talks about with the podcast, Chatty Patties. Rap snitches, tell them all their business, take them to court to be their own star witness. That's the MF Doom line when people quote that, that's MF Doom. So he was quite prescient with that line because these dudes be telling on themselves crazy. Movie, going to be a little controversial here because I understand why people pretend. Wakanda Forever was a mid pack. We can be honest. You do hate that movie. You do hate that movie. R.I.P. I get what I get. Yeah. The challenge at hand?
+00:24:41 Jordan
+The gist?
+00:24:41 Darius
+Yeah. But we are certainly not being honest. Like, yeah, you can't. I think the fever has tempered a little bit and you get people like if they if they make sure no one's listening, be honest about it. Yeah. I remember leaving that theater like that wasn't good. I was like, dude, I rip, but I didn't actually know him. And so, like, your job was to entertain me with a good movie, not throw a funeral for the cast. And you did not like, why? Why are we using the first hour of the movie to throw a funeral?
+00:25:21 Jordan
+Right.
+00:25:22 Darius
+On a multibillion dollar MCU project like you can we they recast it. It's time to move on. I get that. But like, As a consumer expecting a good movie, they did not deliver on that. And while I understand that it was under trying circumstances, I was not, I did not personally know Chadwick.
+00:25:40 Jordan
+And COVID too.
+00:25:41 Darius
+And COVID, but I did not personally know Chadwick, so I was not interested in attending his funeral and they made me. That's nuts.
+00:25:52 Jordan
+But I mean, it was a tough spot. it really was. I mean, they had no way to, they didn't know, they had no way to prepare. I mean, who knows how much time Coogler had to rewrite that whole script, Yeah, my big issue with that particular movie is I felt like the queen died for no reason. Like she just, they killed her and then there was, it was like, okay, you killed my mom, like I'm gonna try to kill you. Then it's like, oh, we need y'all. So let's piece it up.
+00:26:24 Darius
+The core tension is never resolved. It's like, they're in a blood feud and they just decide not to be and they only never explain why. And then it's like they introduce the little girl with the backpack and do nothing with her.
+00:26:36 Jordan
+Riri, yeah.
+00:26:38 Darius
+Lupita's in it for 10 minutes. I don't, like, she's the biggest star left.
+00:26:41 Jordan
+That was a waste of her.
+00:26:45 Darius
+And the movie just had no lead. That was the problem. But it just, you'd rather write a superhero movie without the superhero.
+00:26:52 Jordan
+With no superhero for the first two hours. It just didn't work. Yeah.
+00:26:58 Darius
+It was, you know, extraordinary circumstances, but I, the point of the prompt is what are things people, what are things people are pretending to like? We are 100% pretending to like that movie.
+00:27:09 Jordan
+Well, so, and it's like, it's funny you say that. I feel like that movie was, it's almost like as if you took The Lion King. And instead of focusing the movie on Simba, it was what happened to Pride Rock after Scar took over and Mufasa died. And but there's like no characters in that. Like, you know what I mean? Like, or like what happened when after Nala left to go find Simba. And it's like, okay, well, the mom's just there chilling, being abused by Scar. Everybody's surrendered. There's not much of a story there. You know what I'm saying?
+00:27:39 Darius
+I'm more interested in what's happening off screen and you're not showing me that. And I just, that was, I felt like I was taking crazy pills at the time because people were like. They did it though. Oh my God, it was so amazing.
+00:27:56 Jordan
+No, the scenery was beautiful. The cinematography was great. Obviously the water stuff was super awesome. Also, we spent the whole movie getting our ***** whipped by the blue people.
+00:28:05 Darius
+Yeah.
+00:28:06 Jordan
+So there was that too.
+00:28:08 Darius
+I saw it in IMAX and it was a beautifully shot movie.
+00:28:11 Jordan
+Yeah, absolutely. Stunning movie, great soundtrack.
+00:28:15 Darius
+We give him that. Neymar was a great villain.
+00:28:18 Jordan
+He was cold. He was awesome.
+00:28:20 Darius
+They just didn't do anything with him. And I don't think they have since, have they? I stopped watching after that one.
+00:28:26 Jordan
+Well, I'm pretty sure he's gonna be in Doomsday and probably Secret Wars. So we'll see what they do with that. Also, remember he caught, there was like some accusation against him. So I don't know if that's what caused him to not be in anything for a minute. I can't keep up.
+00:28:40 Darius
+What else you got for this one?
+00:28:44 Jordan
+I think that's all I had to be honest with you. I mean, you got two more if you, if you got those.
+00:28:48 Darius
+No, I mean, I've said it before. I'll hear sushi is something that.
+00:28:51 Jordan
+That's so crazy. I knew you were going to say that. I don't. You like rice, right?
+00:28:56 Darius
+Okay, but I like bland rice, under salted rice with a piece of fish on top that's raw. That only tastes like something. It's just a vehicle for soy sauce. And that's that yellow flap thing that just kind of tastes like I just don't. I don't understand it. It's.
+00:29:20 Jordan
+I love sushi.
+00:29:21 Darius
+You know, we have invented fire now. We like meat just tastes better when it's hot and it's like brought to have to be nuked, but like, you know, brought to a decent temperature. You know, every time I eat sushi, I think to myself, this would taste a lot better hot and cooked. So I think it's like people don't want to sound like simpletons by saying that they just, they want their food cooked. Yeah. Cause I guess that reads low class, but I'll be the one to say it. I will stand before history and say, stop. This **** is trash.
+00:29:54 Jordan
+You know what? Okay, I got one. I feel like people, a lot of people pretend to know how to use chopsticks. I think a lot of people are lying about knowing how to use chopsticks. There's A TikTok to a bar. This guy was holding chopsticks. He was showing how he fakes used them. So he literally is holding chopsticks and he grabs the food with his fingers and puts it like this and he's holding the chopsticks like this and he acts exactly like he just scooped it up with the chopsticks.
+00:30:18 Darius
+Yeah, it's like. It's a stupid way to eat food. You have forks and spoons. Why would we do this? It's like even like some cultures eat with their hands and like that's fine. I love finger food and I have no problem with that. You know, you wash your hands, that's cool. But like there's nothing chopsticks do better than a fork and a spoon and a knife. Not a single thing. It's just the dumbest way to use them though.
+00:30:42 Jordan
+Yeah, it's fine. But it is a flex. It's definitely flex.
+00:30:44 Darius
+You only got to use a typewriter. Like it's just useless now. Do you want to know how to eat like it's the 1400s and we don't haven't invented anything since then? All right, sure. But we have invented plastics and what are true? Silver.
+00:31:02 Jordan
+Utensils, silverware.
+00:31:04 Darius
+No, what is it made out of? I was thinking the metal, but it's definitely not silver. But anyways, we've invented a better way to do this and we should use it.
+00:31:11 Jordan
+I'm trying to think, what else do I think people are pretending to like? Work. I think a lot of people pretend to like work. I don't mean like their particular job. I mean like the whole like grinding culture, like don't ever ******* sleep. Wake up at 5 A.m. And if you know that this whole thing where it's like you got 8 hours of sleep, 8 hours to work, you still got 8 hours to make the rest of your life phenomenal. A</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Topics Covered&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Favorite four-course meals, dessert rankings, and why apple crumble deserves more respect.&lt;/li&gt;
+    &lt;li&gt;Strange personal habits and rituals people rarely admit out loud.&lt;/li&gt;
+    &lt;li&gt;Comfort movies, driving with no destination, and pre-event visualization.&lt;/li&gt;
+    &lt;li&gt;Creating fictional sports storylines and Madden fan fiction.&lt;/li&gt;
+    &lt;li&gt;Things people pretend to like, including adversity, sushi, chopsticks, grind culture, and certain forms of artistic prestige.&lt;/li&gt;
+    &lt;li&gt;Whether people genuinely enjoy struggling or simply enjoy the story that comes afterward.&lt;/li&gt;
+    &lt;li&gt;The difference between ignorance and stupidity.&lt;/li&gt;
+    &lt;li&gt;Bad advice that sounds good but produces terrible outcomes.&lt;/li&gt;
+    &lt;li&gt;&amp;quot;Live life to the fullest&amp;quot; versus making smart long-term decisions.&lt;/li&gt;
+    &lt;li&gt;What is genuinely better today than it has ever been.&lt;/li&gt;
+    &lt;li&gt;Modern technology, access to information, food variety, and consumer convenience.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Questions&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;What strange habit or ritual do you do that you rarely admit to other people?&lt;/li&gt;
+    &lt;li&gt;What is something people only pretend to like?&lt;/li&gt;
+    &lt;li&gt;Do people actually value adversity, or do they only value surviving it?&lt;/li&gt;
+    &lt;li&gt;What is the worst advice you&amp;#39;ve ever received?&lt;/li&gt;
+    &lt;li&gt;What common piece of wisdom sounds good but falls apart in practice?&lt;/li&gt;
+    &lt;li&gt;What is better today than it was for previous generations?&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Observations&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Most people do not enjoy adversity itself; they enjoy the growth, lessons, or stories that come after it.&lt;/li&gt;
+    &lt;li&gt;Comfort routines often exist because they provide stability during stressful periods of life.&lt;/li&gt;
+    &lt;li&gt;Prestige and popularity can pressure people into claiming they enjoy things they actually don&amp;#39;t.&lt;/li&gt;
+    &lt;li&gt;Ignorance can be corrected with information, but poor judgment is much harder to fix.&lt;/li&gt;
+    &lt;li&gt;Bad decisions often compound in ways that are invisible until years later.&lt;/li&gt;
+    &lt;li&gt;Modern life has dramatically improved access to information, education, food, and technology for curious people.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Debate&lt;/h3&gt;
+  &lt;p&gt;Do People Pretend To Like Adversity?
+Jordan argued that adversity is often romanticized and that many people claim to appreciate hardship only after surviving it. Darius agreed that struggle itself is unpleasant and pointed out that some storms never end, making the common &amp;quot;everything happens for a reason&amp;quot; narrative far less comforting than people pretend.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Personal Habits&lt;/li&gt;
+      &lt;li&gt;Self-Awareness&lt;/li&gt;
+      &lt;li&gt;Comfort Routines&lt;/li&gt;
+      &lt;li&gt;Adversity&lt;/li&gt;
+      &lt;li&gt;Personal Growth&lt;/li&gt;
+      &lt;li&gt;Bad Advice&lt;/li&gt;
+      &lt;li&gt;Decision Making&lt;/li&gt;
+      &lt;li&gt;Modern Technology&lt;/li&gt;
+      &lt;li&gt;Education&lt;/li&gt;
+      &lt;li&gt;Information Access&lt;/li&gt;
+      &lt;li&gt;Food Culture&lt;/li&gt;
+      &lt;li&gt;Everyday Philosophy&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="mm\.dd\.yy"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -9437,7 +9851,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9459,6 +9873,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9475,6 +9891,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9794,7 +10214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -10486,6 +10906,20 @@
         <v>265</v>
       </c>
       <c r="E41" s="5"/>
+    </row>
+    <row r="42" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>268</v>
+      </c>
+      <c r="B42" t="s">
+        <v>269</v>
+      </c>
+      <c r="C42" s="10">
+        <v>46297</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>271</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E41" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}"/>
@@ -10499,7 +10933,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -11082,6 +11516,20 @@
         <v>263</v>
       </c>
     </row>
+    <row r="42" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>268</v>
+      </c>
+      <c r="B42" t="s">
+        <v>262</v>
+      </c>
+      <c r="C42" s="9">
+        <v>46297</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D40" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
     <filterColumn colId="3">

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9B428F-EA29-412D-ACCE-800A6EBEFDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763561B1-4C85-4085-BB7E-766704040EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Transcripts!$A$1:$D$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WOOM Archive'!$A$1:$E$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WOOM Archive'!$A$1:$E$42</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="273">
   <si>
     <t>youtube_link</t>
   </si>
@@ -9762,6 +9762,9 @@
   &lt;/div&gt;
 &lt;/section&gt;</t>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=OQ5cZBxo6xY&amp;t=338s</t>
+  </si>
 </sst>
 </file>
 
@@ -9851,7 +9854,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9875,6 +9878,7 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9891,10 +9895,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10890,7 +10890,9 @@
       <c r="D40" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="E40" s="5"/>
+      <c r="E40" s="11" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="41" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
@@ -10922,7 +10924,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E41" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}"/>
+  <autoFilter ref="A1:E42" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}"/>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" xr:uid="{B375DB27-E1B7-490E-9D8C-9444D796161B}"/>
   </hyperlinks>

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763561B1-4C85-4085-BB7E-766704040EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3E97AE-7DAE-4ECC-A0F6-CF91E6CC3BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="278">
   <si>
     <t>youtube_link</t>
   </si>
@@ -9356,9 +9356,6 @@
     <t>What Are People Pretending to Like</t>
   </si>
   <si>
-    <t>09.02.26</t>
-  </si>
-  <si>
     <t>Transcript
 00:00:00 Darius
 about to make the joke that you did the internet thing where you said unpopular opinion and then stated very common practices. It's like habits that I don't want to admit. I pray before a long drive. I decompress after bad days. It's hard for me to go to sleep when I'm anxious. But driving back and forth to Durham is genuinely weird.
@@ -9765,6 +9762,334 @@
   <si>
     <t>https://www.youtube.com/watch?v=OQ5cZBxo6xY&amp;t=338s</t>
   </si>
+  <si>
+    <t>Change, Ownership, and the Cost of Going Out</t>
+  </si>
+  <si>
+    <t>09.22.26</t>
+  </si>
+  <si>
+    <t>09.19.26</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Topics Covered&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Mahershala Ali’s stalled Blade project and whether talented actors should choose franchise money over artistic freedom.&lt;/li&gt;
+    &lt;li&gt;The “one for me, one for you” career strategy and whether Marvel commitments swallow actors’ careers.&lt;/li&gt;
+    &lt;li&gt;What Jordan and Darius are watching, including Once Upon a Time, Snowfall, sports, and Tyler Perry’s latest sequel.&lt;/li&gt;
+    &lt;li&gt;Why viewers should feel free to quit a television show when it stops being rewarding.&lt;/li&gt;
+    &lt;li&gt;The difference between change and evolution, and why cultural correction often becomes overcorrection.&lt;/li&gt;
+    &lt;li&gt;Job-interview etiquette, workplace vibes, social norms, and why bringing iced coffee can signal poor judgment.&lt;/li&gt;
+    &lt;li&gt;Chesterton’s fence and the danger of removing traditions or friction before understanding their purpose.&lt;/li&gt;
+    &lt;li&gt;Sports gambling, fantasy football, and how betting can replace love of the game with anxiety over outcomes.&lt;/li&gt;
+    &lt;li&gt;The difference between aging naturally and performing premature “washed” culture.&lt;/li&gt;
+    &lt;li&gt;The return of physical media, ownership, sound quality, nostalgia, and decision fatigue.&lt;/li&gt;
+    &lt;li&gt;Why streaming weakened album listening, deep cuts, and the experience of letting art grow on an audience.&lt;/li&gt;
+    &lt;li&gt;Why relationship discourse dominates Black online culture and whether televised dating panels reflect real life.&lt;/li&gt;
+    &lt;li&gt;Remote work, downtown Raleigh, third places, expensive nightlife, and the social cost of suburban isolation.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Questions&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Does long-term franchise work limit a talented actor’s career more than it helps?&lt;/li&gt;
+    &lt;li&gt;What is the difference between changing and evolving?&lt;/li&gt;
+    &lt;li&gt;Which social norms were more important than people realized?&lt;/li&gt;
+    &lt;li&gt;Has legal mobile gambling damaged the experience of watching sports?&lt;/li&gt;
+    &lt;li&gt;Why are younger adults so eager to identify as washed?&lt;/li&gt;
+    &lt;li&gt;Why are people paying a premium for physical media again?&lt;/li&gt;
+    &lt;li&gt;What do you prefer to own physically, and what works better digitally?&lt;/li&gt;
+    &lt;li&gt;Why does relationship discourse dominate Black online culture?&lt;/li&gt;
+    &lt;li&gt;If downtown spending has recovered, why does downtown still feel dead?&lt;/li&gt;
+    &lt;li&gt;Have third places disappeared, or have people simply been priced out of them?&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Observations&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;All evolution requires change, but not every change represents meaningful evolution.&lt;/li&gt;
+    &lt;li&gt;Society often solves the last problem by overcorrecting into a new one.&lt;/li&gt;
+    &lt;li&gt;Many social norms functioned as healthy friction, even when their purpose was not obvious.&lt;/li&gt;
+    &lt;li&gt;Making gambling instantly available changed sports fandom from cheering for teams to sweating individual bets.&lt;/li&gt;
+    &lt;li&gt;Physical media turns entertainment back into an event and encourages people to finish the work they selected.&lt;/li&gt;
+    &lt;li&gt;Streaming reduced the amount consumers spend on music, so artists increasingly rely on touring for income.&lt;/li&gt;
+    &lt;li&gt;Online dating content often rewards people who perform for the camera instead of representing ordinary dating behavior.&lt;/li&gt;
+    &lt;li&gt;Remote work can affect nightlife indirectly by breaking the daily habit of spending time downtown.&lt;/li&gt;
+    &lt;li&gt;Suburban gathering spots preserve social activity but reduce spontaneity, bar hopping, and contact with people outside an existing circle.&lt;/li&gt;
+    &lt;li&gt;Third places become less useful as community spaces when bowling, movies, arcades, and nightlife become premium experiences.&lt;/li&gt;
+    &lt;li&gt;Major Themes&lt;/li&gt;
+    &lt;li&gt;Artistic Integrity&lt;/li&gt;
+    &lt;li&gt;Career Trade-Offs&lt;/li&gt;
+    &lt;li&gt;Change vs. Evolution&lt;/li&gt;
+    &lt;li&gt;Social Norms&lt;/li&gt;
+    &lt;li&gt;Cultural Overcorrection&lt;/li&gt;
+    &lt;li&gt;Healthy Friction&lt;/li&gt;
+    &lt;li&gt;Sports Gambling&lt;/li&gt;
+    &lt;li&gt;Aging and Identity&lt;/li&gt;
+    &lt;li&gt;Physical Media&lt;/li&gt;
+    &lt;li&gt;Ownership&lt;/li&gt;
+    &lt;li&gt;Streaming Economics&lt;/li&gt;
+    &lt;li&gt;Music Culture&lt;/li&gt;
+    &lt;li&gt;Relationship Discourse&lt;/li&gt;
+    &lt;li&gt;Remote Work&lt;/li&gt;
+    &lt;li&gt;Downtown Life&lt;/li&gt;
+    &lt;li&gt;Third Places&lt;/li&gt;
+    &lt;li&gt;Community&lt;/li&gt;
+    &lt;li&gt;Cost of Living&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Debate&lt;/h3&gt;
+  &lt;p&gt;Should society remove old norms and friction in the name of freedom and convenience? Jordan argued that change can become an overcorrection when people react too strongly to a prior problem. Darius used Chesterton’s fence, mobile gambling, workplace etiquette, remote work, and downtown decline to argue that some old barriers quietly supported healthier behavior and stronger communities. Both agreed that progress requires understanding what a norm was doing before eliminating it.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transcript
+00:00:00 Darius
+It's like the whole like wash the thing. Like it was in the beginning, antisocial. Like I like to stay in the house or, I, I'm getting older, I'm washed. And then it just like, suddenly I just saw someone one day was like, after 30 plus, don't ask me to come out after 7:00. And I was like, I know, bro, come on, man.
+00:00:19 Jordan
+What the hell are you doing on the weekends?
+00:00:20 Darius
+Come on, dude. I ain't that watch. I'm not ready for the nursing home. Like I'm not.
+00:00:25 Jordan
+There's a, yeah, there's a very, very thick line between being an old in the club and being prematurely watched or whatever you want to call yourself.
+00:00:35 Darius
+Yeah, like, am I out till 3:00 in the clubs anymore? No, but I'm not ready for bingo night either. Like, it's like, welcome to Out the Trunk with Jordan and Darius. My name is Darius. That's these all up in your area on all socials.
+00:00:46 Jordan
+And I'm Jordan. That's Jordan B. writing on all socials.
+00:00:49 Darius
+This is our what's on our mind segment where we where we where we like to let you guys know what's on our mind, what we've seen on the Internet, pop culture, different things like that. It's kind of like an open forum to discuss what we found interesting. And I want to start with what's going to be an extremely unpopular opinion position. All right. Just about I might be 1% of people on Earth who hold this position. I am happy that Blade blew up in Mashallah Ali's face because in a just world, an actor as talented as him choosing to do Marvel slop should be punished. And I'm so happy that the good guys won this time. Sometimes the bad guys lose. I'm glad it ruined his, I'm glad it derailed his career and he should be punished for that terrible decision.
+00:01:35 Jordan
+That's crazy.
+00:01:37 Darius
+It makes me so, in interviews and he's like, they ****** it up. And I was like, oh my, I'm so, I hope the next person sees this and reconsiders. I get it. just, I just, I feel it just fills me with such happiness to see the bad guys lose sometimes.
+00:01:53 Jordan
+And when you say the bad guys, you mean like Marvel or actors?
+00:01:59 Darius
+Everyone, well, Marvel's going to do what they want to do. But talented actors and actresses who choose to do that slop for money, they should be punished constantly. I love it. I hope he never gets another money.
+00:02:15 Jordan
+Yeah, no, I definitely disagree for sure. I like seeing black people.
+00:02:19 Darius
+I said it being popular. It's not just a black thing like that lady who did obsession.
+00:02:24 Jordan
+I hope it blows up in her face that she chose Marvel stuff. I think it was somebody said that actually was not true. She didn't actually turn down a role in Heat, number one. Number 2, when has Michael Mann been known for writing great women characters? Like, can we, like, let's stop. Number one, point #2. Point #3, after she shot Obsession, she didn't work for like a year and a half. These bills got to get paid, bro. And she got severely underpaid for Obsession. So like, get in the bag, I'm not mad at people doing that. Again, that's where the phrase, one for me, one for you comes from. Like, I'm gonna do one blockbuster, get the bag, get my money right. And then I can Robert Pattinson the rest of my career. You feel me? So I think there's a place for both. I get what you're saying. Cause like, you know, if we lost him for a decade doing a vampire, that would not have been great for art. But I mean, he's still doing great movies. So it's not a real.
+00:03:17 Darius
+One for me, one for you doesn't works in theory, never in practice. Where's Winston Duke? Where's Lupita? Marvel just swallows up careers, man. It's not really doesn't really work that way.
+00:03:28 Jordan
+I mean, do you know for a fact they have like a non-compete clause or that they can't they're not able to do other things?
+00:03:34 Darius
+No, but anecdotally, I know when people choose to enter that universe, they stop doing other stuff. So it's like, it can't all, I mean, clearly Marvel's the only common denominator. And no, I'm being a bit over the top. I understand structural forces. Yeah, I understand there are structural forces that make them make the decision that they make. But I'm just glad, like for someone who loves movies and hates Marvel movies and thinks they're all terrible, I'm glad to see it fail one time. Like, sorry it had to be him, but I just hope the next person is like, do I really want to tie up for the next five years? And he just maybe it's just let it be a cautionary tale. It just felt good to see a win for cinema like this.
+00:04:22 Jordan
+I mean, I hear you. But like, I can play Wolverine. He's he did a he did prisoners. He did lay mitts. He did amazing ****. Halle Berry won an Oscar around the same time she was playing Storm. There are you know, it's not it's not necessarily an either or.
+00:04:36 Darius
+You named 3 movies Hugh Jackman did outside of the 30 years he was Wolverine. Yes, that's your example of a one for me, one for you.
+00:04:48 Jordan
+How many, how many songs do you play Wolverine? Okay, he did a lot. He did a lot. But it's been, yeah, it's been like 25 years, yeah.
+00:04:53 Darius
+You got the Prestige, we got Prisoners, and we got- Yeah, Prestige, Prisoners, Les Mis. I would just like to say, since he stopped playing Wolverine, he's been a lot of different ****. He did. He just did the movie where he was voice acting the animals. He just did Sing Song Blue. Yeah, I just refused. Happy Feet. Happy Feet. It just it can't be a coincidence that he disappeared.
+00:05:15 Jordan
+I mean, I hear you. I get your point. I'm not mad at that take. I mean, I do wonder what roles the Marvel, the Avengers passed down or had to pass on because, they're scheduling and stuff like that. I mean, I wouldn't really know, I guess, but that would be cool to see.
+00:05:38 Darius
+Well, it's hard. Yeah, it's impossible to prove a negative, but it's not just the time that you shoot the movie. It's the reshoots that Marvel demands. It's the press that they demands. And then just like the insane shape you have to stay in. Which means, which it's just, All these careers just get swallowed up. And look, I get it. Again, I've said it on another pod, the nerds won, but this time I get to win and I'm happy about it. So we can move on to the next one, man. What are you watching these days, man? Let's let the people catch up with what we're into.
+00:06:19 Jordan
+Right now, I've really just been rewatching stuff for the most part. I've been rewatching Once Upon A Time. I'm on season 4 right now. Premise of the show is basically every character across like pretty much literature and fairy tales and Disney movies are in this enchanted realm. But because the Evil Queen has beef with like an eternal beef with Snow White, she's like, all right, I'm gonna get it back in blood. So she curses them, sends them into our world in this town called Storybrook and wink wink. where everyone there has forgotten who they are. So like they're all just like regular people. So for example, like Geppetto is like a carpenter, Snow White's like a school teacher, I'm trying to think, trying to think. Pinocchio is like a traveling like nomad, who just does crazy **** you know what I'm saying? So it's pretty dope. Every season there's either a new curse or a curse that's broken and there's like a new villain and there's a lot of great backstory. the heroes do villainous **** the villains do heroic ****. There's a lot of anti-heroes. It's really, really cool. It's great like character study on like human nature, which is pretty dope. So I've been watching that pretty much every night for the last couple weeks. What else have I been watching? I'm trying to think. It's really doing that. Football came back like a week and a half ago. So That's been every weekend.
+00:07:36 Darius
+Yeah. And it's like NBA is coming back soon. So it's going to be. I haven't. Yeah, it's just because it's like football Thursday, Friday. I'm not. I usually if I go out, I go out. But if I'm home, I'm probably like playing video games on Friday. And then Saturday football, Sunday football. Monday, I have to prepare for the pod and watch a game. Tuesday, we pod. It's like Wednesday is really the only day. that I can just like have turn my TV on and not have something that I have to do with it, you know?
+00:08:11 Jordan
+Yeah, same.
+00:08:12 Darius
+But I quit Snowfall after season four.
+00:08:17 Jordan
+I did see tweet that,
+00:08:19 Darius
+you know, it's just, you know, it just stopped being interesting to me. And I just want to know one of my like new things is just like,
+00:08:30 Jordan
+Stopping **** you don't want to do.
+00:08:32 Darius
+You can just quit like you can just do things like if a show sucks, people act like they're just obligated to keep going. And it's just like, you know, I'm here to let people know that you can use your free will and just like I just I finished season four and when it was like the actual core group broke up and then what really threw me off was when Leon Spoiler alert, he does that drive by and the little girl gets killed and like 2 episodes later, it's just fixed. And I was like, all right.
+00:09:01 Jordan
+Yeah, it's like, there's a lot of continuity issues in the later seasons.
+00:09:08 Darius
+He's like, we're just going to make the other guy take the fall for it and then he's going to die. And I guess the cops just quit. Like, it's not. Right, because you know how it works. It just got to be too much. And so I stopped watching that. I did watch. I recently watched Tyler Perry's new. Why did I get married movie?
+00:09:27 Jordan
+And I heard bad things.
+00:09:30 Darius
+It's, you know, his movies were never like Oscar worthy cinema, but they were just like regular bad. And now he's just, he's just playing on our phone. Like he's ************ now. He's just playing in your face. Yeah. It's just like, you're not trying. It's just I like the first two. They're good, bad movies, but it's just I, I've always made the case that like, white people get their Adam Sandler, like he's not pumping out great, it's like Tyler Perry does soap opera lifetime esque movies. And so there's a space for that for black content as well. But like, he's just not trying anymore. No, I think I saw they shot it in like a week. Yeah. And it's like in three different locations and it's just. If you because I recently watched the first one, went out, got home a little early. It was like 11 o'clock. Let me just watch this movie Tired. And it was like an hour and a half. And I watched the first one watching the first one and then going to the third one. There is a notable drop in like technical like craft and quality. Yeah, just quality. Like the cameras are better because technology has gotten better, but just like the way he edits it and like the way he shoots scenes and it's just. They it just it feels like he's just releasing first drafts and now and I don't want your rough draft. But that's really it man. Just Adam sports. So you got anything else you're watching?
+00:10:57 Jordan
+Yeah, that's pretty much it. I've just been rewatching that. If I'm watching, I pretty much only watch live TV when I'm watching sports. So if I'm watching sports and I like to have **** I hate commercials. So I'll find a movie or some **** to watch in between and I'll flip back and forth. So I'm usually watching like FX. They show a lot of movies I've seen on repeat. So like a lot of Marvel stuff or action movies, whatever, so on and so forth. So I'll usually flip back and forth between those two channels. Other than that, I haven't really been watching a lot of stuff other than movies for the pod. Because like you said, it's like Sunday football, Monday football, and I'm watching the movie for the pod. Tuesday recording, I may watch the movie again. Wednesday's like my off day.
+00:11:39 Darius
+I don't want to watch the movie on Wednesday.
+00:11:43 Jordan
+And then Thursday's football, Friday, chill, I'm outside. Saturday, I'm usually outside too. So.
+00:11:49 Darius
+Yeah, it's the schedule gets a little packed. I like it though. But definitely, you definitely can feel myself watching a lot less. Well, I'm watching more TV because I'm watching sports, but like I'm not watching TV, if that makes sense. Like my TV is on more. But you know, like during the summer, I might, I mean, I watch most of Snowfall. I rewatched. The hell did I rewatch? I watched one of those iconic shows over the summer. It all runs together once you watch them all 5 plus times. So 3 times gobbled up, man. You ready to get into your first topic?
+00:12:26 Jordan
+Yeah. Speaking of the show, I was referencing Once Upon a Time. There's a character in the show, I'm still seeing he's like one of the bigger villains slash anti-heroes character arcs in the show. And there's a conversation he has with someone where he does some really ****** ** **** and they're like, I thought you changed. Like, what the hell? And he's like, more like evolved. And so I thought it was a kind of a funny like rebrand slash like philosophy in terms of like change versus evolution. Is one is one better than the other? Is one bad? Is one good? Let's get your your initial thoughts on that. I have a couple questions, follow up questions as well.
+00:13:02 Darius
+I think it's like it's like Every rectangle can be a square, or is it the other way around?
+00:13:13 Jordan
+Or a square is a rectangle, but it's not a square.
+00:13:15 Darius
+Right. So it's like all evolution has changed, but that all change is evolution. And so it's kind of like this, which squared rectangle, the people know the saying. I just don't know it off the top of my head. So there is a difference, but all evolution is by definition some sort of change. But you know, Yes, there is a difference between the two. Evolution can be both good and bad, but sometimes change isn't responding to any sort of external stimulus. You're just changing something up to keep things fresh. And that's not necessarily evolution. How about you? What do you think?
+00:13:58 Jordan
+Yeah, I do think there's a difference. I think generally I'd say changes can be worse, quote unquote, than evolution. I think evolution has its pros and cons as well. I think about it like change is just something, obviously, something is different, right? So different doesn't always mean better. I think about it like, for example, today, society, last 20 years, we've seen, we use the phrase, everyone's so sensitive now. And so because everyone became so sensitive or got branded as being sensitive, we kind of overcorrected into just overt political incorrectness and just lack of planners and consideration for other people. And, you know, in somewhere between that is the cancel culture conversation. Right. And but it's also like, you know, do we need to do we need to make everything so drastic just because we feel like we learned our lesson? You know what I'm saying? And like, for example, I think about like the Dark Knight, right? Like he was talking, he's talking to Alfred and he's like, well, you know, you pushed them up to the point of desperation. So they went to someone they didn't understand. That's kind of like, you know, the Batman created the Joker unknowingly because he was so good and put fear into evil. So evil went to someone that they thought he would fear. You get what I'm saying? It's like, so there is a push and pull there.
+00:15:20 Darius
+Yeah, it's just we have a society has a problem with always solving the last problem and not actually getting out in front of the next one. And so it's like, you know, like I was there for I mean, we all we all were was there for like woke one, what they call it. And look, there were some excesses like there were.
+00:15:42 Jordan
+Yeah, for sure. Like, as he's on sorry, bro, like his squid never recovered.
+00:15:47 Darius
+And it's just like just like things like remember the lady who tweeted is famous. She was just tweeting like one of her favorite things to do in the morning is have coffee with her husband on the porch. And people were like telling her to check her white privilege. Oh yeah. It was like, hey guys, I don't know about that one.
+00:16:06 Jordan
+Some of us don't have a ******* porch.
+00:16:10 Darius
+My single mom working three jobs and they have time in the morning. It was like, whoa, everybody.
+00:16:15 Jordan
+It's like, I think she just was happy about her marriage. I think she's just in love with her husband, man. I think that's kind of okay.
+00:16:21 Darius
+Yeah, it's just like, that was, it's just one of those things where it's like, all right now y'all y'all
+00:16:26 Jordan
+like you dragged it bro like come on man it's like uh that's one of my favorite this whole like it's like this whole speaking of coffee it's like there's that thing where now all of a sudden people are upset that it's considered like uncool to bring an iced coffee into a job interview I'm like you might as well walk in there with your barefoot with socks on or just like with a sub eating because is that your couch yeah it's crazy
+00:16:53 Darius
+You should the job interview shouldn't feel and look like one of the errands you're running that day. Like it's not.
+00:16:57 Jordan
+No, it shouldn't feel like you're content creating and you're pulling up with a macho.
+00:17:02 Darius
+Yeah, it's just like you said, it's an overcorrection. It's like, you know, jobs used to make you have like your hair a certain way and like, or just like respectability politics. It became like, you know, you shouldn't have to have certain hairstyles too. You shouldn't have to follow any rules of decorum. And it's like, no, like that's.
+00:17:22 Jordan
+like the hairstyle policing was wrong and that was bad.
+00:17:26 Darius
+But then it's just like it became, anytime a white person asks me what I did over this weekend, that's like an invasive question. And it's like,
+00:17:35 Jordan
+I think they're just making conversation.
+00:17:38 Darius
+It's also just like no one's asking you to tell them about like your wild night to strip club. Just be like, oh, I did some things around the house and me and the fellas got up and watched the game. Like that's all you have to do.
+00:17:47 Jordan
+You can lie. Like you don't actually have to tell them what you literally did if you did some crazy **** that weekend.
+00:17:51 Darius
+Yeah, it's just like, dude, it's just crazy conversation. You have to spend a lot of time around these people and it's just gonna be better if everyone's pleasant about it. Like I don't.
+00:18:01 Jordan
+I commented on the TikTok about the iced coffee thing, and I was like, an interview is a vibe check. That's literally all it is. It's not about seeing if you can do the job. They called you in for the interview because they think you can do the job. They just want to see if you're an ******* or not, basically. I remember I was in an Uber one time on the way to a job interview, and the guy Ubering, he was like, I used to be a hiring manager. I can give you some really good tips and just give you some advice, whatever. And he was like, they're looking for a reason not to hire you when they have you been for a job interview. Like, he basically just like, don't do or say anything stupid. Don't be rude. And you know, you're going to be good. And he actually was really cool. We went over like the star responses and stuff like that. We like practiced the whole time on the way to the job, which is pretty dope. When I back pre pre car in my pre car days.
+00:18:49 Darius
+But yeah, the it's like there's the thing about most jobs, like unless you have like some super specialized technical skill, like you're a surgeon or you're, you know, some like super duper engineer, like 90% of the people are just like, are like the actual work they complete is replaceable. It's just, are you a dope hang for 8 hours a day? I can you, you know, like we can, like we can teach you the job. You know, we're not exactly, we're not, we're not putting the man on the moon at this place. Like we're just, you know, this isn't nautical engineering. We're just, No, we just need someone who's going to show up on time, do the work that is required and be pleasant to be around. And like, if you're in that room, they know you can do the job. It's just they're trying to figure out the vibes. And truly, when you show up with an iced coffee, it's just like it's it's a it's a sign that you can't you're just is it just yeah, you can't adjust or just like is the iced coffee in and of itself a big deal? No, but it signals that you are Just everything with you is going to be pulling teeth. It's like, hey, can you not, and it's just like, well, according to line 37, I'm done. It's like, all right. It took me more effort to rebut this than to just do what I ask.
+00:20:09 Jordan
+Correct. Like someone said, they made a great point. They said, in order to get social rewards, meaning the job, you have to conform to social norms, meaning don't bring the iced coffee.
+00:20:17 Darius
+Yeah. It's just like every, the social norm, like it's, there's a saying, it's called a theory of Chesterton's fence. And it's like, don't, if you see a fence in a field and it has, it's not, it's not doing anything, it's just in the field, you still should make sure you understand what that fence is doing before you remove it. And I think a lot of these social norms were like load bearing principles of society that we just kind of remove thinking they didn't do anything. And they actually were holding up a lot of things that.
+00:20:49 Jordan
+That's a good point.
+00:20:50 Darius
+It just don't remove the fence until you know exactly what that fence was put there to do. And, we're seeing this a lot with like gambling. Like when gambling was something that you had to fly to Vegas to do, or you had to go to like your bookie in a seedy dive bar who barely spoke English, That was like healthy friction in society. It was like, there's nothing, we're not, the police aren't actively investigating this or anything. Like making you go to a casino, put on clothes, shower, go down there and sit at a table in public. That was healthy friction. But now that it's in everybody's pocket, we've removed a load. That friction was load bearing.
+00:21:26 Jordan
+Yes, we've created a nation of addicts, literally.
+00:21:31 Darius
+Me and Lewis were at, I'm not going to name the place, watching Ole Miss LSU Saturday. And we were just talking. We're like, every dude around us, it was just a bunch of dudes with college football was sweating bets, like checking their parlays. And then they lie like, oh, I only put $10 on here. You ain't sweating that hard for $10. I'm like, nobody actually cares about what's happening in this game. Everyone's just sweating.
+00:21:56 Jordan
+No.
+00:21:57 Darius
+And yeah, it's it's different than what it was before. You could gamble on your phone. I've lived. I've been watching football in bars for a long time. Please don't, like, don't tell me this is the same as it always is.
+00:22:09 Jordan
+No, you're hearing the words line over, under.
+00:22:15 Darius
+No one even cares about the actual game. It's like, no, they don't root for this score here and that score here. Like you're rooting for both teams.
+00:22:21 Jordan
+Yeah, it's like, it's like, it's kind of like, like the safe version is fantasy football, which I think is totally healthy. But even with that, like when I used to play like. I'd find myself like being like, I hope we win, but I also hope this dude on the side of the ball gets 100 yards receiving. And I'm like, it's kind of a conflict of interest, you know, when it comes to like your love of the game.
+00:22:41 Darius
+I quit fantasy football for that reason. I found myself like just like rooting for, like you said, conflicting outcomes. And I just.
+00:22:50 Jordan
+Yeah.
+00:22:52 Darius
+I just, it just wasn't fun. And then for that little $50 bet you put in on the 1% chance that you're going to win 500 bucks, like I'd rather just watch football the old way and just cheer for the Vikings to win regardless of how. And just, it's just, I get it. Like what you said, fantasy football though is like a healthy tension. It's a healthy, you know, gamble. But like, When you got people betting on if so-and-so is going to have 4 catches and then it's just, and they're losing, all of you are losing. Everybody I talk to is supposedly a winner. That's not mathematically possible.
+00:23:26 Jordan
+Yeah, man, one of my homeboys, Dennis, one of my best friends, he had a parlay and all he needed week one was Richard Mark Chase to hit 50 yards. And he had like 12 yards for the game. And I can't even repeat the words he said in a group chat that day.
+00:23:43 Darius
+And who's his team?
+00:23:46 Jordan
+He's a Cowboys fan.
+00:23:47 Darius
+Okay, so I was going to say the Cowboys lost that week, right? But I was hoping that like his team won and I'd like he's not even he doesn't even care because he lost his game.
+00:23:55 Jordan
+No, he just he had a bad week regardless.
+00:24:00 Darius
+Yeah, I just think, you know, just be when you remove a social norm, understand why that fence was there in the 1st place. That's, you know, it's We're finding out a lot of things like, you know, like, hey, you actually do have to be pleasant to your coworkers. I didn't think we had to say it out loud. Don't bring iced coffee to interviews.
+00:24:21 Jordan
+No, real **** man. I get tired of this whole like people trying to romanticize being antisocial as like an act of freedom, you know, like a rebellion. And it's like, all right, well, when they fire you, Don't cry. Don't play the cards, you know, like Duke Energy.
+00:24:38 Darius
+Don't care about none of that. They want their money.
+00:24:39 Jordan
+No, they don't give a what, none of that ****. They don't give a what, none of that.
+00:24:44 Darius
+Yeah, it's just it's like the whole, like, wash the thing. Like it was in the beginning. Antisocial. Like, I like to stay in the house or, you know, like, you know, I'm getting older, I'm washed. And then it just like, suddenly I just saw someone one day was like, After 30 plus, don't ask me to come out after 7:00. And I was like, all right, no. Bro, come on, man.
+00:25:06 Jordan
+What the hell are you doing on the weekends?
+00:25:08 Darius
+Come on, dude. I ain't that watch. I'm not ready for the nursing home. Like I'm not ill.
+00:25:12 Jordan
+There's a, yeah, there's a very, very thick line between being an old *** in the club and being prematurely Washed or whatever you want to call yourself.
+00:25:22 Darius
+Yeah. Like, am I out till 3:00 in the clubs anymore? No, but I'm not ready for bingo night either. Like, it's like, it's got to be slipping in between that, you know?
+00:25:30 Jordan
+There are dive bars, there are lounges, I like house parties.
+00:25:32 Darius
+It was like, it was like, man, after 7:00, don't ask a millennial out. And I was like, millennial here, it's fine. Yeah. Is this thing on? I ain't with that one. That one's a little too much.
+00:25:46 Jordan
+Yeah, no, because no, what are you doing at 7 P.m.? Like that's just coming.
+00:25:51 Darius
+Unless you got like one of them jobs or you up at 4 in the morning, you really should not even be like winding. Like it's seven. Is the sun even down during the summer at 7? No, you know, no. Do it a little too much. Yeah. You had some follow up questions for that one you said.
+00:26:12 Jordan
+Yeah. So do you know the phrase, the more things change, the more they stay the same?
+00:26:16 Darius
+Yeah.
+00:26:16 Jordan
+Do you agree with that?
+00:26:20 Darius
+I think to go back to your original point, I think things just whiplash back and forth. And so I think history repeats itself, but I don't think things stay exactly the same. I don't think it's static. History repeats itself. What is it? History doesn't repeat itself, but it rhymes. And so you kind of, like you said, there's a correction and then an overcorrection and then an overcorrection and an overcorrection. And now we got Pat McAfee smoking weed on TV. You know, it's just...
+00:26:56 Jordan
+They went from like... We incorporate everyone to, nah, we showed a White House UFC event.
+00:27:06 Darius
+It was just like we went from sports being like this super stuffy, super serious thing to like, and maybe we should have loosened that up a bit. And now we got people smoking weed on TV. And I just think that's too far. I agree. I agree. Kids could be watching. You know, this is the middle of the day. People have this stuff on at the dentist office.
+00:27:28 Jordan
+Yeah.
+00:27:28 Darius
+I was smoking Saturday.
+00:27:29 Jordan
+It's a Saturday. Come on.
+00:27:30 Darius
+Yeah. Like, dude, it's just like, come on, can we be, can we be grownups? You know, like, you know, if you.
+00:27:34 Jordan
+Pull a stone, fine, but like, don't.
+00:27:37 Darius
+We don't need you like dressed like the Monopoly man, but can we have a little bit? Yeah. Some, rules here. You know, it's just.
+00:27:47 Jordan
+I'm with you on that.
+00:27:50 Darius
+What's your answer to the question on that?
+00:27:54 Jordan
+I'd say I'm more on the agreeing side of that. I think, things shape shift, but they're still at the core. The purpose may be the same. For example, like, is there a difference between a book and a Kindle? No, the form is different. You know, you still have to intake the content. You know, we sought out like for, frying with grease and stuff with an air fryer. Okay, well, you're still using heat to, you know, cook the food. You know, it's like it's just evolution, you know? So in that sense, I do agree.
+00:28:28 Darius
+I saw a tweet the other day or today. It was like of a mall, a Christmas mall, a mall during Christmas in like the 90s. And of course, it's packed. Yeah, it's a giant tree. And someone captioned it with like, private equity ruined this. And look, I'm not the biggest fan of private equity, but consumers decided they don't want to deal with the mall anymore. And we have technology has made us more efficient and we shop online and they could build that mall tomorrow.
+00:28:55 Jordan
+Unless people die on Black Fridays.
+00:28:56 Darius
+They could build that mall tomorrow and yo *** ain't going. I ain't going. You know, like you want them to, who's gonna pay for this empty mall every year so you can see pictures of it? Like it's not, you're not gonna shop there. When's the last time yo *** been to the mall? You know, it's just like, if I go to the mall, it's like a novelty thing. going to the Cheesecake Factory or something for dinner. And I'm like, we walk through the mall. I'm not ever going there.
+00:29:19 Jordan
+Christmas shopping, maybe, something like that.
+00:29:22 Darius
+Yankees got some candles on sale. I don't feel like paying to ship them. Let me just go down to Crabtree.
+00:29:27 Jordan
+I don't know my hat size for like fitted. So I would go to Lid's to measure and do the, you know, whatever.
+00:29:33 Darius
+Yeah, but like it's not like I remember going to the mall was like part of the errand you ran and that's no longer the case. No. So, no, they're not going to keep building malls because no one's going to. Oh, speaking of Kindle versus physical books, my topic here, physical versus digital media, man, according to the RIA, CD and vinyl sales are up 6.9% over this over the same period of time last year. Basically, Every year since COVID, you've seen an increase in physical media sales, basically, especially with regards to like vinyl.
+00:30:13 Jordan
+Yeah.
+00:30:14 Darius
+So obviously physical media comes with an increased expense, almost 10x over. You have to find places to put these things. It's inconvenient and more expensive to have physical media. So why are people willing to pay that premium price for physical copies, in your opinion?
+00:30:32 Jordan
+I think it's funny you brought up COVID because I didn't realize it was since COVID, but I think that year slash two year period really wrecked everyone's perspective or shifted everyone's perspective. I feel like everything became so much more aware of impermanence that I think people just went back to what they know. Like, you know, it's like you have you date someone new and you don't like them. You might text your ex, hey, what's up? You know, and and so, you know, the world came to an end. You know, everybody was locked in their house streaming things. And then they probably were just like, you know what I miss going out to the store and buying **** you know, I also just think, you know, people like comforting. Those are really scary times, you know, that's another factor too. yeah I </t>
+  </si>
 </sst>
 </file>
 
@@ -9854,7 +10179,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9878,7 +10203,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9895,6 +10219,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10214,7 +10542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -10890,8 +11218,8 @@
       <c r="D40" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="E40" s="11" t="s">
-        <v>272</v>
+      <c r="E40" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
@@ -10914,13 +11242,27 @@
         <v>268</v>
       </c>
       <c r="B42" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C42" s="10">
         <v>46297</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>272</v>
+      </c>
+      <c r="B43" t="s">
+        <v>273</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -10935,7 +11277,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -11529,7 +11871,21 @@
         <v>46297</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>272</v>
+      </c>
+      <c r="B43" t="s">
+        <v>273</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3E97AE-7DAE-4ECC-A0F6-CF91E6CC3BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB36BE2-827D-4382-99B8-B9D4D21FF2C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="321">
   <si>
     <t>youtube_link</t>
   </si>
@@ -10090,6 +10090,135 @@
 00:30:32 Jordan
 I think it's funny you brought up COVID because I didn't realize it was since COVID, but I think that year slash two year period really wrecked everyone's perspective or shifted everyone's perspective. I feel like everything became so much more aware of impermanence that I think people just went back to what they know. Like, you know, it's like you have you date someone new and you don't like them. You might text your ex, hey, what's up? You know, and and so, you know, the world came to an end. You know, everybody was locked in their house streaming things. And then they probably were just like, you know what I miss going out to the store and buying **** you know, I also just think, you know, people like comforting. Those are really scary times, you know, that's another factor too. yeah I </t>
   </si>
+  <si>
+    <t>topics</t>
+  </si>
+  <si>
+    <t>Aging &amp; Adulthood, Class &amp; Money, Movies &amp; Cinema, Community &amp; Public Life</t>
+  </si>
+  <si>
+    <t>Aging &amp; Adulthood, Class &amp; Money, Marriage &amp; Family, Pop Culture &amp; Celebrity</t>
+  </si>
+  <si>
+    <t>Technology &amp; Internet Culture, Creativity &amp; Art, Media Criticism &amp; Fandom, Sports &amp; Athletics</t>
+  </si>
+  <si>
+    <t>Marriage &amp; Family, Relationships &amp; Dating, Social Norms &amp; Etiquette, Nostalgia &amp; Hobbies</t>
+  </si>
+  <si>
+    <t>Creativity &amp; Art, Class &amp; Money, Work &amp; Ambition, Music &amp; Hip-Hop</t>
+  </si>
+  <si>
+    <t>Community &amp; Public Life, Social Norms &amp; Etiquette, Technology &amp; Internet Culture, Work &amp; Ambition</t>
+  </si>
+  <si>
+    <t>Relationships &amp; Dating, Marriage &amp; Family, Aging &amp; Adulthood</t>
+  </si>
+  <si>
+    <t>Marriage &amp; Family, Class &amp; Money, Nostalgia &amp; Hobbies</t>
+  </si>
+  <si>
+    <t>Marriage &amp; Family, Relationships &amp; Dating, Technology &amp; Internet Culture, Aging &amp; Adulthood</t>
+  </si>
+  <si>
+    <t>Friendship &amp; Social Circles, Work &amp; Ambition, Creativity &amp; Art, Social Norms &amp; Etiquette</t>
+  </si>
+  <si>
+    <t>Friendship &amp; Social Circles, Marriage &amp; Family, Community &amp; Public Life</t>
+  </si>
+  <si>
+    <t>Work &amp; Ambition, Aging &amp; Adulthood, Friendship &amp; Social Circles, Personal Growth &amp; Discipline</t>
+  </si>
+  <si>
+    <t>Relationships &amp; Dating, Nostalgia &amp; Hobbies, Creativity &amp; Art, Personal Growth &amp; Discipline</t>
+  </si>
+  <si>
+    <t>Music &amp; Hip-Hop, Pop Culture &amp; Celebrity, Media Criticism &amp; Fandom</t>
+  </si>
+  <si>
+    <t>Aging &amp; Adulthood, Social Norms &amp; Etiquette</t>
+  </si>
+  <si>
+    <t>Media Criticism &amp; Fandom, Pop Culture &amp; Celebrity, Technology &amp; Internet Culture</t>
+  </si>
+  <si>
+    <t>Movies &amp; Cinema, Music &amp; Hip-Hop, Pop Culture &amp; Celebrity, Media Criticism &amp; Fandom</t>
+  </si>
+  <si>
+    <t>Sports &amp; Athletics, Class &amp; Money, Food &amp; Food Culture, Media Criticism &amp; Fandom</t>
+  </si>
+  <si>
+    <t>Music &amp; Hip-Hop, Nostalgia &amp; Hobbies, Community &amp; Public Life, Class &amp; Money</t>
+  </si>
+  <si>
+    <t>Personal Growth &amp; Discipline, Work &amp; Ambition, Aging &amp; Adulthood, Creativity &amp; Art</t>
+  </si>
+  <si>
+    <t>Aging &amp; Adulthood, Pop Culture &amp; Celebrity, Relationships &amp; Dating, Technology &amp; Internet Culture</t>
+  </si>
+  <si>
+    <t>Sports &amp; Athletics, Movies &amp; Cinema, Pop Culture &amp; Celebrity, Media Criticism &amp; Fandom</t>
+  </si>
+  <si>
+    <t>Technology &amp; Internet Culture, Social Norms &amp; Etiquette, Media Criticism &amp; Fandom, Pop Culture &amp; Celebrity</t>
+  </si>
+  <si>
+    <t>Food &amp; Food Culture, Marriage &amp; Family, Class &amp; Money, Technology &amp; Internet Culture</t>
+  </si>
+  <si>
+    <t>Music &amp; Hip-Hop, Aging &amp; Adulthood, Nostalgia &amp; Hobbies, Pop Culture &amp; Celebrity</t>
+  </si>
+  <si>
+    <t>Social Norms &amp; Etiquette, Class &amp; Money, Technology &amp; Internet Culture, Community &amp; Public Life</t>
+  </si>
+  <si>
+    <t>Friendship &amp; Social Circles, Community &amp; Public Life, Aging &amp; Adulthood, Social Norms &amp; Etiquette</t>
+  </si>
+  <si>
+    <t>Creativity &amp; Art, Personal Growth &amp; Discipline, Relationships &amp; Dating, Pop Culture &amp; Celebrity</t>
+  </si>
+  <si>
+    <t>Creativity &amp; Art, Personal Growth &amp; Discipline, Pop Culture &amp; Celebrity, Work &amp; Ambition</t>
+  </si>
+  <si>
+    <t>Technology &amp; Internet Culture, Class &amp; Money, Aging &amp; Adulthood, Personal Growth &amp; Discipline</t>
+  </si>
+  <si>
+    <t>Community &amp; Public Life, Technology &amp; Internet Culture, Friendship &amp; Social Circles, Food &amp; Food Culture</t>
+  </si>
+  <si>
+    <t>Music &amp; Hip-Hop, Pop Culture &amp; Celebrity, Media Criticism &amp; Fandom, Marriage &amp; Family</t>
+  </si>
+  <si>
+    <t>Music &amp; Hip-Hop, Sports &amp; Athletics, Creativity &amp; Art, Movies &amp; Cinema</t>
+  </si>
+  <si>
+    <t>Class &amp; Money, Sports &amp; Athletics, Music &amp; Hip-Hop, Technology &amp; Internet Culture</t>
+  </si>
+  <si>
+    <t>Social Norms &amp; Etiquette, Aging &amp; Adulthood, Relationships &amp; Dating, Personal Growth &amp; Discipline</t>
+  </si>
+  <si>
+    <t>Aging &amp; Adulthood, Relationships &amp; Dating, Media Criticism &amp; Fandom, Food &amp; Food Culture</t>
+  </si>
+  <si>
+    <t>Aging &amp; Adulthood, Technology &amp; Internet Culture, Media Criticism &amp; Fandom, Work &amp; Ambition</t>
+  </si>
+  <si>
+    <t>Technology &amp; Internet Culture, Personal Growth &amp; Discipline, Movies &amp; Cinema, Nostalgia &amp; Hobbies</t>
+  </si>
+  <si>
+    <t>Nostalgia &amp; Hobbies, Aging &amp; Adulthood, Personal Growth &amp; Discipline, Creativity &amp; Art</t>
+  </si>
+  <si>
+    <t>Marriage &amp; Family, Community &amp; Public Life, Creativity &amp; Art, Technology &amp; Internet Culture</t>
+  </si>
+  <si>
+    <t>Food &amp; Food Culture, Personal Growth &amp; Discipline, Technology &amp; Internet Culture, Nostalgia &amp; Hobbies</t>
+  </si>
+  <si>
+    <t>Movies &amp; Cinema, Social Norms &amp; Etiquette, Technology &amp; Internet Culture, Community &amp; Public Life</t>
+  </si>
 </sst>
 </file>
 
@@ -10179,7 +10308,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10203,6 +10332,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -10542,7 +10674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -10550,9 +10682,10 @@
     <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="66.7109375" customWidth="1"/>
     <col min="5" max="5" width="45.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>106</v>
       </c>
@@ -10568,8 +10701,11 @@
       <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="F1" t="s">
+        <v>278</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>107</v>
       </c>
@@ -10585,8 +10721,11 @@
       <c r="E2" s="5" t="s">
         <v>157</v>
       </c>
+      <c r="F2" s="11" t="s">
+        <v>279</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>108</v>
       </c>
@@ -10602,8 +10741,11 @@
       <c r="E3" s="6" t="s">
         <v>146</v>
       </c>
+      <c r="F3" s="11" t="s">
+        <v>280</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>109</v>
       </c>
@@ -10619,8 +10761,11 @@
       <c r="E4" s="5" t="s">
         <v>147</v>
       </c>
+      <c r="F4" s="11" t="s">
+        <v>281</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>110</v>
       </c>
@@ -10636,8 +10781,11 @@
       <c r="E5" s="5" t="s">
         <v>148</v>
       </c>
+      <c r="F5" s="11" t="s">
+        <v>282</v>
+      </c>
     </row>
-    <row r="6" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>111</v>
       </c>
@@ -10653,8 +10801,11 @@
       <c r="E6" s="5" t="s">
         <v>158</v>
       </c>
+      <c r="F6" s="11" t="s">
+        <v>283</v>
+      </c>
     </row>
-    <row r="7" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>112</v>
       </c>
@@ -10670,8 +10821,11 @@
       <c r="E7" s="5" t="s">
         <v>159</v>
       </c>
+      <c r="F7" s="11" t="s">
+        <v>284</v>
+      </c>
     </row>
-    <row r="8" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>113</v>
       </c>
@@ -10687,8 +10841,11 @@
       <c r="E8" s="5" t="s">
         <v>177</v>
       </c>
+      <c r="F8" s="11" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="9" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>114</v>
       </c>
@@ -10704,8 +10861,11 @@
       <c r="E9" s="5" t="s">
         <v>160</v>
       </c>
+      <c r="F9" s="11" t="s">
+        <v>286</v>
+      </c>
     </row>
-    <row r="10" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>115</v>
       </c>
@@ -10721,8 +10881,11 @@
       <c r="E10" s="5" t="s">
         <v>161</v>
       </c>
+      <c r="F10" s="11" t="s">
+        <v>287</v>
+      </c>
     </row>
-    <row r="11" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>116</v>
       </c>
@@ -10738,8 +10901,11 @@
       <c r="E11" s="5" t="s">
         <v>162</v>
       </c>
+      <c r="F11" s="11" t="s">
+        <v>288</v>
+      </c>
     </row>
-    <row r="12" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>117</v>
       </c>
@@ -10755,8 +10921,11 @@
       <c r="E12" s="5" t="s">
         <v>163</v>
       </c>
+      <c r="F12" s="11" t="s">
+        <v>289</v>
+      </c>
     </row>
-    <row r="13" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>118</v>
       </c>
@@ -10772,8 +10941,11 @@
       <c r="E13" s="5" t="s">
         <v>164</v>
       </c>
+      <c r="F13" s="11" t="s">
+        <v>290</v>
+      </c>
     </row>
-    <row r="14" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>119</v>
       </c>
@@ -10789,8 +10961,11 @@
       <c r="E14" s="5" t="s">
         <v>165</v>
       </c>
+      <c r="F14" s="11" t="s">
+        <v>291</v>
+      </c>
     </row>
-    <row r="15" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>120</v>
       </c>
@@ -10804,8 +10979,11 @@
         <v>231</v>
       </c>
       <c r="E15" s="5"/>
+      <c r="F15" s="11" t="s">
+        <v>292</v>
+      </c>
     </row>
-    <row r="16" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>121</v>
       </c>
@@ -10819,8 +10997,11 @@
         <v>232</v>
       </c>
       <c r="E16" s="5"/>
+      <c r="F16" s="11" t="s">
+        <v>293</v>
+      </c>
     </row>
-    <row r="17" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>122</v>
       </c>
@@ -10836,8 +11017,11 @@
       <c r="E17" s="5" t="s">
         <v>149</v>
       </c>
+      <c r="F17" s="11" t="s">
+        <v>294</v>
+      </c>
     </row>
-    <row r="18" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>123</v>
       </c>
@@ -10853,8 +11037,11 @@
       <c r="E18" s="5" t="s">
         <v>166</v>
       </c>
+      <c r="F18" s="11" t="s">
+        <v>295</v>
+      </c>
     </row>
-    <row r="19" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>124</v>
       </c>
@@ -10870,8 +11057,11 @@
       <c r="E19" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="F19" s="11" t="s">
+        <v>296</v>
+      </c>
     </row>
-    <row r="20" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>125</v>
       </c>
@@ -10887,8 +11077,11 @@
       <c r="E20" s="5" t="s">
         <v>168</v>
       </c>
+      <c r="F20" s="11" t="s">
+        <v>297</v>
+      </c>
     </row>
-    <row r="21" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>126</v>
       </c>
@@ -10902,8 +11095,11 @@
         <v>237</v>
       </c>
       <c r="E21" s="5"/>
+      <c r="F21" s="11" t="s">
+        <v>298</v>
+      </c>
     </row>
-    <row r="22" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>127</v>
       </c>
@@ -10919,8 +11115,11 @@
       <c r="E22" s="5" t="s">
         <v>169</v>
       </c>
+      <c r="F22" s="11" t="s">
+        <v>299</v>
+      </c>
     </row>
-    <row r="23" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>128</v>
       </c>
@@ -10936,8 +11135,11 @@
       <c r="E23" s="5" t="s">
         <v>170</v>
       </c>
+      <c r="F23" s="11" t="s">
+        <v>300</v>
+      </c>
     </row>
-    <row r="24" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>129</v>
       </c>
@@ -10953,8 +11155,11 @@
       <c r="E24" s="5" t="s">
         <v>150</v>
       </c>
+      <c r="F24" s="11" t="s">
+        <v>301</v>
+      </c>
     </row>
-    <row r="25" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -10968,8 +11173,11 @@
         <v>241</v>
       </c>
       <c r="E25" s="5"/>
+      <c r="F25" s="11" t="s">
+        <v>302</v>
+      </c>
     </row>
-    <row r="26" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>131</v>
       </c>
@@ -10985,8 +11193,11 @@
       <c r="E26" s="5" t="s">
         <v>171</v>
       </c>
+      <c r="F26" s="11" t="s">
+        <v>303</v>
+      </c>
     </row>
-    <row r="27" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>132</v>
       </c>
@@ -11000,8 +11211,11 @@
         <v>243</v>
       </c>
       <c r="E27" s="5"/>
+      <c r="F27" s="11" t="s">
+        <v>304</v>
+      </c>
     </row>
-    <row r="28" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>133</v>
       </c>
@@ -11017,8 +11231,11 @@
       <c r="E28" s="5" t="s">
         <v>151</v>
       </c>
+      <c r="F28" s="11" t="s">
+        <v>305</v>
+      </c>
     </row>
-    <row r="29" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>134</v>
       </c>
@@ -11034,8 +11251,11 @@
       <c r="E29" s="5" t="s">
         <v>152</v>
       </c>
+      <c r="F29" s="11" t="s">
+        <v>306</v>
+      </c>
     </row>
-    <row r="30" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>135</v>
       </c>
@@ -11051,8 +11271,11 @@
       <c r="E30" s="5" t="s">
         <v>172</v>
       </c>
+      <c r="F30" s="11" t="s">
+        <v>307</v>
+      </c>
     </row>
-    <row r="31" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>136</v>
       </c>
@@ -11068,8 +11291,11 @@
       <c r="E31" s="5" t="s">
         <v>153</v>
       </c>
+      <c r="F31" s="11" t="s">
+        <v>308</v>
+      </c>
     </row>
-    <row r="32" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>137</v>
       </c>
@@ -11085,8 +11311,11 @@
       <c r="E32" s="5" t="s">
         <v>154</v>
       </c>
+      <c r="F32" s="11" t="s">
+        <v>309</v>
+      </c>
     </row>
-    <row r="33" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>138</v>
       </c>
@@ -11102,8 +11331,11 @@
       <c r="E33" s="5" t="s">
         <v>155</v>
       </c>
+      <c r="F33" s="11" t="s">
+        <v>310</v>
+      </c>
     </row>
-    <row r="34" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>139</v>
       </c>
@@ -11119,8 +11351,11 @@
       <c r="E34" s="5" t="s">
         <v>173</v>
       </c>
+      <c r="F34" s="11" t="s">
+        <v>311</v>
+      </c>
     </row>
-    <row r="35" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>140</v>
       </c>
@@ -11136,8 +11371,11 @@
       <c r="E35" s="5" t="s">
         <v>156</v>
       </c>
+      <c r="F35" s="11" t="s">
+        <v>312</v>
+      </c>
     </row>
-    <row r="36" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>141</v>
       </c>
@@ -11153,8 +11391,11 @@
       <c r="E36" s="5" t="s">
         <v>174</v>
       </c>
+      <c r="F36" s="11" t="s">
+        <v>313</v>
+      </c>
     </row>
-    <row r="37" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>142</v>
       </c>
@@ -11170,8 +11411,11 @@
       <c r="E37" s="5" t="s">
         <v>175</v>
       </c>
+      <c r="F37" s="11" t="s">
+        <v>314</v>
+      </c>
     </row>
-    <row r="38" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>143</v>
       </c>
@@ -11187,8 +11431,11 @@
       <c r="E38" s="5" t="s">
         <v>176</v>
       </c>
+      <c r="F38" s="11" t="s">
+        <v>315</v>
+      </c>
     </row>
-    <row r="39" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>144</v>
       </c>
@@ -11204,8 +11451,11 @@
       <c r="E39" t="s">
         <v>267</v>
       </c>
+      <c r="F39" s="11" t="s">
+        <v>316</v>
+      </c>
     </row>
-    <row r="40" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>145</v>
       </c>
@@ -11221,8 +11471,11 @@
       <c r="E40" t="s">
         <v>271</v>
       </c>
+      <c r="F40" s="11" t="s">
+        <v>317</v>
+      </c>
     </row>
-    <row r="41" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>264</v>
       </c>
@@ -11236,8 +11489,11 @@
         <v>265</v>
       </c>
       <c r="E41" s="5"/>
+      <c r="F41" s="11" t="s">
+        <v>318</v>
+      </c>
     </row>
-    <row r="42" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>268</v>
       </c>
@@ -11250,8 +11506,11 @@
       <c r="D42" s="4" t="s">
         <v>270</v>
       </c>
+      <c r="F42" s="11" t="s">
+        <v>319</v>
+      </c>
     </row>
-    <row r="43" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>272</v>
       </c>
@@ -11263,6 +11522,9 @@
       </c>
       <c r="D43" s="4" t="s">
         <v>276</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB36BE2-827D-4382-99B8-B9D4D21FF2C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64D1AE8-CEC5-41F6-A66D-AB80611B8E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
@@ -10094,130 +10094,130 @@
     <t>topics</t>
   </si>
   <si>
-    <t>Aging &amp; Adulthood, Class &amp; Money, Movies &amp; Cinema, Community &amp; Public Life</t>
-  </si>
-  <si>
-    <t>Aging &amp; Adulthood, Class &amp; Money, Marriage &amp; Family, Pop Culture &amp; Celebrity</t>
-  </si>
-  <si>
-    <t>Technology &amp; Internet Culture, Creativity &amp; Art, Media Criticism &amp; Fandom, Sports &amp; Athletics</t>
-  </si>
-  <si>
-    <t>Marriage &amp; Family, Relationships &amp; Dating, Social Norms &amp; Etiquette, Nostalgia &amp; Hobbies</t>
-  </si>
-  <si>
-    <t>Creativity &amp; Art, Class &amp; Money, Work &amp; Ambition, Music &amp; Hip-Hop</t>
-  </si>
-  <si>
-    <t>Community &amp; Public Life, Social Norms &amp; Etiquette, Technology &amp; Internet Culture, Work &amp; Ambition</t>
-  </si>
-  <si>
-    <t>Relationships &amp; Dating, Marriage &amp; Family, Aging &amp; Adulthood</t>
-  </si>
-  <si>
-    <t>Marriage &amp; Family, Class &amp; Money, Nostalgia &amp; Hobbies</t>
-  </si>
-  <si>
-    <t>Marriage &amp; Family, Relationships &amp; Dating, Technology &amp; Internet Culture, Aging &amp; Adulthood</t>
-  </si>
-  <si>
-    <t>Friendship &amp; Social Circles, Work &amp; Ambition, Creativity &amp; Art, Social Norms &amp; Etiquette</t>
-  </si>
-  <si>
-    <t>Friendship &amp; Social Circles, Marriage &amp; Family, Community &amp; Public Life</t>
-  </si>
-  <si>
-    <t>Work &amp; Ambition, Aging &amp; Adulthood, Friendship &amp; Social Circles, Personal Growth &amp; Discipline</t>
-  </si>
-  <si>
-    <t>Relationships &amp; Dating, Nostalgia &amp; Hobbies, Creativity &amp; Art, Personal Growth &amp; Discipline</t>
-  </si>
-  <si>
-    <t>Music &amp; Hip-Hop, Pop Culture &amp; Celebrity, Media Criticism &amp; Fandom</t>
-  </si>
-  <si>
-    <t>Aging &amp; Adulthood, Social Norms &amp; Etiquette</t>
-  </si>
-  <si>
-    <t>Media Criticism &amp; Fandom, Pop Culture &amp; Celebrity, Technology &amp; Internet Culture</t>
-  </si>
-  <si>
-    <t>Movies &amp; Cinema, Music &amp; Hip-Hop, Pop Culture &amp; Celebrity, Media Criticism &amp; Fandom</t>
-  </si>
-  <si>
-    <t>Sports &amp; Athletics, Class &amp; Money, Food &amp; Food Culture, Media Criticism &amp; Fandom</t>
-  </si>
-  <si>
-    <t>Music &amp; Hip-Hop, Nostalgia &amp; Hobbies, Community &amp; Public Life, Class &amp; Money</t>
-  </si>
-  <si>
-    <t>Personal Growth &amp; Discipline, Work &amp; Ambition, Aging &amp; Adulthood, Creativity &amp; Art</t>
-  </si>
-  <si>
-    <t>Aging &amp; Adulthood, Pop Culture &amp; Celebrity, Relationships &amp; Dating, Technology &amp; Internet Culture</t>
-  </si>
-  <si>
-    <t>Sports &amp; Athletics, Movies &amp; Cinema, Pop Culture &amp; Celebrity, Media Criticism &amp; Fandom</t>
-  </si>
-  <si>
-    <t>Technology &amp; Internet Culture, Social Norms &amp; Etiquette, Media Criticism &amp; Fandom, Pop Culture &amp; Celebrity</t>
-  </si>
-  <si>
-    <t>Food &amp; Food Culture, Marriage &amp; Family, Class &amp; Money, Technology &amp; Internet Culture</t>
-  </si>
-  <si>
-    <t>Music &amp; Hip-Hop, Aging &amp; Adulthood, Nostalgia &amp; Hobbies, Pop Culture &amp; Celebrity</t>
-  </si>
-  <si>
-    <t>Social Norms &amp; Etiquette, Class &amp; Money, Technology &amp; Internet Culture, Community &amp; Public Life</t>
-  </si>
-  <si>
-    <t>Friendship &amp; Social Circles, Community &amp; Public Life, Aging &amp; Adulthood, Social Norms &amp; Etiquette</t>
-  </si>
-  <si>
-    <t>Creativity &amp; Art, Personal Growth &amp; Discipline, Relationships &amp; Dating, Pop Culture &amp; Celebrity</t>
-  </si>
-  <si>
-    <t>Creativity &amp; Art, Personal Growth &amp; Discipline, Pop Culture &amp; Celebrity, Work &amp; Ambition</t>
-  </si>
-  <si>
-    <t>Technology &amp; Internet Culture, Class &amp; Money, Aging &amp; Adulthood, Personal Growth &amp; Discipline</t>
-  </si>
-  <si>
-    <t>Community &amp; Public Life, Technology &amp; Internet Culture, Friendship &amp; Social Circles, Food &amp; Food Culture</t>
-  </si>
-  <si>
-    <t>Music &amp; Hip-Hop, Pop Culture &amp; Celebrity, Media Criticism &amp; Fandom, Marriage &amp; Family</t>
-  </si>
-  <si>
     <t>Music &amp; Hip-Hop, Sports &amp; Athletics, Creativity &amp; Art, Movies &amp; Cinema</t>
   </si>
   <si>
-    <t>Class &amp; Money, Sports &amp; Athletics, Music &amp; Hip-Hop, Technology &amp; Internet Culture</t>
-  </si>
-  <si>
-    <t>Social Norms &amp; Etiquette, Aging &amp; Adulthood, Relationships &amp; Dating, Personal Growth &amp; Discipline</t>
-  </si>
-  <si>
-    <t>Aging &amp; Adulthood, Relationships &amp; Dating, Media Criticism &amp; Fandom, Food &amp; Food Culture</t>
-  </si>
-  <si>
-    <t>Aging &amp; Adulthood, Technology &amp; Internet Culture, Media Criticism &amp; Fandom, Work &amp; Ambition</t>
-  </si>
-  <si>
-    <t>Technology &amp; Internet Culture, Personal Growth &amp; Discipline, Movies &amp; Cinema, Nostalgia &amp; Hobbies</t>
-  </si>
-  <si>
-    <t>Nostalgia &amp; Hobbies, Aging &amp; Adulthood, Personal Growth &amp; Discipline, Creativity &amp; Art</t>
-  </si>
-  <si>
-    <t>Marriage &amp; Family, Community &amp; Public Life, Creativity &amp; Art, Technology &amp; Internet Culture</t>
-  </si>
-  <si>
-    <t>Food &amp; Food Culture, Personal Growth &amp; Discipline, Technology &amp; Internet Culture, Nostalgia &amp; Hobbies</t>
-  </si>
-  <si>
-    <t>Movies &amp; Cinema, Social Norms &amp; Etiquette, Technology &amp; Internet Culture, Community &amp; Public Life</t>
+    <t>Aging &amp; Personal Growth, Money &amp; Class, Movies &amp; Cinema, Friendship &amp; Community</t>
+  </si>
+  <si>
+    <t>Aging &amp; Personal Growth, Money &amp; Class, Relationships &amp; Family, Sports &amp; Athletics</t>
+  </si>
+  <si>
+    <t>Technology &amp; Internet Culture, Creativity &amp; Art, Movies &amp; Cinema, Sports &amp; Athletics</t>
+  </si>
+  <si>
+    <t>Relationships &amp; Family, Social Norms &amp; Etiquette, Technology &amp; Internet Culture</t>
+  </si>
+  <si>
+    <t>Creativity &amp; Art, Money &amp; Class, Work &amp; Ambition, Music &amp; Hip-Hop</t>
+  </si>
+  <si>
+    <t>Friendship &amp; Community, Social Norms &amp; Etiquette, Technology &amp; Internet Culture, Work &amp; Ambition</t>
+  </si>
+  <si>
+    <t>Relationships &amp; Family, Aging &amp; Personal Growth</t>
+  </si>
+  <si>
+    <t>Relationships &amp; Family, Money &amp; Class</t>
+  </si>
+  <si>
+    <t>Relationships &amp; Family, Aging &amp; Personal Growth, Technology &amp; Internet Culture</t>
+  </si>
+  <si>
+    <t>Friendship &amp; Community, Work &amp; Ambition, Creativity &amp; Art, Social Norms &amp; Etiquette</t>
+  </si>
+  <si>
+    <t>Friendship &amp; Community, Relationships &amp; Family</t>
+  </si>
+  <si>
+    <t>Work &amp; Ambition, Aging &amp; Personal Growth, Friendship &amp; Community</t>
+  </si>
+  <si>
+    <t>Relationships &amp; Family, Creativity &amp; Art, Aging &amp; Personal Growth, Technology &amp; Internet Culture</t>
+  </si>
+  <si>
+    <t>Music &amp; Hip-Hop, Creativity &amp; Art</t>
+  </si>
+  <si>
+    <t>Aging &amp; Personal Growth, Social Norms &amp; Etiquette</t>
+  </si>
+  <si>
+    <t>Technology &amp; Internet Culture, Movies &amp; Cinema, Social Norms &amp; Etiquette</t>
+  </si>
+  <si>
+    <t>Movies &amp; Cinema, Music &amp; Hip-Hop, Creativity &amp; Art</t>
+  </si>
+  <si>
+    <t>Sports &amp; Athletics, Money &amp; Class, Food &amp; Lifestyle, Technology &amp; Internet Culture</t>
+  </si>
+  <si>
+    <t>Music &amp; Hip-Hop, Friendship &amp; Community, Money &amp; Class</t>
+  </si>
+  <si>
+    <t>Aging &amp; Personal Growth, Work &amp; Ambition, Creativity &amp; Art</t>
+  </si>
+  <si>
+    <t>Aging &amp; Personal Growth, Relationships &amp; Family, Technology &amp; Internet Culture</t>
+  </si>
+  <si>
+    <t>Sports &amp; Athletics, Movies &amp; Cinema</t>
+  </si>
+  <si>
+    <t>Technology &amp; Internet Culture, Social Norms &amp; Etiquette, Movies &amp; Cinema</t>
+  </si>
+  <si>
+    <t>Food &amp; Lifestyle, Relationships &amp; Family, Money &amp; Class, Technology &amp; Internet Culture</t>
+  </si>
+  <si>
+    <t>Music &amp; Hip-Hop, Aging &amp; Personal Growth</t>
+  </si>
+  <si>
+    <t>Social Norms &amp; Etiquette, Money &amp; Class, Technology &amp; Internet Culture, Work &amp; Ambition</t>
+  </si>
+  <si>
+    <t>Friendship &amp; Community, Aging &amp; Personal Growth, Social Norms &amp; Etiquette</t>
+  </si>
+  <si>
+    <t>Creativity &amp; Art, Aging &amp; Personal Growth, Relationships &amp; Family, Social Norms &amp; Etiquette</t>
+  </si>
+  <si>
+    <t>Creativity &amp; Art, Aging &amp; Personal Growth, Work &amp; Ambition</t>
+  </si>
+  <si>
+    <t>Technology &amp; Internet Culture, Money &amp; Class, Aging &amp; Personal Growth</t>
+  </si>
+  <si>
+    <t>Friendship &amp; Community, Technology &amp; Internet Culture, Sports &amp; Athletics, Food &amp; Lifestyle</t>
+  </si>
+  <si>
+    <t>Music &amp; Hip-Hop, Movies &amp; Cinema, Technology &amp; Internet Culture, Relationships &amp; Family</t>
+  </si>
+  <si>
+    <t>Money &amp; Class, Sports &amp; Athletics, Music &amp; Hip-Hop, Technology &amp; Internet Culture</t>
+  </si>
+  <si>
+    <t>Social Norms &amp; Etiquette, Aging &amp; Personal Growth, Relationships &amp; Family, Movies &amp; Cinema</t>
+  </si>
+  <si>
+    <t>Aging &amp; Personal Growth, Relationships &amp; Family, Movies &amp; Cinema, Food &amp; Lifestyle</t>
+  </si>
+  <si>
+    <t>Aging &amp; Personal Growth, Technology &amp; Internet Culture, Work &amp; Ambition, Movies &amp; Cinema</t>
+  </si>
+  <si>
+    <t>Technology &amp; Internet Culture, Aging &amp; Personal Growth, Movies &amp; Cinema, Money &amp; Class</t>
+  </si>
+  <si>
+    <t>Aging &amp; Personal Growth, Work &amp; Ambition, Creativity &amp; Art, Technology &amp; Internet Culture</t>
+  </si>
+  <si>
+    <t>Relationships &amp; Family, Friendship &amp; Community, Creativity &amp; Art, Technology &amp; Internet Culture</t>
+  </si>
+  <si>
+    <t>Food &amp; Lifestyle, Aging &amp; Personal Growth, Technology &amp; Internet Culture, Creativity &amp; Art</t>
+  </si>
+  <si>
+    <t>Movies &amp; Cinema, Social Norms &amp; Etiquette, Technology &amp; Internet Culture, Money &amp; Class</t>
   </si>
 </sst>
 </file>
@@ -10722,7 +10722,7 @@
         <v>157</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -10742,7 +10742,7 @@
         <v>146</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -10762,7 +10762,7 @@
         <v>147</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -10782,7 +10782,7 @@
         <v>148</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -10802,7 +10802,7 @@
         <v>158</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -10822,7 +10822,7 @@
         <v>159</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -10842,7 +10842,7 @@
         <v>177</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -10862,7 +10862,7 @@
         <v>160</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -10882,7 +10882,7 @@
         <v>161</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -10902,7 +10902,7 @@
         <v>162</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -10922,7 +10922,7 @@
         <v>163</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -10942,7 +10942,7 @@
         <v>164</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -10962,7 +10962,7 @@
         <v>165</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11018,7 +11018,7 @@
         <v>149</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11038,7 +11038,7 @@
         <v>166</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11058,7 +11058,7 @@
         <v>167</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11078,7 +11078,7 @@
         <v>168</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11116,7 +11116,7 @@
         <v>169</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11136,7 +11136,7 @@
         <v>170</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11156,7 +11156,7 @@
         <v>150</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11194,7 +11194,7 @@
         <v>171</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11232,7 +11232,7 @@
         <v>151</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11252,7 +11252,7 @@
         <v>152</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11272,7 +11272,7 @@
         <v>172</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11292,7 +11292,7 @@
         <v>153</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11312,7 +11312,7 @@
         <v>154</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11332,7 +11332,7 @@
         <v>155</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -11352,7 +11352,7 @@
         <v>173</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>311</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64D1AE8-CEC5-41F6-A66D-AB80611B8E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276B2435-B7E0-4F7E-9AFD-DBC9A0D41D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Transcripts!$A$1:$D$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WOOM Archive'!$A$1:$E$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WOOM Archive'!$A$1:$F$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -10353,10 +10353,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -11528,7 +11524,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E42" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}"/>
+  <autoFilter ref="A1:F43" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}"/>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" xr:uid="{B375DB27-E1B7-490E-9D8C-9444D796161B}"/>
   </hyperlinks>

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276B2435-B7E0-4F7E-9AFD-DBC9A0D41D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A29D34A-E678-47CA-B718-263287902338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="322">
   <si>
     <t>youtube_link</t>
   </si>
@@ -10219,6 +10219,9 @@
   <si>
     <t>Movies &amp; Cinema, Social Norms &amp; Etiquette, Technology &amp; Internet Culture, Money &amp; Class</t>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=pRj-ktSar14&amp;t=5s</t>
+  </si>
 </sst>
 </file>
 
@@ -11484,7 +11487,9 @@
       <c r="D41" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="E41" s="5"/>
+      <c r="E41" s="5" t="s">
+        <v>321</v>
+      </c>
       <c r="F41" s="11" t="s">
         <v>318</v>
       </c>

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A29D34A-E678-47CA-B718-263287902338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07848CE-0584-4F40-802F-59E6433A3BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="321">
   <si>
     <t>youtube_link</t>
   </si>
@@ -10219,9 +10219,6 @@
   <si>
     <t>Movies &amp; Cinema, Social Norms &amp; Etiquette, Technology &amp; Internet Culture, Money &amp; Class</t>
   </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=pRj-ktSar14&amp;t=5s</t>
-  </si>
 </sst>
 </file>
 
@@ -11487,9 +11484,7 @@
       <c r="D41" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>321</v>
-      </c>
+      <c r="E41" s="5"/>
       <c r="F41" s="11" t="s">
         <v>318</v>
       </c>

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07848CE-0584-4F40-802F-59E6433A3BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDBBDDE-2E8F-42C4-A689-AF62E15E8DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="322">
   <si>
     <t>youtube_link</t>
   </si>
@@ -10219,6 +10219,9 @@
   <si>
     <t>Movies &amp; Cinema, Social Norms &amp; Etiquette, Technology &amp; Internet Culture, Money &amp; Class</t>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=pRj-ktSar14&amp;t=5s</t>
+  </si>
 </sst>
 </file>
 
@@ -10308,7 +10311,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10335,6 +10338,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -11484,7 +11488,9 @@
       <c r="D41" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="E41" s="5"/>
+      <c r="E41" s="12" t="s">
+        <v>321</v>
+      </c>
       <c r="F41" s="11" t="s">
         <v>318</v>
       </c>

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDBBDDE-2E8F-42C4-A689-AF62E15E8DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE84045-90F6-4485-8704-D59E249E1137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="327">
   <si>
     <t>youtube_link</t>
   </si>
@@ -10222,6 +10222,326 @@
   <si>
     <t>https://www.youtube.com/watch?v=pRj-ktSar14&amp;t=5s</t>
   </si>
+  <si>
+    <t>TV Rankings, Body Image, and Modern Miracles</t>
+  </si>
+  <si>
+    <t>09.29.26</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Topics Covered&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Ranking favorite 21st-century television shows and debating what those choices reveal about personality and taste.&lt;/li&gt;
+    &lt;li&gt;Psych, The Wire, Breaking Bad, Insecure, Game of Thrones, The Americans, Mad Men, Dexter, and other all-time favorites.&lt;/li&gt;
+    &lt;li&gt;Why shows released after monoculture fractured may never receive the recognition earlier hits enjoyed.&lt;/li&gt;
+    &lt;li&gt;Which acclaimed series are overrated, underrated, or simply designed for a different audience.&lt;/li&gt;
+    &lt;li&gt;Why landing a television finale is difficult and whether an ending needs to be happy, realistic, or merely well written.&lt;/li&gt;
+    &lt;li&gt;Six Feet Under, The Americans, and The Big Bang Theory as examples of memorable finales.&lt;/li&gt;
+    &lt;li&gt;What went wrong with Game of Thrones, including rushed pacing, abandoned character arcs, and increasingly weak writing.&lt;/li&gt;
+    &lt;li&gt;Sylvester Stallone discussing steroids, eating disorders, stunt injuries, and the body-image cost of playing Rocky and Rambo.&lt;/li&gt;
+    &lt;li&gt;Male body-image pressure, enhanced Hollywood physiques, social-media fitness culture, and unrealistic expectations.&lt;/li&gt;
+    &lt;li&gt;Aging, celebrity criticism, and the backlash directed at Jasmine Guy and other performers for looking their age.&lt;/li&gt;
+    &lt;li&gt;Height expectations, dating preferences, and the appearance standards men cannot naturally change.&lt;/li&gt;
+    &lt;li&gt;A medical procedure that uses tooth tissue to help restore vision.&lt;/li&gt;
+    &lt;li&gt;Cancer-treatment progress, targeted therapies, and the value of extending quality years even without a universal cure.&lt;/li&gt;
+    &lt;li&gt;Nintendo 64 turning 30 and its influence on modern gaming.&lt;/li&gt;
+    &lt;li&gt;Jordan’s first business trip, per diem lessons, and family members worrying that unfamiliar jobs may be pyramid schemes.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Questions&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;What does your top-10 television list say about you?&lt;/li&gt;
+    &lt;li&gt;Which show deserves a much larger audience than it received?&lt;/li&gt;
+    &lt;li&gt;What is the greatest television finale of all time?&lt;/li&gt;
+    &lt;li&gt;Do fairytale endings matter, or does an ending only need to make sense?&lt;/li&gt;
+    &lt;li&gt;What exactly went wrong with Game of Thrones?&lt;/li&gt;
+    &lt;li&gt;Which popular show do you simply not understand the hype around?&lt;/li&gt;
+    &lt;li&gt;Are modern male body-image expectations becoming unrealistic?&lt;/li&gt;
+    &lt;li&gt;How much of online fitness culture is staged, enhanced, or misleading?&lt;/li&gt;
+    &lt;li&gt;Are short men judged unfairly in modern dating?&lt;/li&gt;
+    &lt;li&gt;What medical advancement have you recently found fascinating?&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Observations&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Some great shows missed the monoculture era and therefore never became universally recognized classics.&lt;/li&gt;
+    &lt;li&gt;Limited series and one-season productions should be judged differently from shows that sustain stories across many years.&lt;/li&gt;
+    &lt;li&gt;Great finales are rare because writers often know how to start a story but struggle to land the plane.&lt;/li&gt;
+    &lt;li&gt;Audiences can accept an unhappy ending when the writing remains consistent with the characters.&lt;/li&gt;
+    &lt;li&gt;The actors who established male body ideals often suffered from the same body-image pressures themselves.&lt;/li&gt;
+    &lt;li&gt;Many social-media physiques are influenced by steroids, lighting, camera quality, angles, and post-workout pumps.&lt;/li&gt;
+    &lt;li&gt;People compare ordinary bodies to images created by an entire industry designed to make bodies look exceptional.&lt;/li&gt;
+    &lt;li&gt;Aging is natural, but the internet increasingly treats visible aging as failure.&lt;/li&gt;
+    &lt;li&gt;Medical progress should also be measured in additional healthy years, birthdays, and family milestones.&lt;/li&gt;
+    &lt;li&gt;Entertainment rankings stop being fun when viewers treat personal taste as proof of intelligence.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Debate&lt;/h3&gt;
+  &lt;p&gt;Are modern male body-image expectations becoming as unrealistic as those historically imposed on women? Jordan argued that men increasingly face pressure around height, physique, and features that cannot always be changed naturally. Darius emphasized how Hollywood, steroids, fitness influencers, camera techniques, and social media create impossible standards for younger men. Both agreed that much of what audiences see online is not an honest representation of reality.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Television&lt;/li&gt;
+      &lt;li&gt;Storytelling&lt;/li&gt;
+      &lt;li&gt;Series Finales&lt;/li&gt;
+      &lt;li&gt;Monoculture&lt;/li&gt;
+      &lt;li&gt;Pop Culture&lt;/li&gt;
+      &lt;li&gt;Body Image&lt;/li&gt;
+      &lt;li&gt;Social Media&lt;/li&gt;
+      &lt;li&gt;Fitness Culture&lt;/li&gt;
+      &lt;li&gt;Steroids&lt;/li&gt;
+      &lt;li&gt;Aging&lt;/li&gt;
+      &lt;li&gt;Dating&lt;/li&gt;
+      &lt;li&gt;Masculinity&lt;/li&gt;
+      &lt;li&gt;Hollywood&lt;/li&gt;
+      &lt;li&gt;Medical Innovation&lt;/li&gt;
+      &lt;li&gt;Cancer Research&lt;/li&gt;
+      &lt;li&gt;Technology&lt;/li&gt;
+      &lt;li&gt;Video Games&lt;/li&gt;
+      &lt;li&gt;Career Growth&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>Movies &amp; Cinema, Technology &amp; Internet Culture, Aging &amp; Personal Growth, Social Norms &amp; Etiquette</t>
+  </si>
+  <si>
+    <t>Transcript
+00:00:01 Jordan
+I would like to apologize for my video quality, guys. The lighting in this room is not great. I'm on the road for a business trip. And I've been ripping around all day for work. And like I literally got into me, I was like, where are you?
+00:00:11 Darius
+Go ahead, brush your shoulders off, man. We, you a big dog now, you on business trips?
+00:00:15 Jordan
+Yeah, I'm on business trips. She don't want a puppy, she want a big dog.
+00:00:21 Darius
+Go ahead and brush your shoulders off for the people, man. Congratulations. Welcome to Out the Trunk with Jordan and Darius. My name is Darius. That's Steve's all up in the area on all socials.
+00:00:31 Jordan
+And I'm Jordan. Is Jordan to be riding on all socials?
+00:00:34 Darius
+This is our What's On Our Minds segment, our weekly conversation about what's on our mind, what we've seen on the internet, what's going on. And I'd start with the viral New York Times top 10 TV shows thing that literally everyone has done. And so I figured it was a good way to start off a conversation with the quick talking points. So we're going to put our top 10 list on the screen here for the audience to follow along. So what were your top 10, man? Top 10. Keep in mind, it's the 21st century listeners. So Martin and Living Single and Seinfeld and Friends. Yes, that 21st Friends.
+00:01:11 Jordan
+None of those are available. It was all after the year 2000 guys. We are not stupid.
+00:01:16 Darius
+Yes. Just, you know, Sopranos started in 99, Sex and the City started in the late nineties. Yeah. So correct. With that being said, what were your top ten?
+00:01:30 Jordan
+All right. So my top ten are. Did you rank yours or you just went? I just went. OK, cool. OK, so my top ten is Psych, The Big Bang Theory, the US Office version or the Office US version of The Office. How to Get Away with Murder, Game of Thrones, How I Met Your Mother, Insecure, Modern Family, Scandal, and Dexter.
+00:01:55 Darius
+All right, we had two overlaps.
+00:01:58 Jordan
+Okay.
+00:02:01 Darius
+I went with The Shield, Criminally Underrated, Breaking Bad, Insecure, Game of Thrones, The Americans, The Wire, House MD, Mad Men, 24, and six feet under another currently in underrated TV show. So what was what was your favorite one?
+00:02:25 Jordan
+Oh, that's tough. My favorite of these shows. Hmm. I'd have to go with stuff because there's like five I can look that I can make a case for. I'd say my favorite. I'm going to go with Psych. It's funny, it's innovative, it's got serious and heartfelt moments. It's a murder mystery, which I love. It's got kind of a Sherlock Holmes, Dr. Watson feel, the dynamic between Dulay Hill and James Rodriguez. One of the great one-two punches of all time in sitcom history, if you ask me. The running gags on the show are legendary. They're super unique. Instead of saying like, don't be ridiculous, they'd say like, don't be, and then something crazily ridiculous, like don't be Beverly Hills Cop 3 or something like, **** like that. Like it was always really cool, unique and funny. Yeah, that's probably my favorite show. I've rewatched it the most. And yeah, just it's one of those shows where you hope you love the show so much. You hope the cast are still friends after the show's done.
+00:03:27 Darius
+Yeah.
+00:03:27 Jordan
+And they actually are all still friends.
+00:03:30 Darius
+What do you think your top 10 list says about you?
+00:03:34 Jordan
+Oh, that's a good question. It says I have a pretty eclectic taste in entertainment, for sure. I love comedy. There's that thing that most serial killers are Virgos. I'm not big into the signs, but my favorite shows in here would not debunk that theory. I'll put it like that. I do have a fascination with crime and true crime and stuff like that. Hence, you know, Dexter, Scandal, How to Get Away with Murder, for sure, and obviously Game of Thrones, there's murder, that's the whole show. I think the my slate of shows shows that I do. I love ensembles. So I love shows that are centered around friendship and great cast, great chemistry. All these shows have great character development, like extremely well done character arcs. So I love a good story. I mean, it sounds cliche, but I do genuinely love a good story. I think it says I'm a pretty complex individual, so I'm drawn to complex characters.
+00:04:39 Darius
+Okay. I'm blanking on a question. You have any questions for me?
+00:04:50 Jordan
+Same question. I mean, I know it's not creative to ask it back, but that is I do. I was wondering, like, what does what do your show say about you?
+00:05:00 Darius
+I lack for whimsy, that's for certain. Every last one of these shows is very serious and very dark. Certainly could use a little, is it levity or no, brevity is short. Levity, I think is.
+00:05:13 Jordan
+Levity is like, that's what I was looking for.
+00:05:15 Darius
+Yeah, yeah, you know, I mean, House MD, you know, there was some comedy in there despite, you know, the, yeah, there's not, Insecure had some comedy, but no, there's no like straightforward comedy in here at all. And so my favorite is The Liar. That's the greatest show of all time. That's not even really, most people wouldn't even debate that. And so you almost have to start with what's #2 and then probably Mad Men. Yeah, I would go Mad Men.
+00:05:50 Jordan
+I'm not going to say it on this pod.
+00:05:51 Darius
+What did you say?
+00:05:52 Jordan
+It was a joke that I wouldn't say so bad, but I'm not going to say it on this pod.
+00:05:56 Darius
+I don't know.
+00:05:57 Jordan
+It circles back to our conversation Saturday night at the bar.
+00:06:05 Darius
+Okay, fair enough. No, yeah, certainly lacking for some levity. But you know, a top 10 can only have 10. But no, I don't really watch a lot of comedies. Even to the extent that I do, they're all from the 90s. And like we said, they don't count here. Right. But even then, like, I almost put sitcoms in a different thing than like, okay, drama. Like to me, like, I don't mean this. There's no way to say this. Like, these are like the grown up shows and like sitcoms are like for a different mindset. And so I would put those. It's almost like they like the list bothers me.
+00:06:47 Jordan
+They're low stakes.
+00:06:49 Darius
+Yeah, it doesn't let bother me for a few things. It's like it had a couple of one season shows on there and I just don't think I talked. Yep. Like Station 11 was an amazing show, but like how many great shows? How many good shows would be great if they can densed it all down to 10 hours, you know, like it's.
+00:07:08 Jordan
+Every show would be the best show ever.
+00:07:09 Darius
+Yeah, Chernobyl, Station 11, Watchmen, like they did. It's just, they're just doing two different things, you know, Correct.
+00:07:19 Jordan
+It's funny you bring that up because I was going to put American Crime Story because they do the monster series, like the serial killer series. They did one on, what's his name? Ed Negan. I can't forget his name. They did one on Jeffrey Dahmer. That was really, really good. And then there was, they did the OJ story as well as the assassination of Versace. And those two seasons were otherworldly. They were incredible. But I was like, they each came up as their own separate show. So I was like, I'm not gonna, I'm not gonna do that.
+00:07:49 Darius
+It's cheating. I just think that, you know, how many shows like Lost came out and like, but if you, if Lost was able to just do three seasons, it would just be so much better than if it's had spin its wheel for six seasons. So let me ask you this. If the one show on your list that you feel like not enough people have seen and if you could make everybody watch it, what would it be?
+00:08:17 Jordan
+Okay. I feel these are pretty mainstream shows. I'd either have to go with Psych or Dexter because so Psych was on US. It was just not a huge network. It's basic cable, you know, so that I don't know how many people saw it. It kind of feels like one of those shows that like you love that you don't know if anyone else has seen really, I feel.
+00:08:40 Darius
+Like most people know that as a show that came on after Suits. I don't really think a lot of people. Right, exactly.
+00:08:45 Jordan
+Yeah.
+00:08:46 Darius
+That's what I know. I was Googling it when you said it.
+00:08:49 Jordan
+Cause like growing up, it was, it was, you know, it was Suits, it was Monk, and it was, it was Psych. And I feel like it was kind of sandwiched in between those two shows. So I don't know. It has a huge following, of course, but I don't, I feel like it never got the full, you know, appreciation that it deserved or recognition that it deserved. I'd say Dexter too. Like Dexter was a ******* phenomenal show. It was really funny, really dark. It was a great character study. It kind of it sort of preceded a lot of the true crime stuff we watch nowadays, you know, with like the confession tapes that Netflix does and all that kind of stuff. So I'd say Dexter and Psych for sure.
+00:09:26 Darius
+Okay. For me, That's a tough to pick one. But if I had to pick one, it would be the Americans. It's a close, but I would go with the Americans because I believe that that show came out after monoculture. Like all the other shows on my list came out when we all watched the same thing. And now everyone's attention is fractured. And I just feel like if the Americans had come out five years earlier, it would be considered a Pantheon show. two under deep cover Russian spies living in DC and they just go out on spy missions. And it's really honestly about it's a family show. It's about them raising kids as spies. And I just feel like that's one of the best shows ever. And it's never going to be considered that because, you know, it came out after everyone's attention fractured. Yeah. So yeah, that one. And then If I had to pick a #2, it would be 6 feet under. HBO show came out in the early 2000s before everybody had HBO. So I think a lot of people just finished that one. Basically, it's a family owned funeral home and each episode starts with the death and like they're charged with like getting the body ready for the funeral. But the show is really about the family and managing the business. Okay. And so, you know, there's The dad dies in the first episode, spoiler alert. So the sons have to run the business and you're dealing with the, mom, the widow's grief and the daughter growing up and then the two sons trying to run a business that, they may not, it may not have been what they wanted to do with their lives. So that one would be #2 on the list. And it honestly, it had the greatest season series finale ever. It went off the air 20 years ago, so I can spoil it. Basically, Because every episode of the show starts with a death. The last montage is how all the main characters died in their lives. So it was like, oh, you see one of the characters, actually a dude from Dexter. This was the show he did before that, Michael Hall.
+00:11:38 Jordan
+Oh, okay.
+00:11:39 Darius
+And so that's how I got Dexter, basically. More or less, yeah. And so like, basically the daughter who's the youngest is like driving down the road and it's just a montage of flash forwards of how all the characters end up dying. And so, the Dexter character, he was gay in the show, but his boyfriend then husband was like, they flash forward to him. He's a cop in the show, but fast forward to him in the future. And he's like an elderly man working security and someone like robs his Brinks truck and kills him. And then you see his name and his that he died. And then it goes to Michael C. Hall. And one of the coolest moments of the show is his last moments, he just had like a picnic with his family. And like his last moments of live alive is he sees his husband, like young and youthful one last time, and then he collapsed and dies. And like, this is all the final montage of the show because a big part of the writing of the show was them navigating being like just gay dudes. And, you know, this is the early 2000s. And getting married and, the, just like any relationship, them getting married, him coming out to his mom, do they want kids, so on and so forth. And him being a cop and all that goes into that hyper masculine workforce. And so, I thought it's really touching when you see that final montage and you see like, you know, he sees his husband who died 10 years ago, based when you do the math, young and youthful one last time. And so I thought that to me, that's like the, When people talk about great endings, you always see Six Feet Under up there because it's hard to land the plane. I don't rate, I don't judge people for bad endings. I think it's just really hard to land the plane, but this one did it well.
+00:13:28 Jordan
+Okay, you actually pivoted right into my next question. I was gonna ask you, what's your favorite finale of your favorite shows?
+00:13:36 Darius
+If I exclude Six Feet Under, Man, that's tough. Let's get the bad ones out. The wires ending was not great. Breaking Bad. I could take it or leave it. Insecures was cool. Game of Thrones is not great. So we're really dealing with the shield, the Americans and six feet under. I'm going to go with the Americans because spoiler alert, the second to last episode, their cover gets blown. And then the last episode is them being extra. No, because that's when you get that's when you're exfiltrated. That's what we're looking for. And so there's so they have two children who are Americans born here. Their daughter knew about them being spies and was like training for it. And their son had no idea. And so they're on the run on the last episode and they call their son one last time. They bring in their daughter back to Russia and they call their son one last time. And, they can't tell him because, every phone's tapped at this point. And so they just say, right, that's emotional. And then they get on the train where they're going to Montreal and they're checking for passports and the train takes off because they're all sitting separately because they're undercover trying to get out. And the train takes off and you see Elizabeth look out the window and their daughter had got off the train and stayed behind. And so they were stuck going to Russia without their children, either of their children. And so That's up there. And with the, with, yeah, if I took six feet under off, that would be my favorite ending. How about you?
+00:15:18 Jordan
+I'm gonna go. A lot of these did not have.
+00:15:28 Darius
+It's hard.
+00:15:29 Jordan
+It is, it is. It really, it's really hard. It's almost like the better the show, the worse the ending because it's just, it's so difficult. And plus you never know when your show's gonna end, you don't have a set. You know what I mean?
+00:15:40 Darius
+That's why movies are better because you have a beginning, middle, and end when you start. And so.
+00:15:44 Jordan
+Correct. I'm going to go with, you know, How to Get Away with Murder has a beautiful ending for Annalise, not so much for everybody else. It's a show called Hacking with Murder, so I, but I'm gonna go with the Big Bang Theory. I think they really nailed that ending.
+00:16:06 Darius
+That's a good one.
+00:16:06 Jordan
+That's one of the few phonalysis. I'm gonna hold you like that one brought me to tears, man. Like Sheldon's speech at the end where he finally recognized the toll he took on everyone in his life and the price they paid for him to get to where he was. Him acknowledging that Howard is an astronaut, you know, him shouting out Penny and Leonard's pregnancy and saying that the first day that we met, he said, our kids will be beautiful and smart. And he said, I have no doubt that they will be. That callback to episode one was amazing. Amy finally holding him accountable for being selfish and being an *** because she just called him a lot, I felt like. Leonard getting to slap Sheldon, one of the greatest moments in the history of the show for me. They won the Nobel Prize, of course, they beat up the hacks who tried to rob him of the award. I just wish, Linda and Penny having a kid, I just really wish that they had given Raj a better ending. I hated that he still ended the show with nobody and just no, like, he ended the show the same way he started the show. You know, he had an arc, of course, he learned how to speak and all that stuff. He got more confident, but still, I just hated that he didn't get a fairytale ending as well. But I'd say the big man through, they stuck the landing on that ending for sure.
+00:17:18 Darius
+Do fairytale endings matter?
+00:17:24 Jordan
+Only in this situation, because everyone else got a fairy tale ending but him.
+00:17:28 Darius
+I. I don't wait for happy endings. I just want a good ending and a realistic.
+00:17:35 Jordan
+I feel you. But it was a great ending. It was a great ending.
+00:17:40 Darius
+Yeah, I did enjoy the and then they you know, they're eating Chinese food and like the it's an acapella version of the intro song. I thought that was pretty dope. But that show had, to me, fallen off in those last couple of seasons. So I kind of just hopped on YouTube and watched the ending.
+00:17:56 Jordan
+I hear you. So if you ever get a chance, go on YouTube and watch the table read of the final episode. Man, that heartbreak, like emotional damage, like that **** hurt.
+00:18:11 Darius
+Were they crying because the show was ending or crying because they were making $1,000,000 an episode and now they got to go back to the real world?
+00:18:18 Jordan
+Probably both.
+00:18:21 Darius
+Old girl hosted Jeopardy for like 6 weeks. I haven't heard from anybody since.
+00:18:24 Jordan
+Yeah, I'm trying to think of any of them who, I mean, Jim Parsons won the lottery, though, because he produced Young Sheldon, and that show ran for seven or eight years. And then there's George and Mandy's first marriage, whatever the show's called, and that's still running. So he's eating off Sheldon forever, basically.
+00:18:45 Darius
+I mean, he was the star of the show, so true for sure.
+00:18:48 Jordan
+Yeah.
+00:18:50 Darius
+So we both have Game of Thrones on the list. Yeah, we both have our objections for the ending. But I often hear people complain about the ending, but I never hear them say what they didn't like about it. So I'm asking you, what about the Game of Thrones ending? Did you not like table stakes off the top? We know it was super sped up. So right. What is it about you that you didn't like?
+00:19:16 Jordan
+I feel like they wasted the secret of Jon's heritage. I think I hated that they completely wasted four seasons of Jaime Lannister's character arc. Like they just for him to just go right back to Ceresi. What was the point of any of this? I hated that Ceresi got like a quick and painless death. She deserved a far more gruesome death. To me, that was my biggest issue with the finale. I mean, Bran being king, do we even need to talk about that? I feel like, okay, so you don't like Franklin's ending in Snowfall, but in general, I do feel like he would have found some way to have some sort of decent life after it all went to hell, or had some sort of failsafe, some sort of ace up his sleeve. And I feel like the same way for Tyrion in Thrones where he just did all that to end up like it just didn't make sense to me. I just feel like he was way too smart to end up how he ended up plus a nervous character like a ************ at the last like two seasons and he threw various under the bus. I didn't like that either.
+00:20:25 Darius
+He ended up handed the king of Westeros though. I don't know.
+00:20:27 Jordan
+I mean, well, you know what, that's fair. That's fair. You're right. You're right. But I just, what they did with him that whole ending season, I hated.
+00:20:35 Darius
+No, I mean, it is. I watched rewatch Game of Thrones this summer. It was my summer rewatch. And yeah, I'm a bit of a of a truther on the ending. Like, I think season seven was fine. Just a little sped up.
+00:20:49 Jordan
+Same.
+00:20:49 Darius
+I remember season eight. I was like, okay, I can't defend this.
+00:20:52 Jordan
+No. Yeah, it was. It was like somebody said all of Jon Snow's lines in season eight was She's my queen.
+00:21:00 Darius
+Yeah, it's just like. It's like when you. Like you start a podcast or something and you like 10 minutes later, you're like, What? I don't. Oh, I actually made it three x. Like, you just like you, like, hit the button and it just it is. It is jarring. I don't. Yeah, I don't have a problem where people ended up. Jamie returning to Cersei felt true to the character to me. That's fair. Like, I don't. I don't need emotionally satisfying endings as long as like the writing makes sense. It makes sense. So I don't think Cersei dying in a pile of rubble. I don't know. I don't think that'd be a pleasant experience. But I do like Daenerys burning down the castle. I was cool with that.
+00:22:02 Jordan
+Looking back, I was cool with that.
+00:22:03 Darius
+Yeah, it just.
+00:22:04 Jordan
+That was your friend's dying wish.
+00:22:06 Darius
+The problem is that, yeah, they beheaded her best friend in front of her. Yeah. She lost the dude with the scaly skin, Jorah.
+00:22:19 Jordan
+Jorah Mormont.
+00:22:22 Darius
+No, I mean, she had they had been hinting at it. just was way too fast. And ultimately what ****** me off about the show, the ending was that when Daenerys set sail for Westeros. No, Westeros was the whole thing, right? Yeah, I think it was Westeros. When Daenerys set sails for Westeros, she has three full, fully grown dragons, all the smartest advisors, the Dothraki, the Unsullied. And there's nothing to do, but just have her run. Like she shows up, it's over, the show's over. And so like, they kept coming up with like increasingly absurd reasons why she wouldn't just use the dragons and win. Correct. And it just got dumber and dumber and dumber. And like Tyrion would give her bad advice and it would blow up in her face and then she'd be starting like, he would be like, oh, let's do this. And then like the boats would get destroyed and then they would lose. the Greyjoy girl and then it would just be like You have three drag like this is like there's a reason why Spin those are Gary's ruled for hundreds of years and it's because once you have dragons the game is over and so You know it just got really really stupid and I can forgive anything but stupid writing and so That's why I left snowfall because I just felt like The police only mattered when the plot needed them to. They only existed when the plot needed them to. Right. So I just was just like, this is stupid. Like when you watch a show like The Wire, like even when you pivot to the drug dealers, the concern about police wasn't ever like ever. It was always there even when they were like, you know, that's part of it. And then you're watching Franklin like do, you know, multimillion dollar kilo exchanges in parks in broad daylight, killing people in broad daylight?
+00:24:17 Jordan
+Dumping them in canyons and broad tail light.
+00:24:19 Darius
+And then he like, they kill Man Boy and he's like, call the police and tell them he tried to jump you. But that doesn't explain like the three gang members that Jerome and D-Ray just murdered in the parking lot. And I'm just like, it just got too stupid. It did.
+00:24:36 Jordan
+And you know, and my biggest thing too is, and this is just like chest move **** not in real life, but just chest move **** in that world, okay? Why the **** did he not kill Louis? Franklin was too smart to have let Louis live. She was by far the biggest liability to the empire. She wanted the throne and you cannot have someone like that around. You have to kill them. I don't know why he didn't do that.
+00:24:58 Darius
+Someone made the good point. They feel like this show is set in 1986, I think. But Louis is written like a 2026 like feminist character. And a woman in the drug trade in 86 just It just wouldn't be that bad. Would it move that way? Yeah, you know, she wouldn't like it would just it felt very much like it wouldn't be that stupid. Yeah, it just felt very much written like a modern woman, you know, you know, I mean, I guess I get, you know, it's possible. It is possible. She was very smart. But it just felt a bit like, you know, like, like some some of the most annoying parts of Twitter wrote her character.
+00:25:39 Jordan
+She was like, it was like they took Shiv from succession and put her in that world. Like that's kind of what her character was. Like she was, I had the killer mentality. She was smart and cunning and all that. But you got every, you ruined everything because you wanted to be the guy. It's like what we talked about with Draymond versus Barkley. You know, you say you want to win, but you're not willing to sacrifice for the good of the team. And that's why the team lost.
+00:26:05 Darius
+And she's making a lot of money. It wasn't like she was broke. So last question on this and then we'll get out of here. What's one show you saw on everyone's list that you were just like, I don't get it.
+00:26:18 Jordan
+Let's see. Let me look here. Pull the list back up. There was a few. I was also more surprised by some of the shows that weren't on the list too. Let me see. Well, I'm scrolling for that. I meant to ask you. Did you see that debate that Bamani had with that guy on that podcast with Trey Jones?
+00:26:37 Darius
+No, there's too many hot mics. I turned that **** off after like 10 seconds.
+00:26:41 Jordan
+So they were talking and he was talking about The Wire and the guy was talking about what Sopranos, he said Sopranos is better because Sopranos had more character development or like, oh, the characters more, yeah, the characters more developed and more interesting than The Wire. And I just thought that was insane. It's reminded was like every character in Sopranos is just dumb. He's like, you're telling me that Omar had no had no depth. Like, you know what I mean? Like, it was just insane. I couldn't figure out if the guy just like, how do I put this without? It felt like he couldn't see the depth. And I don't know if because he wasn't looking for it or because he didn't expect depth to come from those characters.
+00:27:27 Darius
+Yeah, I mean, I thought the Sopranos was fine. That's, it wouldn't have made my top 10, even if it was eligible. Yeah, look, I mean, you're not gonna give me to say anything about the Wire. It's the greatest show of all time. And I tried to get away, like I saw some people it's a litmus test for how, I try to get a, I tweeted something like, y'all ain't going to be start calling people stupid over ranking TV shows. Can we be like, can we just, can something just be fun?
+00:27:56 Jordan
+Like it's supposed to be fun, guys.
+00:27:58 Darius
+It's just supposed to be fun, man. Like, we like, you know, you're not intelligent. Cause you know, it's like, all right guys, can we just, we're just ranking TV shows. Ain't none of us getting royalty checks. We ain't write none of this ****. That's also the question was like, cause Breaking Bad was #1. And it's like, would Breaking Bad be my number one? No. But like, it's not like they put Ozark at #1. Like Breaking Bad is a worthy option. It's just, I don't, I wouldn't have it there. It's like, I don't, you know, but to answer the question, I think The Wire is just, it's not a show for someone who just, you know, wants to, who's used to Netflix TV. As I'll put it that way. And so that's what I got. As nice as I could put it without calling people stupid in the name of a damn TV show ranking list. Can something just be fun that we just talk, shoot ****? Like can something just be the thing we do and we still be doing something at work? Like can we just ********?
+00:28:56 Jordan
+No, yeah, it's supposed to be water cooler talk. That's really all this is water cooler talk. It's not supposed to be, you know, some divisive thing.
+00:29:06 Darius
+I saw one person was like, Breaking Bad is a certain type of white blogger's dream because they think that they could be a chemist, they could sell. I was like, dude, can we just, can we be like.
+00:29:16 Jordan
+No, it's not supposed to be.
+00:29:17 Darius
+It's not that deep, man.
+00:29:19 Jordan
+Come on, guys. It's not that, it's not, and at no point is race a factor in that show either, you know?
+00:29:24 Darius
+No, man. It's just, a lot of Mexicans in that show. It's not, it's diverse. It's just, there's no black people. You just.
+00:29:31 Jordan
+Correct. Which, why would we be in New Mexico? So that's realistic to me.
+00:29:36 Darius
+Also, it's childish to not watch anything that doesn't, you can't see yourself in. That's a very dry way to look at the world. But let's get back to the question. What's a show that's on a lot of people's list that you were just like, I don't get it.
+00:29:50 Jordan
+Okay, yeah, I'd say, you know, this show, it just wasn't for me. I'm gonna go with Girls, The Leland Dunham Show. Yeah, it just wasn't for me. I'm not the demographic. I'm not saying it's not a great show, a good show. I just, it wasn't for me. So I don't know how it got that high, I guess.
+00:30:17 Darius
+I have not watched any of it. I can just look at it and tell it's not for me. Two men, you mentioned it. That's what made me think of the question. Succession, don't get it. Paradise, don't get it. I just I've tried with Paradise.
+00:30:32 Jordan
+I put on the list.
+00:30:33 Darius
+Yeah. Wasn't into that succession. I was like, I feel like it's on HBO and it looks like a prestige show. So everyone just kind of made it one and I just wasn't into it. But I liked it.
+00:30:47 Jordan
+I just never finished. It's fun and it's got some of the the ruthlessness of the shows we do like from HBO. And I think that's part of what people kind of clung to, you know? And it came along right after Game of Thrones. And I think people were just missing that Sunday night. HBO Phenom.
+00:31:05 Darius
+Yeah, that's I mean, I think that's what that's kind of what I was saying is like people just just kind of mapped over the like HBO followed the formula and people just mapped the result over. And yeah, you know, so anything else for the list?
+00:31:22 Jordan
+I would say True Detective. is too low. And it granted the show, I think only ran like 3, maybe four seasons. But that first season was so peak. I think just off that season alone, you got to put it higher up on the list. That show was insane.
+00:31:39 Darius
+Yeah, I think the fact that two, three, or four weren't, well, two was terrible. Three, three was fine and four was good. When they went to Alaska with Jodie Foster, that was legit. Yeah, okay, yeah, The one with Maha Shala Ali was solid. That second season where Vince Vaughn tried to be serious. Rachel McAdams.
+00:32:00 Jordan
+Richard McAdams. Yeah. Colin Farrell, I think was in it too.
+00:32:03 Darius
+Yeah. They could have kept that one. But the one, the first season will always be goated. I think people, well, they only ranked the first season. So, you know.
+00:32:12 Jordan
+True.
+00:32:12 Darius
+There was some one season shows that are above it that were kind of wrong. But. Yeah. All right, man. You got the next topic.
+00:32:23 Jordan
+Yes, I was Sylvester Stallone, obviously famously played Rocky. He did a like hour, hour and a half long New York Times interview. It's transcribed as well as it's a video interview, camera interview, whatever you want to call it. And he talked about how playing Rocky and playing Rambo and all those characters in the 80s gave him, led to him having eating disorders. He said he was, you know, had bulimia. He talked about the toll that taking steroids took on his body and just the toll of doing his own stunts. he was like, guys, don't do your own stunts. I've had so many back surgeries, knee surgeries, dude. Like, it's not worth it. Just let snack guys do their thing, you know. I thought it was really interesting one because.
+00:33:04 Darius
+Let them tear their bodies up. Let the help do that ****.
+00:33:15 Jordan
+Let the guys who can't act do this.
+00:33:18 Darius
+Your face is what's important here. Nobody knows them. Let them deal with the concussions.
+00:33:24 Jordan
+Right. It's like, you know, the guy who makes sense to me. Let's have him put his life at risk.
+00:33:29 Darius
+I love when Richard accidentally tell the truth.
+00:33:31 Jordan
+Right. It's like my favorite genre of interviews. Yeah, I loved it. It was really cool. I thought it was really cool and interesting that the guy who unknowingly perpetuate a lot of the body image issues that men have today. Suffered them himself. I thought that was really cool and honest of him to say. And we've talked a little bit about body image issues with men on the show,</t>
+  </si>
 </sst>
 </file>
 
@@ -10311,7 +10631,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10338,7 +10658,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -10355,6 +10674,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10674,7 +10997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -11488,7 +11811,7 @@
       <c r="D41" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="E41" s="12" t="s">
+      <c r="E41" t="s">
         <v>321</v>
       </c>
       <c r="F41" s="11" t="s">
@@ -11527,6 +11850,23 @@
       </c>
       <c r="F43" s="11" t="s">
         <v>320</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>322</v>
+      </c>
+      <c r="B44" t="s">
+        <v>323</v>
+      </c>
+      <c r="C44" s="10">
+        <v>46311</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -11541,7 +11881,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -12152,6 +12492,20 @@
         <v>277</v>
       </c>
     </row>
+    <row r="44" spans="1:4" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>322</v>
+      </c>
+      <c r="B44" t="s">
+        <v>323</v>
+      </c>
+      <c r="C44" s="9">
+        <v>46311</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D40" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
     <filterColumn colId="3">

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE84045-90F6-4485-8704-D59E249E1137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B00D69-F1BE-489E-9346-F9879DA0FA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="328">
   <si>
     <t>youtube_link</t>
   </si>
@@ -10542,6 +10542,9 @@
 00:33:31 Jordan
 Right. It's like my favorite genre of interviews. Yeah, I loved it. It was really cool. I thought it was really cool and interesting that the guy who unknowingly perpetuate a lot of the body image issues that men have today. Suffered them himself. I thought that was really cool and honest of him to say. And we've talked a little bit about body image issues with men on the show,</t>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-aZ5d3Nkv04&amp;t=1s</t>
+  </si>
 </sst>
 </file>
 
@@ -10631,7 +10634,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10658,6 +10661,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -10674,10 +10678,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11831,6 +11831,9 @@
       <c r="D42" s="4" t="s">
         <v>270</v>
       </c>
+      <c r="E42" s="12" t="s">
+        <v>327</v>
+      </c>
       <c r="F42" s="11" t="s">
         <v>319</v>
       </c>

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B00D69-F1BE-489E-9346-F9879DA0FA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A102F5FB-1418-42CB-BE75-8FE4699AB9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="30660" yWindow="16080" windowWidth="24240" windowHeight="13020" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
@@ -10543,7 +10543,7 @@
 Right. It's like my favorite genre of interviews. Yeah, I loved it. It was really cool. I thought it was really cool and interesting that the guy who unknowingly perpetuate a lot of the body image issues that men have today. Suffered them himself. I thought that was really cool and honest of him to say. And we've talked a little bit about body image issues with men on the show,</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=-aZ5d3Nkv04&amp;t=1s</t>
+    <t>https://www.youtube.com/watch?v=R-UnyCCYd0U&amp;t=1s</t>
   </si>
 </sst>
 </file>

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A102F5FB-1418-42CB-BE75-8FE4699AB9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0635AE2-957A-49A8-BBCB-AFCF579056DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30660" yWindow="16080" windowWidth="24240" windowHeight="13020" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="334">
   <si>
     <t>youtube_link</t>
   </si>
@@ -10545,6 +10545,359 @@
   <si>
     <t>https://www.youtube.com/watch?v=R-UnyCCYd0U&amp;t=1s</t>
   </si>
+  <si>
+    <t>Chesterton's Fence, Sports, and Empty Platitudes</t>
+  </si>
+  <si>
+    <t>10.06.26</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Topics Covered&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Social-media engagement, likes, followers, and internet validation.&lt;/li&gt;
+    &lt;li&gt;The changing purpose of Instagram and the shift from sharing experiences to sharing oneself.&lt;/li&gt;
+    &lt;li&gt;TikTok, AI-generated trends, and whether older generations are discovering AI for the first time.&lt;/li&gt;
+    &lt;li&gt;Women’s online engagement versus men’s online engagement.&lt;/li&gt;
+    &lt;li&gt;Chesterton’s Fence and how it applies to sports and society.&lt;/li&gt;
+    &lt;li&gt;Player empowerment, salary caps, second-apron rules, and team loyalty in the NBA.&lt;/li&gt;
+    &lt;li&gt;The rise of three-point shooting and whether optimization has made basketball less entertaining.&lt;/li&gt;
+    &lt;li&gt;College football NIL deals, transfer portals, and whether college sports are losing their identity.&lt;/li&gt;
+    &lt;li&gt;Bad platitudes including “Don’t judge a book by its cover,” “Everything happens for a reason,” and “It’s the thought that counts.”&lt;/li&gt;
+    &lt;li&gt;Dating norms, social-media influence, and approaching people in real life.&lt;/li&gt;
+    &lt;li&gt;Dynamic pricing, concert tickets, airline-style pricing models, and live-event affordability.&lt;/li&gt;
+    &lt;li&gt;Stevie Wonder ticket prices, supply and demand, and luxury experiences.&lt;/li&gt;
+    &lt;li&gt;Tomatoes being classified as both fruits and vegetables due to history and tax policy.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Questions&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;What load-bearing pillars of sports are being removed right now?&lt;/li&gt;
+    &lt;li&gt;Has player empowerment gone too far?&lt;/li&gt;
+    &lt;li&gt;Is college football still college football?&lt;/li&gt;
+    &lt;li&gt;Have algorithms removed the feeling of getting a good deal?&lt;/li&gt;
+    &lt;li&gt;Which common piece of advice is actually terrible advice?&lt;/li&gt;
+    &lt;li&gt;Do social-media conversations distort how people interact in real life?&lt;/li&gt;
+    &lt;li&gt;Should artists intentionally keep ticket prices affordable for fans?&lt;/li&gt;
+    &lt;li&gt;What traditions exist because they solve problems we no longer recognize?&lt;/li&gt;
+    &lt;li&gt;When should somebody simply “do the thing” instead of waiting for perfect conditions?&lt;/li&gt;
+    &lt;li&gt;Are luxury experiences becoming exclusively for wealthy consumers?&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Observations&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Fans connect with teams through continuity, not constant roster turnover.&lt;/li&gt;
+    &lt;li&gt;Optimization and entertainment are not always the same thing.&lt;/li&gt;
+    &lt;li&gt;College sports relied on the perception of amateurism more than people realized.&lt;/li&gt;
+    &lt;li&gt;Social media often rewards the loudest voices, not the most representative voices.&lt;/li&gt;
+    &lt;li&gt;Many platitudes exist because they sound comforting rather than because they are true.&lt;/li&gt;
+    &lt;li&gt;Algorithms increasingly price products exactly at the consumer's breaking point.&lt;/li&gt;
+    &lt;li&gt;The loss of low-stakes social interactions has made dating feel more stressful.&lt;/li&gt;
+    &lt;li&gt;People often want empathy rather than solutions when discussing problems.&lt;/li&gt;
+    &lt;li&gt;Bad days do not necessarily mean a bad life trajectory.&lt;/li&gt;
+    &lt;li&gt;The best time to start something is usually before you feel fully ready.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Debate&lt;/h3&gt;
+  &lt;p&gt;Should sports prioritize what is optimal or what is entertaining? Jordan argued that modern rules incentivize behavior that may be mathematically correct but less enjoyable to watch. Darius expanded the discussion using Chesterton's Fence, arguing that sports have removed important traditions and structures without fully understanding why fans loved them in the first place.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Social Media&lt;/li&gt;
+      &lt;li&gt;Attention Economy&lt;/li&gt;
+      &lt;li&gt;AI&lt;/li&gt;
+      &lt;li&gt;Sports&lt;/li&gt;
+      &lt;li&gt;Player Empowerment&lt;/li&gt;
+      &lt;li&gt;NBA&lt;/li&gt;
+      &lt;li&gt;College Football&lt;/li&gt;
+      &lt;li&gt;NIL&lt;/li&gt;
+      &lt;li&gt;Tradition&lt;/li&gt;
+      &lt;li&gt;Chesterton's Fence&lt;/li&gt;
+      &lt;li&gt;Consumer Culture&lt;/li&gt;
+      &lt;li&gt;Dynamic Pricing&lt;/li&gt;
+      &lt;li&gt;Dating&lt;/li&gt;
+      &lt;li&gt;Modern Relationships&lt;/li&gt;
+      &lt;li&gt;Life Advice&lt;/li&gt;
+      &lt;li&gt;Optimism&lt;/li&gt;
+      &lt;li&gt;Risk Taking&lt;/li&gt;
+      &lt;li&gt;Personal Growth&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>Technology &amp; Internet Culture, Sports &amp; Athletics, Money &amp; Class, Aging &amp; Personal Growth</t>
+  </si>
+  <si>
+    <t>10.23.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transcript
+00:00:01 Darius
+People don't understand supply and demand dynamics. It's like when you go see, Drake or Megan Stallion in Charlotte, you're competing with the people in Charlotte who want to see them that night, right? Someone like Stevie Wonder on a last run at Madison Square Garden, you're competing with people who want to fly. So you're competing with Everyone in the world with money who wants to see Stevie Wonder?
+00:00:25 Jordan
+Yes.
+00:00:26 Darius
+Don't even open the link on your phone unless your money is right. You wasting, you ************. You're not getting in that building for less than $1,000. You not parking your car for less than $1,000?
+00:00:38 Jordan
+For less than $100. Yeah.
+00:00:41 Darius
+Welcome to Out the Trunk with Jordan and Darius. I'm Darius. That's Steve's I love the area on all socials.
+00:00:46 Jordan
+And I'm Jordan. That's Jordan B riding on all socials.
+00:00:50 Darius
+This is our segment we've titled What's On Our Mind, kind of our pop culture conversational segment where we let you guys know what's on our mind. Normally, I start off with a warm up question, but I don't have anything today. So we're tossing it to my trusty co-host with the opener. So what you got?
+00:01:07 Jordan
+Yes, I was going on Twitter yesterday, you know, just bored throughout the course of the day. And this girl made a tweet went viral. She was like, Yeah, but my post do 250 likes. I'm like, I know my stories get 250 likes. That's why I know I took like a really nice picture or something like that. And this guy was like, all the guys were like, what the ****? Like, it was like, we live in a totally different world because dudes were like, bro, if I get 10 likes, I'm a sex symbol. Yeah.
+00:01:35 Darius
+I don't have 250 followers. So I. I would, okay, so I don't care about likes, but I would be lying if I say I didn't notice when some photos get more likes than others.
+00:01:54 Jordan
+Right.
+00:01:54 Darius
+But 250, I would think, I think, I would think my phone was like glitching. I don't even know. Yeah. Women do live in an alternate universe because only two.
+00:02:07 Jordan
+I put no autographs, please.
+00:02:09 Darius
+Yeah. Okay. Is she like a celeb or something or just like a regular woman?
+00:02:15 Jordan
+No, I was just like a regular girl.
+00:02:16 Darius
+250. That's that's a lot.
+00:02:20 Jordan
+And then this one girl quoted it with the guy. The guy was like, what? And this girl was like, dang, that's crazy. You don't even get 10 likes for like a fresh cut.
+00:02:31 Darius
+The most likes I've ever gotten. I that wasn't my cat. So that doesn't count. That's cheating.
+00:02:40 Jordan
+Right.
+00:02:41 Darius
+I posted a selfie for the first time in a long time in a red shirt a couple of weeks ago, and I think it hit 11. So that is my record. And I just don't I don't I don't care. It's hard to like it's all right. You're on Instagram. So a part of you does care. Like, I'm not going to be that person who says, like, you don't care at all. Why do you care? I don't I really don't. But I think I like the slice of the internet that I've carved for myself where I'm only interacting with people who have met me in real life. Or if not met me in real life or know me in real life, we go back so many years through so many different channels. It's like I know them. Or if I pulled up in their city, we'd meet for a beer or something. I don't understand the regular people who have 10,000 followers from an unlocked account and just deal with strangers in their mentions all day at work. If it's not my job to deal with strangers in my mentions, I don't think I'd ever want to do it for free.
+00:03:51 Jordan
+I get that. Yeah, it's funny because like you think you want to go viral and for certain things or whatever, if I post like a poem, I want that to go viral, obviously, or, I want our podcast **** to go viral clearly. But, I have like viral comments on posts and ****. And I'm like, I'm still getting likes in them from like six months ago, a year ago. And it's like, okay, don't stop like notifying me that it got a like on that. You know what I mean?
+00:04:13 Darius
+I don't even comment on other people's IG. I will bookmark and like them, but like comment I just, not that I feel like I'm above it. I just, I'm not native to socials that way. It came after I was an adult. So like a lot of the customs and norms of it aren't ingrained. Like I just don't comment. I will like in bookmark stuff though. I have a robust list of bookmarks and I like things, but yeah, that it shows people what you like. I'm a bit more judicious about what I like. By a bit, I mean a lot. I tweeted the other day that one of the best decisions I ever made for my attention span was never downloading TikTok. And again, that's not like a I'm better than people think. It's just that at 38, like I said, like the last social I'm going to download is Snapchat. Like I'm done learning new social media apps. And so TikTok came after Snapchat. So that was it. And even Snapchat, I don't use that ****.
+00:05:14 Jordan
+Right.
+00:05:16 Darius
+Yeah, I don't use it to post. I'll put it that way. I use it because the messages disappear.
+00:05:24 Jordan
+Right, for sure. Yeah, we use it for the disappearing feature, for sure. Yeah, it's perfect for weekends. It's great for weekends. Yeah, somebody was like, yeah, I mean, it's funny the way people like focus so much on likes and like, and it can get in your head, of course, for sure. Like if you post something and it doesn't get like a lot of interaction that may make you not post as much. I hear people say that a lot with Instagram in particular, because especially the way the algorithm works now, it's like all ads, you don't really see your friends on there anymore for whatever reason and **** you know, that's a factor too.
+00:05:58 Darius
+So are you so when people say they post something and it doesn't get engagement and they get disappointed, where's that coming from?
+00:06:09 Jordan
+Like psychologically.
+00:06:10 Darius
+Yeah. So like, Okay, so if you post, okay, if you post a fresh cut selfie and it just throws up bricks, okay, I understand how that would feel away. But like, I see people like repost a GIF that they saw and I'm like, what am I okay? If you, if I don't, what engagement are you looking for that? Like, you know.
+00:06:30 Jordan
+Yeah, no, I get you. Yeah, I think like if it's something that you made, like something original, then you, I would, I have definitely been like, oh, that's weird. I thought that would get more engagement, whatever, for sure. If it's just some, like a lot of my story posts are not things that I made, I'm like posting something. So I don't care if that gives engagement, whatever, you know. So I mean, I think it depends. I think most people care if it's something personal to them that they're posting as opposed to just some random ****. I think part of the thing with Instagram is now that like, it used to be like we post Like 10 years ago, Instagram was like from memes and random ****. Oh, I drank coffee today or I saw a bird, whatever, and now I'm also like, it has to be like a big event for you to, for you to post now, almost, you feel like it almost has to be like a, the internet kind of makes you think it just by comparison, once you see other people post, I guess it can seep into your mind where you're like, well, I don't have a new baby. I didn't buy a house and I didn't buy a new car today. So I guess I shouldn't post anything on Instagram. You know what I mean?
+00:07:33 Darius
+I have noticed that the camera Instagram was more interesting when the camera faced outward, when people were showing the things that their world. And now the cameras flipped inward. Inward, not inward. I think it's it's it's a selfies like them rambling in their cars. Yeah. And I just don't I'm not into that as much. I do. I do like what people so I'm big on On my stories, I don't do a lot of reposting other stuff because I feel like people follow me for me. And so, I will share reels that I find particularly funny with certain people, but. Sure. Yeah, I don't know. Like I posted the nine album thing **** yesterday. I hate to date the pod. And like a lot of people like responded to that with like genuine engagement. And one, a couple of people asked me where to find the link to do it and ended up posting theirs. And so like, that was actually like a fun engagement. So I just try to post.
+00:08:39 Jordan
+Yeah, those are fun. I like those.
+00:08:42 Darius
+You know, if it's not things that I'm doing, it's like a get to know me type thing. So I find that To keep the essence of what Instagram is supposed to be, So I was super late to IG, man. I didn't. I didn't start posting. Until I ****. 2020, 20. Like, I think COVID made me start posting on Instagram. Yeah, it's crazy. I had an account, but I like. Yeah, I mean, I would post. very rarely, or I would post exclusively behind close friends. Like I didn't really start posting like regular, degular stuff to my stories until I would say COVID. Like I'm a super late adopter to socials, man. Like my first, the first cell phone I owned, I was 17, my 17th birthday. So it's like, you know, I'm not a native.
+00:09:34 Jordan
+Yeah. I was like 17 when I got my first cell phone, you know, so yeah, I'm kind of similar to that. I think on Instagram, I got on Instagram and I was in college, maybe like 2013, 2014, something like that. But that's when it was like just memes and **** and like, you know, silly stuff. It's to the point where I remember like that started like when I was like meeting people out, whatever they'd be like, you know, for me to grow, they go through Instagram and ****. And they would tell me like, you need to post yourself more because if I didn't know you in real life, I would think you were like a bot or a catfish, because it was just like my feet was like all memes. And so I started like, okay, I'll post myself more. I guess that makes sense. It does look a little odd, I guess. You know, so yeah, I'm with you because I never really knew exactly what to use Instagram for, I guess, because it's so It can be anything, you know, it's not like, and it was before content became content and it was before it was niches, niches and oh, I'm on this side of Instagram and so on and so forth, you know, all the algorithms and stuff started to take over.
+00:10:35 Darius
+Yeah, I'm still. I don't ask, we exchange numbers with women. We don't really do the exchanging Instagram thing. So if, I mean, I'm certain like someone I talk to would like scroll my Instagram, but.
+00:10:48 Jordan
+I. Oh no, like they would get my number and then you've come up with a follow suggestion and then they would go through and.
+00:10:54 Darius
+Yeah. I mean, I'm certain it's happened and they just never told me. But like the idea that like, I would meet a woman and the next thing I would do would just like scroll her Instagram. You know, it's not really. I'm lying. I have done that, but know it's not.
+00:11:10 Jordan
+They're about to say, well, come on man.
+00:11:13 Darius
+I have done that. If for no other reason than to check the recency of the photos. So.
+00:11:19 Jordan
+Yes.
+00:11:20 Darius
+You know, so it's.
+00:11:24 Jordan
+Or if you were fated when you met, you kind of want to make sure, you know.
+00:11:27 Darius
+I do. I try to limit my screen time these days, but I don't really hit the for you page and just like scroll the endless reels because I just find so much of that stuff original. I just really just I'm on there to look at people's stories and beyond that, I know a lot of people who use IG almost like television. They're just like watching the reels of randoms for you page. And it's just the same 7.
+00:11:59 Jordan
+Trends.
+00:11:59 Darius
+Trends over and over and over again. Okay, so while we're here, what is supposed to be funny about the Quavo takeoff thing?
+00:12:06 Jordan
+It's nothing. is funny about it. Nothing. Not a single thing is funny about it. None of them were funny. The first one or two were like kind of cute, but then everybody started doing it. I was like, okay, bro. Like also the song is the video came out what, five years ago? Four, three, four years ago? Like what?
+00:12:19 Darius
+Yeah.
+00:12:20 Jordan
+I don't know. I don't. I don't find it funny or original. And also you're wasting water. So can you stop, please?
+00:12:28 Darius
+Well, so that's a bit that's a bit debunked. Data centers don't really use more water than any other industrial building, but. But they're still using water. I mean, so am I, you know, like what you need it.
+00:12:44 Jordan
+Fake Quavo does not.
+00:12:46 Darius
+Yeah. So. Okay. Beyond, I don't even care if it's just because a lot of people are saying it's distasteful because Takeoff died. And I'm like, Takeoff is a public figure. We make fun of dead celebrities all the time. You know, he's not a private citizen.
+00:13:00 Jordan
+They're not making fun of him. They're just doing the right.
+00:13:03 Darius
+But people are like, it's like, I understand why Quavo might feel away, but I understand why regular people feel away. Takeoff, like, you know, he was a celebrity. He was a public figure. He was known for 10 plus years. He wasn't some obscure random rapper. But I just scrolling through thought people were like writing their own raps to it and doing their own things. And then I found out it's literally just them mapping their face onto it and doing the same exact mechanisms. And I just don't get it.
+00:13:31 Jordan
+It's like facial replacement, basically. Like they do in movies. Yeah. It's not for me. I'm not the demographic, I guess. I feel like the older Like the 35 and up crowd on Facebook seemed to really get a kick out of it from what I've seen.
+00:13:47 Darius
+Oh, Speedy Morbin.
+00:13:47 Jordan
+The Four Loco crowd, I feel like it's for them.
+00:13:50 Darius
+Yeah, Speedy, he posted a video, he was like, how y'all expect us to react when y'all post the take off thing. He's like, oh my God, wow. You know what it is? It's literally just the same ******* thing.
+00:14:07 Jordan
+It's the equivalent of when little kids are like, you want to see something cool and they just fall down.
+00:14:14 Darius
+It's like, yeah, you're right though. It is like old people showing us they know how to use AI now.
+00:14:21 Jordan
+Look at me, look what I can do. it was like it was like when they did the trend like 2 weeks ago where it was what I would have looked like in the 80s. everybody did the AI with the windbreakers and ****. Also, it's funny because there are people who were I know who were alive in the 80s who used AI. And it's like, you can just post a throwback because you know, you didn't look like that in the 80s.
+00:14:39 Darius
+Yeah. So like, at least that is like interesting, right? It's a different.
+00:14:44 Jordan
+It was fun.
+00:14:45 Darius
+It was fun. It was interesting. I understand why someone's I don't object to people using like All technology uses energy and the idea that like you're going to shame people out of using, something that's useful because it's bad for the environment. Okay. I honestly nobody. I see one electric car per 1000 vehicles. Per right. And they're not even expensive anymore. So yeah.
+00:15:09 Jordan
+Also like people are like, oh, don't use AI. And it's like, I do get it. And I do think there's element of that is scary. But like we use Siri every day.
+00:15:17 Darius
+Yeah. And also just. It's like people think if they put their ear into la la la la, it'll just go away.
+00:15:24 Jordan
+Yeah.
+00:15:25 Darius
+Yeah.
+00:15:25 Jordan
+It's like a valiant effort, but.
+00:15:30 Darius
+You know. Also, to say there's no use for it is just wrong. And you can say like, I don't use it for creative things. I don't think, I think there's a, but like math and code and helping plan a vacation. I don't know why I would do that the hard way. I've made the joke on the pod before. Like, so you want me to go back to like, cooking over an open fire with sticks and stones too? Like, where does like, my stove uses fossil fuels. So what do we, well, my stove's electric now, but you get what I mean. Like it's, you know, you listen to some of these people and it's like, we still be driving cars with our feet if we let them run the world. It's like, so. You got anything else for that one?
+00:16:22 Jordan
+No, I just thought it was really, really funny. I'm like, honestly, it did give me like much more insight into like the things women go through, you know, because I imagine you just wake up first and you scroll Instagram to see what your friends posted or some **** whatever. And you just have 300 thirsty kind of like trying to bed you every day.
+00:16:43 Darius
+I have had a couple of homegirls show me their inboxes and it's a ******* war zone.
+00:16:47 Jordan
+Yeah, bro, it's nuts.
+00:16:48 Darius
+I mean, you know, I thought it was like people that over exaggerating.
+00:16:56 Jordan
+Yeah.
+00:16:57 Darius
+I mean.
+00:16:58 Jordan
+My sister told me some of the **** a guy said in her DMs one time and I'm like, he just opened up with that with you and you didn't know this guy like, yeah.
+00:17:08 Darius
+Shoot your shot, but like, get it, can it like?
+00:17:11 Jordan
+Be respectful, please.
+00:17:13 Darius
+Keep it in the balance of, you know, Jesus Christ, respectability, you know? Yeah, it's I remember one time I'll leave the friend out of it. She showed me her inbox on a dating app and it was most of the pictures would have to be blurred out if we put them on the pot like they're like it was nuts. Just like an ice cold, you know, I don't know who that like.
+00:17:41 Jordan
+Like the kind of **** you need to take a shower after reading.
+00:17:44 Darius
+I was kind of mad that she didn't give me like a trigger warning.
+00:17:48 Jordan
+Okay, ****.
+00:17:50 Darius
+I didn't want to see that to start my evening.
+00:17:52 Jordan
+Oh, oh, oh, got you, got you, got you.
+00:17:54 Darius
+Yeah.
+00:17:54 Jordan
+But, you know, like to catch a predator, basically.
+00:17:58 Darius
+Not great, Bob. You know, shout out to Pete Campbell.
+00:18:02 Jordan
+Yeah. So it was crazy.
+00:18:04 Darius
+Yeah. So last week on the pod, I made mention of an old saying called Chesterton's fence. Basically, if you see a fence in the middle of the field before you remove it, make sure you understand why that fence was there. And earlier today, I was thinking about how that applies to sports. And so I have a couple of answers, but I'm gonna start with you, man. So if you think about the way sports are changing with like the optimization for money and the optimization for winning, What are some ways sports are changing that you feel are impacting the core identity of the sport? And what are some core, some like load bearing pillars of sports that we're taking for granted and changing? And if we change, it could like change at your own peril, if you will. So that's a poorly worded question. So I'll just ask you straight up. I get what you're saying. What are some core changes to sports that you feel are load bearing?
+00:18:57 Jordan
+Okay, I'd say. the second apron, I think is one thing that I really think is going to ruin, not ruin, but it's going to, like people are big loyalists, at least they pretend to be when it comes to sports. Like, oh, we want to see players jump around, move around. It's like, well, with these second apron, you're forcing organizations to make pay cuts or give or forcing the players to take care cuts, which they shouldn't have to do and don't want to do, and they have limited time to earn this maximum earning potential and leave off that for the next 50 years, you know, whatever. I think secondary is one thing for sure that's kind of ruining the period of the game. The days of, you know, guys playing, Kobe Bryant, Tim Duncan, those guys playing 20 years for an organization, those days are over. And we love to blame it on certain players moving and **** like that, but the organizations are doing it and the owners are doing it too. They're fostering the environment as well. I think that's one thing for sure that is negatively impacting sports. I mean, the New York Knicks, they, their chance to have an honest shot at a repeat is probably done because they can't pay Carlton Townsend what he deserves to be paid. Like an $80 million pay cut is crazy, you know, especially after just what he just sacrificed and the way he played in those playoffs.
+00:20:06 Darius
+Well, quick interjection. They don't have to. They could pay him. Well, true. Right.
+00:20:11 Jordan
+Well, that's the thing.
+00:20:12 Darius
+It's like that's an important distinction to make. So I agree. I have on here players changing teams. for whatever reason it may be, I think fans by and large like to see the same characters in the movie come back. And even if the headlining players stay the same, if you think about those 90 bulls, Dennis Rodman was a key part of that story. Luke Longley was a key part of that story. Ron Harper was a key part of that story. If every year it was just Jordan Pippen and Tony Ku coach and then five new dudes from new teams, it wouldn't hit the same. You know, if I remember those Spurs teams, it was Bruce Bowen, it was Steven Daniel, Steven Jackson, Avery Johnson, it was Brent Berry. Yeah, and those I do. I think it matters. And I think that we part of it was kind of us to being obsessed with the transaction. And yeah, that's true. And then all these players changing teams and we kind of lost. Yeah, I agree to long story short of it is that I agree. I think there was a whole movement of people just like pushing player empowerment, player empowerment, player empowerment, and that's fine. don't get me wrong, but to act like there was, they spoke about it as if there was no downside. And there is downside when fans have no attachment to you. Like I've said this before on the pod, like Kevin Durant playing on seven different teams. That's the reason why no one likes him anymore. We sort of were told that these players choosing where they play and moving around is like, there's no drawbacks to it. And I don't think that's necessarily true. I think players staying in one place was a bit of a load bearing principle. And we have moved that fence. And I just don't know if we're going to like what's on the other side of it. There's like no, like the Knicks won their first championship in 40 something years. They're about to repeat in three weeks. Not even just that. They're about to repeat in three weeks. And what are we talking about? Contracts, aprons, and like you need an accounting degree to follow the lead.
+00:22:27 Jordan
+Exactly. It's like we've all low-key become capologists,
+00:22:31 Darius
+sports fans, because it's not why any of us got into this, you know. Yeah, it's like, you know, the superstar on the team is the GM now. And I just don't think that's why anyone got into sports. why are we talking about Karl-Anthony Townsend's salary on the eve of a, they're about to get their rings. They even gotten their rings yet. Like, you know, it's funny.
+00:22:53 Jordan
+And who knows if he's even going to finish the year with the team, you know, who knows if there's going to be a trade coming if he demands a trade. Even I mean, the Thunder, we took about like Sam Preston and all those pictures and ****. It's like, yeah, it's incredible. But those guys aren't, they're not going to pay them what they're worth on those second contracts. So all those guys who hooped in the playoffs last year and the year before that, they have one or two more years together as a collective and that team's gonna look very different.
+00:23:17 Darius
+Yeah, it's like I listen to a lot of NBA podcasts and when the season starts, the games are the game. But I just get so tired of talking about cap holds and this smack slide and 30% of this and I got trade
+00:23:31 Jordan
+kickers and incentives and it's
+00:23:33 Darius
+just like, that's not why any of us got into this. And we just, it's a very lawyerly, it's like I have to be smart and numbers driven at work. When I go, oh, I want to watch a basketball game, man. And it's almost beside the point, you know, I have on here too many threes in that threes are like dessert. Like it's great, but it can't be your whole diet. And a lot of people struggle to make the distinction between optimal strategy and what's most entertaining. And I would never say shooting a bunch of threes is a bad strategy because it like 3 is 50% more than two. It's the right thing to do.
+00:24:17 Jordan
+I just don't enjoy the shooters who are efficient.
+00:24:19 Darius
+You don't have to. That's the thing about it. They like if you shoot 32% from three, it's still a better shot than a lot of twos.
+00:24:25 Jordan
+It's just three is so much 40 to.
+00:24:30 Darius
+Three is just so much more than two. You really don't like, and that's the thing. That's the what makes it so frustrating is that they're right. Like the math is rock solid on it. Like honestly, teams probably don't shoot enough mathematically.
+00:24:41 Jordan
+True.
+00:24:42 Darius
+That's why you have to make the distinction between if it's good math or if it's entertaining to watch. And I didn't get into basketball to watch one dude while four people stand around a three point line. I can't stand when there's a fast break. and they pull up to shoot a three, or you could tell that the guy with the ball in his hand is looking for an open three-point shooter and not attacking the basket, even though I understand that's the right thing to do.
+00:25:04 Jordan
+True. And even some of that is a misnomer because, you know, we saw the Rockets go 0 for 27 from 3 and cost themselves a shot at possibly a title. You know, the words, yeah, they shot a lot of threes. Steph Curry's greatest shooter ever shot a lot of made a lot of threes, shot a lot of threes. But they also scored a lot of paint points. Steph Curry led the league or his top five and top 10 in his prime in paint points damn near every year. Like there's it wasn't like he was just jacking up threes and he was afraid to go into the paint. You know what I mean? Like there are people I think people are like, oh, Steph Curry changed the game, which he did, but he's an anomaly. He's there's not there's more than there's not just one him, you know what I mean? And people try to duplicate that and replicate that across league wide. And I think that's part of what has, caused the game to suffer a bit as well too, has become a three point shooting contest. And you have guys who shoot 30% from 30, taking five threes a game in the playoffs. Those are turnovers.
+00:25:51 Darius
+That's the thing. It's like, even if like, let's say you shoot 30% from three and otherwise you would shoot, I don't know, 45% from two. It's still smarter to shoot a bunch of threes, but it's a lot more misses objectively. And so to the viewer, I'm just watching these dudes miss a lot of shots. And again, it's not really why we got, I can't remember, like when's the last player whose reputation was built on dunking on people?
+00:26:21 Jordan
+LeBron. I think that's it.
+00:26:23 Darius
+Right, he's 41 years old. You know, and we've totally, that whole archetype, that whole Sean Kemp Vince Carter. I'm here to put your whole arm through the hoop. That player has been legislated out of the game.
+00:26:39 Jordan
+Correct.
+00:26:40 Darius
+And that was an entertaining player to watch.
+00:26:42 Jordan
+Right.
+00:26:43 Darius
+And so now you see that.
+00:26:44 Jordan
+Lock City wouldn't exist today.
+00:26:45 Darius
+Right. Blake Griffin. Yeah, like Blake Griffin. If he came around drafted today, I don't know how impactful he would be because he couldn't shoot.
+00:26:54 Jordan
+And so I don't want to live.
+00:26:58 Darius
+I just don't know if I want to live in a world where a player like Blake Griffin isn't impactful. Right. And so baseball did a really good job of it. So baseball. the math got a hold of it first. And so baseball was more or less like a solved puzzle for a while because you had so much data on where the batters hit the ball that the defense could just put the hitters, I mean the defenders, where the ball is going to go.
+00:27:22 Jordan
+Where they're going to hit it.
+00:27:23 Darius
+And you could literally predict, oh, this guy hits it here 40% of the time, so I'm going to move my players here. And so there were no balls in play. You know, every at bat was a strikeout or a home run. No one ever stole bases because the math says that's bad because you rather just, the out is more important than the extra base. And so what they do, they wouldn't change the rules. They ban the shift. They're like, okay, I understand it's mathematically important, but it's my job as a commissioner to make sure that my product is entertaining. And so I don't blame the teams because it's their job to win football or win basketball games. It's on the league to adjust the rules so that the The product is entertaining. And so you have anything else for that one?
+00:28:12 Jordan
+I think here. What are some we take for granted? Losing. I think we take losing for granted.
+00:28:21 Darius
+Okay.
+00:28:23 Jordan
+Like championships are important and championships matter. But if everyone is supposed to have one and everyone does whatever they have to do to get one, then how much do championships matter? people are like, oh, you got to win one. And they take the joy out of it. Like to the point where the players not even happy that they win the championship, they're just relieved. And they're like, oh, thank God, they don't call me a loser for the rest of my career. And that was, that's really what Katie was talking about when he said that, you know, that thing about like, I thought championship would do all of this things for you give me all of this satisfaction and it didn't. I mean, of course there's a lot of gold medal theory there too, but it's also because you, You punish these guys so much for not winning that when they do win, it's like, all right, well, I guess I'm going to be called like the best player to never win a championship. But like, now what? You know.
+00:29:09 Darius
+I have a problem with that. That's what the money's for. But I will say that there's a difference between never winning a championship and never competing for one. And so I don't think people look at Charles Barkley or Patrick Ewing or. Like Carl Malone, John Stockton, like players.
+00:29:33 Jordan
+Miller.
+00:29:34 Darius
+Yeah, it's all Reggie Miller. They're still esteemed. They didn't win a championship, but they competed for one. They either made the finals or made the conference finals or like they had iconic matchups against moments. Other people who won a bunch of each other
+00:29:48 Jordan
+and other great players. Yeah.
+00:29:49 Darius
+And I think we view them differently than we view like a Vince Carter who never really competed for a championship.
+00:29:54 Jordan
+Tracy McGrady never had a shot.
+00:29:55 Darius
+Yeah. James Harden. we respect your career if you competed for a championship.
+00:30:02 Jordan
+Yeah.
+00:30:03 Darius
+But if you lost in the first round, I'm sorry.
+00:30:07 Jordan
+Yeah, like, did you see the clip of Gil Arena's new podcast? He's talking to Boogie Cousins and Nick Young. Nick Young was saying like, if you didn't make it out the first round, you weren't a great player.
+00:30:18 Darius
+Yeah.
+00:30:18 Jordan
+And like some of the guys got like, felt a way about it. It's like, greatness means winning or at least competing or elevating your team. If you didn't get out the first round ever, I'm sorry about how great were you like? That's my thing too. You know what? That's another thing on the list. Bag talk. Like having a bag, bag work, whatever the **** that is supposed to mean. A lot of players have quote unquote great bags or better bags than some other players and those players did not win or get close to winning. They did not elevate their teams. Tracy McGrady had a great bag. Kobe Bryant in his book famously said he could do everything I could do but at 6'9 Except get out the first round. So how much was that? How much did that pack matter? You know what I mean? And that's not just like the teammate actually is an example. There's a lot of players that like we say, oh, their bag is crazy, their bag is better, whatever. Okay, but like, think about all the wings who have quote unquote great bags. How many of them won on an elite level besides Kevin Durant?
+00:31:08 Darius
+I mean, honestly, I've always said the most overrated thing in basketball is making difficult shots. Because it looks cool. And so You know, Kyrie Irving is like a well regarded player where I </t>
+  </si>
 </sst>
 </file>
 
@@ -10634,7 +10987,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10661,7 +11014,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -10678,6 +11030,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10997,7 +11353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -11831,7 +12187,7 @@
       <c r="D42" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="E42" t="s">
         <v>327</v>
       </c>
       <c r="F42" s="11" t="s">
@@ -11870,6 +12226,23 @@
       </c>
       <c r="F44" s="11" t="s">
         <v>325</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>328</v>
+      </c>
+      <c r="B45" t="s">
+        <v>329</v>
+      </c>
+      <c r="C45" s="10">
+        <v>46318</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -11884,7 +12257,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -12509,6 +12882,20 @@
         <v>326</v>
       </c>
     </row>
+    <row r="45" spans="1:4" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>328</v>
+      </c>
+      <c r="B45" t="s">
+        <v>329</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D40" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
     <filterColumn colId="3">

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0635AE2-957A-49A8-BBCB-AFCF579056DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB96DAD-9FFF-4C28-8D27-57C7826CB29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="335">
   <si>
     <t>youtube_link</t>
   </si>
@@ -10898,6 +10898,9 @@
 00:31:08 Darius
 I mean, honestly, I've always said the most overrated thing in basketball is making difficult shots. Because it looks cool. And so You know, Kyrie Irving is like a well regarded player where I </t>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=nZ5EakaMIbY&amp;t=4s</t>
+  </si>
 </sst>
 </file>
 
@@ -10987,7 +10990,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11014,6 +11017,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -11030,10 +11034,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12207,6 +12207,9 @@
       <c r="D43" s="4" t="s">
         <v>276</v>
       </c>
+      <c r="E43" s="12" t="s">
+        <v>334</v>
+      </c>
       <c r="F43" s="11" t="s">
         <v>320</v>
       </c>

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB96DAD-9FFF-4C28-8D27-57C7826CB29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FF6478-0F5D-4CD3-BAC4-F64DEA242FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="341">
   <si>
     <t>youtube_link</t>
   </si>
@@ -10901,6 +10901,418 @@
   <si>
     <t>https://www.youtube.com/watch?v=nZ5EakaMIbY&amp;t=4s</t>
   </si>
+  <si>
+    <t>Talent vs. Catalog, Horror Survival, and Halloween Do's &amp; Don'ts</t>
+  </si>
+  <si>
+    <t>10.13.26</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Topics Covered&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Demystifying the voting process, sample ballots, nonpartisan race research, and civic responsibility.&lt;/li&gt;
+    &lt;li&gt;Horror movie survival scenarios, evaluating Scream, Halloween (Michael Myers), The Birds, and The Last of Us.&lt;/li&gt;
+    &lt;li&gt;Home invasion horror logic (The Strangers, You're Next) and weaponizing everyday kitchen items (boiling water, cast-iron skillets, knives).&lt;/li&gt;
+    &lt;li&gt;The psychology of horror: adrenaline disparities between predators and victims, and the survival rule of "minding your business."&lt;/li&gt;
+    &lt;li&gt;Halloween costume etiquette: avoiding blackface/racially tone-deaf choices, inappropriate couples costumes depicting abuse/tragedy, and overly obscure outfits.&lt;/li&gt;
+    &lt;li&gt;Venue-appropriate costume boundaries: school events and neighborhood trunk-or-treats vs. nightlife functions.&lt;/li&gt;
+    &lt;li&gt;Night-out logistics: eating heavy protein meals beforehand, touchscreen glove accessibility, and venue bouncer policies on toy props.&lt;/li&gt;
+    &lt;li&gt;Conspiracy theory rankings across four distinct categories: aliens, government secrets, historical mysteries, and unexplained disappearances.&lt;/li&gt;
+    &lt;li&gt;Historical mystery analysis: the disappearance of the Lost Colony of Roanoke and theories of indigenous assimilation.&lt;/li&gt;
+    &lt;li&gt;True crime case study: the 10-minute disappearance of Maura Murray and the probability of catastrophic bad luck.&lt;/li&gt;
+    &lt;li&gt;Mathematical and scientific probability of extraterrestrial life versus human exceptionalism.&lt;/li&gt;
+    &lt;li&gt;The "One Must Go" R&amp;amp;B legends debate: Whitney Houston, Mariah Carey, Janet Jackson, and Mary J. Blige.&lt;/li&gt;
+    &lt;li&gt;Technical vocal perfection vs. emotional depth, vulnerability, and full-album replay value.&lt;/li&gt;
+    &lt;li&gt;Industry economics: the loss of label-funded vocal coaching and live instrumentation, leading to "whisper singing" and the economic dominance of hip-hop over R&amp;amp;B.&lt;/li&gt;
+    &lt;li&gt;The athletic demands and lung capacity conditioning required for live concert performances and rapid-fire rapping.&lt;/li&gt;
+    &lt;li&gt;Global trivia: France's 12 time zones across its overseas territories and the biological self-regeneration of the human liver.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Questions&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Which horror movie do you think you could actually survive?&lt;/li&gt;
+    &lt;li&gt;Are horror movie characters genuinely stupid, or do audiences severely overestimate calm decision-making during high-stakes terror?&lt;/li&gt;
+    &lt;li&gt;Why do victims in home invasion movies rarely utilize home-court advantage and everyday kitchen weapons?&lt;/li&gt;
+    &lt;li&gt;What makes a Halloween costume fun and recognizable versus self-indulgent or socially tone-deaf?&lt;/li&gt;
+    &lt;li&gt;How much does Black historical trauma justify skepticism toward official government narratives?&lt;/li&gt;
+    &lt;li&gt;Is extraterrestrial life a conspiracy theory or a mathematical certainty given the scale of the universe?&lt;/li&gt;
+    &lt;li&gt;What matters more in a musical legacy: transcendent technical vocal talent or a replayable, emotionally resonant catalog?&lt;/li&gt;
+    &lt;li&gt;Why has modern commercial R&amp;amp;B struggled economically compared to hip-hop production?&lt;/li&gt;
+    &lt;li&gt;How do elite live performers develop the aerobic stamina needed to sing or rap while moving at full speed?&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Observations&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;The biggest barrier to voting is often self-inflicted discouragement; showing up is usually as simple and quick as standing in line for movie snacks.&lt;/li&gt;
+    &lt;li&gt;Survival in horror scenarios usually comes down to one basic rule: mind your own business instead of investigating strange sounds or trespassing.&lt;/li&gt;
+    &lt;li&gt;Meeting home invasion violence with passivity is irrational; attackers arrive with peak adrenaline, so defenders must immediately equalize the violence with whatever tools are at hand.&lt;/li&gt;
+    &lt;li&gt;Costumes worn to children's school events or neighborhood block parties belong to an entirely different category than costumes worn to nightlife districts.&lt;/li&gt;
+    &lt;li&gt;Black communities often hold conspiratorial views because historical reality (slavery, Jim Crow literacy tests, deliberate disenfranchisement) already reads like a conspiracy theory.&lt;/li&gt;
+    &lt;li&gt;Extraterrestrial life is not an outlandish supernatural belief; mathematically, the idea that Earth is the sole harbor of intelligent life in an infinite universe is far less probable.&lt;/li&gt;
+    &lt;li&gt;Technical vocal perfection does not equal replay value; music must evoke authentic feeling and personal connection rather than sterile admiration.&lt;/li&gt;
+    &lt;li&gt;The shift toward "whisper singing" reflects modern label economics: record labels no longer invest in vocal coaches, arrangers, and live bands when rap tracks can be produced cheaply with a beat and a microphone.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Debate&lt;/h3&gt;
+  &lt;p&gt;Vocal Talent vs. Replayable Catalog (Whitney Houston vs. Mariah, Janet, and Mary J. Blige): Jordan sparked the debate using the viral social media prompt requiring the permanent elimination of one discography among Whitney Houston, Mariah Carey, Janet Jackson, and Mary J. Blige. Jordan argued that despite Whitney being one of the greatest vocalists to ever live, her studio albums lack the consistent, front-to-back replay value and everyday emotional resonance of Mary J. Blige's raw grief, Mariah's songwriting mastery, or Janet's joyful pop anthems. Darius agreed, extending the argument to broader music culture: technical vocal gymnastics (citing Adele, Sam Smith, and Jennifer Hudson) often feel cold or exhausting if the music fails to connect emotionally. Both hosts concluded that while Whitney possessed an unmatched instrument, music is fundamentally about how it makes the listener feel, making an undeniable catalog far more valuable than technical vocal ability alone.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Civic Duty &amp;amp; Voting&lt;/li&gt;
+      &lt;li&gt;Horror Cinema &amp;amp; Survival Tropes&lt;/li&gt;
+      &lt;li&gt;Crisis Psychology &amp;amp; Human Instincts&lt;/li&gt;
+      &lt;li&gt;Halloween Culture &amp;amp; Social Etiquette&lt;/li&gt;
+      &lt;li&gt;Conspiracy Theories &amp;amp; Unexplained Mysteries&lt;/li&gt;
+      &lt;li&gt;Extraterrestrial Probability &amp;amp; Science&lt;/li&gt;
+      &lt;li&gt;Music Criticism &amp;amp; Vocal Performance&lt;/li&gt;
+      &lt;li&gt;Talent vs. Catalog&lt;/li&gt;
+      &lt;li&gt;Music Industry Economics&lt;/li&gt;
+      &lt;li&gt;Historical Trauma &amp;amp; Cultural Skepticism&lt;/li&gt;
+      &lt;li&gt;Trivia &amp;amp; Science&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>Movies &amp; Cinema, Music &amp; Hip-Hop, Social Norms &amp; Etiquette</t>
+  </si>
+  <si>
+    <t>10.30.26</t>
+  </si>
+  <si>
+    <t>Transcript
+00:00:00 Jordan
+Just head to hand, I like my chances.
+00:00:01 Darius
+Just fight. Like I always say, like the strangers, if me and my girl are in the woods and I look out and it's one dude and two girls, I'm like, hey, babe, boil some water. I'm gonna go get the bats. We go, we go, as soon as they walk in, I need you to throw that hot *** water on him. And we just go, we going to fight.
+00:00:18 Jordan
+We're gonna figure it out.
+00:00:19 Darius
+We gotta sit here and wait on them to come in and kill us. Like that's stupid.
+00:00:22 Jordan
+At some point you gotta go on the offensive.
+00:00:25 Darius
+Grab some pots and pans, cut up all the lights. We got knives in here. The kitchen is full of weapons. If you just welcome to Out the Trump with Jordan and Darius. My name is Darius. That's Steve's I love me area on all socials.
+00:00:36 Jordan
+And I'm Jordan. That's Jordan B. Riding on all socials.
+00:00:40 Darius
+This is our segment we like to call. This is a segment we've titled What's on our Mind. It's officially titled where we let you guys know what's on our mind, what's going on in the world, things that we're talking about, curiosity, such and such. Starting off, this episode is releasing on 1030. Not going to let you guys know when we actually recorded it, but election day is Tuesday, federal election. Get out to vote. Let your voice be heard. Generally speaking, we, you know, like to keep it light here, but every so often, you know, the real world collides with it. So definitely get out there and make yourself be heard.
+00:01:12 Jordan
+Yes, it is important. It does matter, especially in the local level, state level, your kids, school districts, all that kind of stuff. That stuff really doesn't matter. Don't believe whatever you were told or whatever you think you believe in terms that you're too insignificant to make a difference. That is ********.
+00:01:30 Darius
+100%. Also, there's several options on the ballot that are nonpartisan. So you can actually like just Google, you know, this nonpartisan ballot. Where should who's endorsed by who and you can tell which line they run on from there. So you can print yourself a sample ballot out, fill it out at home so you know what to do. I know everyone thinks they know everything, but it can be a bit nerve-wracking in there. So if you can practice ahead of time and don't feel bad if you have to do that.
+00:02:00 Jordan
+And even like when you're in there and you're like, he wants to vote for, you're like, wait, just want to make sure that I have the right buttons. So I don't. It's nerve wracking, man. You're like, our future depends on it.
+00:02:12 Darius
+So yeah, if I get out there, you can check your voter registry. They'll tell you where to go.
+00:02:17 Jordan
+Correct.
+00:02:18 Darius
+I have, I go, I go early. By the time this airs, I've already gone. I'm usually in and out in 20 minutes.
+00:02:24 Jordan
+So yeah, for real **** ***. It's in my clubhouse. It's right there. They give you the pamphlets and stuff so you can kind of read what side you're on and stuff like that. I'd also recommend like Googling keywords based on party lines. Sometimes it sounds like it's something that's beneficial to you and it's really, really not. So just make sure to do that as well.
+00:02:43 Darius
+Yeah, it's just, there's a lot of fear mongering about how hard it is to vote. I think oftentimes people who I tend to agree with on other things almost self-defeat themselves by talking about how terrible voting is and how hard it is, and it can become discouraging for people. So I like to tell people that I never had a hard time voting. I just show up.
+00:03:03 Jordan
+No, it's actually really simple.
+00:03:04 Darius
+It's really simple. So, you know, just go.
+00:03:07 Jordan
+It's like getting a movie ticket, literally. It's about the same amount of time.
+00:03:12 Darius
+Speaking of movies, like if you wait for snacks in a movie line, it's just like that. Like it's like, Your eyes are just moving. Okay. But once it's over, you're like, I got my snacks and you're done and 20 minutes and you're good to go. So yes, absolutely.
+00:03:25 Jordan
+And also, again, not to be too heavy, but people really fought and died for us to be able to even step in that line in the 1st place. And that means something. And we owe our ancestor that ancestors that 100%.
+00:03:36 Darius
+That is not one ounce of hyperbole is actually true. And you do owe it to them. And so I'm unequivocal about that. So yeah, get on vote. So keeping with that theme, this is releasing on 1030, which means tomorrow is Halloween. So we got a couple of Halloween esque questions, kind of sort of to keep things interesting, keep it on theme. So my first topic, a couple of questions on it, but we're going to start with Which horror movie do you think you would survive?
+00:04:12 Jordan
+Yeah, that's tough because it really depends on the situation and where I'm at and who I'm associated with. Do I know the people that are the targets? You know what I mean? I feel like in horror movies it's usually just like, which, are you close with white people or not? Yeah, my answer is like, dependent.
+00:04:32 Darius
+That is true.
+00:04:33 Jordan
+So I jotted down, because it's funny, because I have some movies written down here. And there's some movies where you could make the case for literally both, depending on what you're doing. So for Scream, I wrote I'd survive because I ain't going to be in no white girl's house like that in the 90s. You know what I'm saying? And if she got a bunch of murder around her and **** I'm really not going to be around her. So there's that. Michael Myers, me and him, we have no smoke. I did not. I didn't know his mama. You know what I'm saying? I'm sorry. She was a ******. And I know his sister was trying to *** **** while he was she was supposed to come out trick-or-treating. That he got to do with me. So I'm good. Also, I can run and I'm fast. So he's not catching me. We have footage. We do have footage. We do have footage. I'm like that for real.
+00:05:16 Darius
+See them win a foot race and the next week he was cartwheeling in pools. I might have the week switched up, but there's evidence of that. is real.
+00:05:24 Jordan
+Yes. I also wrote that I would survive the movie Birds, the old Alfred Hitchcock movie.
+00:05:30 Darius
+I haven't seen that one.
+00:05:31 Jordan
+It's literally like just birds just attacking the **** out of people. Like imagine like the pterodactyl scene from Jurassic World where they just start scooping people up and dropping them in the ocean with the big swimming dinosaur type **** that but just with massive crows essentially. And I'm just gonna sit in the house so that they're not getting me. Those are some movies that I would survive. Which ones would you survive?
+00:05:57 Darius
+I have here. It's not a movie. It's a video game slash TV show, but the last of us. Caveat being if you're in a population center, you're cooked. Like if you know, if you were it's just, there's nothing you can do. But if you're like at least in a suburb and you survive like the first wave, I had to think that I would be pretty good at surviving like the, after the first wave, like the post-apocalyptic, I would call it like the Jackson commune. I'd have probably been pretty good about surviving that once you get to doing the patrols and staying disciplined and so on and so forth. It's also like my favorite, this kind of like my latest obsession is like that. It's one of my favorite like worlds ever built in video gaming history. And so I don't know, it just kind of fit in that way. Which horror movie would kill me first? Statistically, all of them. Right. But I like I have down here Freddy Krueger, I forget Nightmare on Elm String, I think is what it's called. Mostly because I don't know how anyone survived like the dude literally haunting your dreams. So yeah. And I sleep like a rock. So it would be, it'd be over for me. So which one would you be out of here in short order?
+00:07:18 Jordan
+So first of all, I just saw your Instagram or text you sent me like a little while ago. I was working on stuff. Rest in peace. One of the guys who was in final decision destination literally just like died. And then it was like, he'd survived all these like near-death experiences. And it's crazy because that was the first movie that I wrote down, which I would die because it's just so many random deaths. I can't protect myself against all those things, you know?
+00:07:41 Darius
+I was reading the list of **** that he beat before the, we won't identify it, but I was like, damn, what did you do? Are you running from death? Literally.
+00:07:53 Jordan
+That's like some Deathly Hallows type ****. What the ****?
+00:07:56 Darius
+It was like you got out of a burning car the week before. I'm like, all right now.
+00:08:00 Jordan
+Yeah, I'm like, bro, whoa. Did you find a Ouija board as a child? Like, what? How does that happen? What is going on, man?
+00:08:06 Darius
+RIP, though, man. That's a terrible idea.
+00:08:07 Jordan
+Rest in peace for real, for that's awful.
+00:08:09 Darius
+But I just was like, I was reading that like, damn, that is final decision.
+00:08:12 Jordan
+If you said it to me and I read the **** I'm like, I don't even have time to deal with this right now. I'm waiting for the podcast. I was like, what? Let's see. Sinners, I'm probably out of here because I'm going to be in a juke drunk party in my *** off and I wouldn't be paying attention to ****. And also if.
+00:08:32 Darius
+You've been in that moonshine. Yeah, man.
+00:08:34 Jordan
+I'd have been, I'd been, I'd have been out there.
+00:08:37 Darius
+You ain't think about it. Think about what's happening outside.
+00:08:41 Jordan
+I'd have been out there with trying to be in that closet with Pearling or Annie or Who's the other one? Oh my God, I'm blanking. ****. I'm tripping. But yeah, no, but any of the three women leads, I'd have been trying to spend some time with them that night.
+00:09:02 Darius
+So on my bucket list of things to do is a juke joint in some podunk southern town. That just looks like a great time.
+00:09:10 Jordan
+Yeah, you'll be in there hitting the murder man.
+00:09:14 Darius
+Yes, 100%. I look a damn fool trying it, but I'm gonna get it done.
+00:09:20 Jordan
+Yeah, I got about 60% of it. Yes, I'd be in there with sinners and I'd be in there partying and I wouldn't be paying attention either. You know what I'm saying? I mean, maybe it would have been safe because I'd have been, I'm like, hold you. Cornbread was out there, you know, playing bouncer. His wife was like that. I'd have been. Somebody, she also slept on because everybody talks about all the pretty girls in that movie and everybody just like leaves her out and I'm like, yo, dog, to look that fine while playing a slave in the field is ridiculous.
+00:09:48 Darius
+To be fair, she's in the movie all of five minutes.
+00:09:51 Jordan
+That is also true.
+00:09:52 Darius
+That is also true. A lot of people just forgot she was in the movie.
+00:09:54 Jordan
+That's true.
+00:09:57 Darius
+Most people didn't see it three times like us.
+00:09:59 Jordan
+Yeah, that is also true. Yeah, so sinners, I'm probably out of here. I'm trying to think. I'd survive weapons because I know how to avoid crazy looking people. So that lady wouldn't go have ****. I wouldn't be near her. She wouldn't get to me.
+00:10:16 Darius
+Also, both of us would have just checked the ring cameras right away. Like, hey, the kids disappeared. There's everyone has a ring camera. Can you look at them?
+00:10:23 Jordan
+Everyone has a ring camera.
+00:10:24 Darius
+Oh, they all ran through the house.
+00:10:25 Jordan
+Yeah, let's triangulate. You know, it's pretty simple. If you see 50 kids running through the street like this.
+00:10:31 Darius
+Yeah, you would think someone would have checked the ring camera by like the first 5 minutes.
+00:10:36 Jordan
+I think they should have said that movie in like the 80s. I think they would have made it a little more potent.
+00:10:40 Darius
+They should have. Yeah, that ending was trashed because the room was phenomenal with the ending sucked. It was just, and I'm not even an ending has to be great person, but it at least has to tie the like it together and it just never did. They just took the lady off and moved on.
+00:10:57 Jordan
+Yeah. What was the one we reviewed last Halloween? You're next.
+00:11:02 Darius
+Sleepy Hallow. Oh, you're next.
+00:11:04 Jordan
+I'd have survived that because half them would have survived. They just ducked.
+00:11:09 Darius
+Also just like, any sort of home invasion, like the strangers, just fight back. Yeah, right, They're always just running and I'm like, y'all are men. They might have some weapons. Okay, cool. But they don't have firearms.
+00:11:26 Jordan
+Yeah, just hand to hand. I like my chances.
+00:11:28 Darius
+Just fight. Like I always say, like the strangers, if me and my girl are in the woods and I look out and it's one dude and two girls, I'm like, hey babe, boil some water. I'm gonna go get the bats. We go, we go, as soon as they walk in, I need you to throw that hot *** water on him. And we just go, we going to fight.
+00:11:45 Jordan
+We're gonna figure it out.
+00:11:47 Darius
+We're not gonna sit here and wait on them to come in and kill us. Like that's stupid.
+00:11:50 Jordan
+It's up when you gotta go on the offensive.
+00:11:52 Darius
+Grab some pots and pans, cut up all the lights. We got knives in here. Our kitchen is full of weapons if you just are a bit intuitive, you know.
+00:12:00 Jordan
+Right. They're always in a cabinet that has a really nice kitchen too. That's if you notice that. Like, bro, everything you need right there. Yeah, but hit the head with a fire skillet.
+00:12:10 Darius
+Mine sits above my cabinet. So one time I went and grabbed it and it like fell out of my head and it hit like the edge of my head. And man, Ibuprofen, baby. It's, and that was an accident. So imagine swinging with your full force.
+00:12:23 Jordan
+Yeah. I almost knocked myself out of the gym. I was doing the, I was on the lat pull down machine and I was sitting backwards facing it so I could do, I don't, whatever it called, where you're behind your back, you know. And I just like zoned out when I was, and I just like, boom. And I was like, well, I'm gonna get up. Hopefully no one saw that.
+00:12:41 Darius
+It's, you know, well, yeah, that's dangerous. Don't do that. But yeah, it's like, I can look in my kitchen right now and see four different weapons that I would use if I was in one of those your next movies. These people just run and wait to be killed and that's stupid. They do.
+00:12:59 Jordan
+And it's funny. That's a note I wrote as well is like, well, I guess you had a question about are we too harsh on the characters in horror movies? Are they or are they actually stupid?
+00:13:09 Darius
+Yeah, it's just basically we all call them stupid and it's just like, are we unfair to them?
+00:13:15 Jordan
+I think there's something to both. I think because for one, if you're in a high stress situation, you've never been in before, your adrenaline's going crazy, this is not like an argument. This is not normal conflict. This isn't a bar fight. Someone's trying to kill you. Like when was the last time someone was in your house trying to kill you? Hopefully never. You know what I mean?
+00:13:31 Darius
+And you're going from a position of calm, watching TV and sleep, and you're defending yourself against someone who's been hyping them. Like their adrenaline is high already. And you have to get to their adrenaline level and meet their level of violence. And that's just a lot harder than people think.
+00:13:47 Jordan
+Correct. It's comfortable, you're in your pajamas, you hear the voice.
+00:13:50 Darius
+They don't call ahead of time and be like, hey, in 30 minutes we're pulling up. They just, they're just there. And you have to in an instant assess the situation and get to their level.
+00:14:00 Jordan
+And that's the way to prepare for that. So yeah, that's tricky. I will say one common theme in a lot of horror movies is I find that the key to survival is literally this simple. Minding your business. There's so many times in horror movies where it's like, people were like, oh, I heard a noise. Let me go in the woods and see what, or like, you know, like Jeepers Creepers where they like saw that weird dude and they just kept like poking around and then he killed him. You know, like it's just, if you just like mind your business in a horror movie, not 10, you're gonna be okay. Like the kids who go into the haunted house. I don't know, man. Maybe don't go in the house on Halloween.
+00:14:35 Darius
+I don't even go into the like the, trend of the haunted house excursions. Not my thing. I'm not really into that, but.
+00:14:43 Jordan
+Yeah, we can do a hayride. We can do a fall festival.
+00:14:46 Darius
+Apple picking. Dope. Great time.
+00:14:48 Jordan
+Yeah, for sure. Pumpkin patch.
+00:14:49 Darius
+100 bucks for a bag of apples. You can get the grocery store for eight, but it's about the experience. Correct. Yeah, exactly. No, I guess. I'm with you. I have it out here. We overestimate our ability to think calm in a crisis, but there is some decision making that you'll be 20 minutes into the movie long after you've known. One of my biggest ones, like I just said earlier, is the strangers where it's like they never, just they never went on the offense. And it's like, you know, you have home court advantage. You know, you have to. At some point you have to understand that these people are here to kill us. And Either we're going to make that easy for them or we're going to make that hard for them.
+00:15:33 Jordan
+Right.
+00:15:34 Darius
+If they win, they win. That's fine. They're going to do it anyway. But at least make it hard, you know. Yeah, for sure. Just don't sit there and get killed. Just doesn't make any sense to me.
+00:15:45 Jordan
+Yeah.
+00:15:47 Darius
+You want to head into your next topic.
+00:15:49 Jordan
+Yeah. So I got some Halloween do's and don'ts for the people out here. Yeah. So the first don't is actually, you would think I wouldn't say this, but Again, if you have to question if your makeup is too dark and could be perceived as blackface, just don't do it. Also, don't do blackface. There's that too. That's a big don't. If you're doing group costumes, don't have the black friend be an animal. Remember that when you're that. Remember that when you had the black girl piece Scooby-Doo. What?
+00:16:22 Darius
+How disconnected are you from blackness that you thought you were going to be the dog? Like there's nothing wrong with going out with an all white crew. Like sometimes it just happens. I get that. I'm not judging you for that. Like you saw nothing wrong with being the dog.
+00:16:35 Jordan
+About the fact that they had you. Right.
+00:16:38 Darius
+I just would love to know your what your thought process. You know.
+00:16:42 Jordan
+Yeah. It's like, or even like, there's like a lot of couples content on the internet. And there's interracial couple content. And then there's the other side where it gets real, I don't have the word for it. I don't know, minstrel show-ish or whatever, you know. And some of those hot costumes can sort of bleed into that if they're not careful. So, you know, heads up. Let's see what else I have here. Oh, yeah, for again, a couple costumes. Those are like my favorite things to see on social media during Halloween, like cute couples costumes, stuff, salt and pepper, you know, Superman and Lois Lane, whatever. But like, Maybe don't do Bobby and Whitney or O.J. and Nicole or Sid and Nancy, you know what I mean?
+00:17:22 Darius
+Okay, well, Bobby and Whitney, I think can be done tastefully. O.J. and Nicole. That's not the same thing.
+00:17:36 Jordan
+Well, no, I'm not comparing Bobby to, but just like, don't do like, okay, don't do Icantina, you know what I mean?
+00:17:45 Darius
+Oh, yeah, 100%. Don't do Akantina. Don't do. Well, yeah.
+00:17:49 Jordan
+Don't do Rihanna and Chris.
+00:17:50 Darius
+You know, if there has been documented domestic violence between the couple, which I guess is Bobby and Whitney, just that, you know, you can just, yeah, if when you put it on.
+00:18:03 Jordan
+Maybe do Whitney and Robin. That might be a safer choice. You know, we all inclusive, baby.
+00:18:12 Darius
+Yeah, you know. I read Robin's biography and she outed Whitney Houston, basically.
+00:18:18 Jordan
+I say, yeah.
+00:18:20 Darius
+Posthumously out of there. I don't even know. Is that appropriate? I guess neither of us can make that decision, but it feels a bit inappropriate.
+00:18:27 Jordan
+But I believe so.
+00:18:30 Darius
+Yeah, I have on here regarding costumes. Make your costume recognizable. If I have to Google it, if you have to have a picture with it. It's not the end of the world, but it kind of defeats the purpose if people can't just tell right away what the costume is. And like, it's like, I was the cameraman and saw, it's like, no one knows what that is.
+00:18:51 Jordan
+Oh yeah, I saw that, yeah, I saw that.
+00:18:53 Darius
+I think no one's gonna know what the **** that is.
+00:18:56 Jordan
+Correct. So those costumes, you make those, like you make a skit on your phone and then you like post those. You don't go out with those because again, if like that's just not. It's hard to read unless you're doing it as a group and then everyone kind of piece together. Oh, you're such and such, you're such and such, you're such and such. That makes sense. But yeah, I agree with you on that one for sure.
+00:19:13 Darius
+Regarding kids costumes.
+00:19:15 Jordan
+Yeah.
+00:19:16 Darius
+The costume is for the kid. It's not for you. So no Craig and Day Day. Like that's not your four year old has never seen that movie.
+00:19:24 Jordan
+Never seen Friday.
+00:19:25 Darius
+You know, like Halloween is for them. not necessarily, but their night is for them. Trick or treating is for them.
+00:19:34 Jordan
+Get that kid a Spider-Man costume.
+00:19:36 Darius
+Yeah, he wants to be Superman. Like, you know, he wants to be Iron Man. He does not want to be Smokey from Friday. Right.
+00:19:45 Jordan
+That's not cute looking back in his graduation slideshow.
+00:19:50 Darius
+Speaking of kids, make your costume venue appropriate. I have no problem with sexy nurse costumes or devil costumes. Why are you wearing that down to the school for your kids event?
+00:20:04 Jordan
+Right.
+00:20:05 Darius
+That's for Saturday night on Glenwood. That's not for the neighborhood block party. Right.
+00:20:10 Jordan
+Don't go as Dexter's mom to or Miss Elastic or Elastigirl to the thing.
+00:20:17 Darius
+There's a costume for the neighborhood block party where you know, I guess kids don't trick or treat anymore. They just kind of like Keep them in the neighborhood and they go to door to door.
+00:20:25 Jordan
+Yeah. And the trunk or treats are big now, too.
+00:20:27 Darius
+That's a costume for that. And there's a costume for the function.
+00:20:31 Jordan
+Correct.
+00:20:32 Darius
+You can wear this one to the function, but you can't wear the function costume to the neighborhood.
+00:20:36 Jordan
+No, no, no, no, no. One has flexibility. One does not.
+00:20:39 Darius
+Correct. You know, I've seen some some costumes at gatherings where children are, and I'm like, you know, you're wrong for that. I appreciate it. There are children here. Let's, save it. Like, we are going out. Don't get me wrong. I'm not one of those. We too over this. No, you go out on Halloween. Have a great time. But like there's a costume for the daytime and there's like 10 o'clock, the flip switches and we can do the evening costumes, you know?
+00:21:12 Jordan
+Correct. Yeah, that's a good one. Oh, also don't Halloween on an empty stomach. Make sure to eat something heavy, preferably protein. and rice or something before you go out there and Halloween to your best ability, because you'll pay for it the next two days in November.
+00:21:31 Darius
+Also eat before you put on the costume, trying to eat with a costume on, pain in the ***. It's a little logistical, you know?
+00:21:39 Jordan
+Yeah, make sure you can text and like use your phone and stuff in your costume, **** like that. I remember I went to Miles Morales one year and I had to have, I was at the bar and I had to have them like cut the fingertips off some of the gloves so I could use my phone.
+00:21:50 Darius
+Also props. Bouncers is not going to let you in with a shield and a sword. Leave that in the car. No bouncer worth his ***. Yeah. You argue with him and you're dead wrong. You can't come into the club with a sword. You know you can't. Like just leave it in the car.
+00:22:06 Jordan
+If your uniform has any sort of weaponry, especially that look real, do not walk around with those, please. Especially if you look like us. Come on, y'all.
+00:22:14 Darius
+You know, You have to plan for the world you live in, not the one you wish existed. Correct. Yeah. Can't be walking around with toy firearms after hours or period. But generally it's a really bad idea. Yeah.
+00:22:31 Jordan
+You want to make sure everybody feels safe and the rainbow costume might be cool, but keep the just wear the vest to the party or to the downtown **** and then leave the props in the car.
+00:22:42 Darius
+Do be a good sport about it. I'm not even a person that dresses up, but just don't be a Grinch. Like have fun. Even if the costume is stupid, tell them it looks great. Pretend like if they're explaining something and you don't get it, just pretend you do. Just play along, be a good sport. It's one night a year where, well, it's one of the few nights a year where adults just get to dress up and be silly and just go along with it.
+00:23:06 Jordan
+Right, exactly. That's the appeal of Comic-Con and stuff.
+00:23:10 Darius
+Yeah, 100%. You know, I've seen situations where someone is explaining the costume to me. I mean, see how it was. Someone would explain the costume to me and I didn't know what the **** they were talking about, but I was like, man, that **** fire. Yeah. Oh, it looked just like the movie. What movie was that? Oh, I did see that. And just, you know, they might even know you ************ but it's just like one of those things that's just a social contract. So right. Keeping with that. You have any other ones?
+00:23:34 Jordan
+I think that's all I had for that. topic, at least from what I wrote down. You got anything else?
+00:23:42 Darius
+No, I didn't. I think we covered all of the bases there. So somewhat horror related, but kind of not. We're kind of stretching the definition here a little bit, but conspiracy theory rankings. So I gave you 4 categories. Aliens, kind of self-explanatory, historical mystery, government conspiracy, unexplained experience, your favorite one of these conspiracies and which rank them by how much you actually believe them to be true. So start with #4.
+00:24:11 Jordan
+Whatever you want.
+00:24:13 Darius
+So it's your category, your favorite in each, and then you rank them by which is least believable to most believable.
+00:24:20 Jordan
+Okay, so unexplained disappearance, I think, was it the one Amelia Earhart was lost in like the Bermuda Triangle or something like that? one's pretty funny. Next for government, I think it's, as I say, the crack epidemic was imposed by the government.
+00:24:45 Darius
+It was no fault when Reagan gave me the visuals.
+00:24:48 Jordan
+Yeah. History, historical conspiracy, I'd say that Walt Disney is like frozen at Disney World, like his body is frozen at Disney World, or is it just his head? One of the two. I think maybe his, but his corpse is like frozen at Disney World. There's a theory that it's frozen somewhere underground there.
+00:25:09 Darius
+But I can see it.
+00:25:11 Jordan
+Yeah. And then the alien-esque one or whatever. I'd say probably, there's a theory that maybe the dinosaurs actually didn't have scales. They had feathers. I think that's pretty cool, the idea of a T-Rex just having feathers and looking like Big Bird.
+00:25:36 Darius
+I think that's actually confirmed that dinosaurs had feathers. And basically, I don't know about all, but basically all popular depictions of them are just wrong. They all look like big.
+00:25:48 Jordan
+Yeah. Which I think is actually pretty ******* dope. My favorite of those four, I'd have to say The idea of the government moving weight, it's pretty funny. I find it. Yeah, well, that's the thing. Cause like a lot of, so a lot of the historical and government conspiracies that we've kind of been inundated with are like things that they would do or have done or could do to us from a cultural perspective. And none of that is unbelievable because of what they've done to us. So it's like, you know.
+00:26:27 Darius
+I'd be getting on black folks for being conspiratorial, but I am. I am a bit empathetic and understanding because our history reads like a conspiracy theory.
+00:26:36 Jordan
+Yeah, imagine if you took an alien, no pun intended, came down here, and you were like, hey, so these white men went to another continent, took people from there, tripped them with their name, their language, their culture, their religion, their music, everything, brought them to another land, enslaved them, changed everything about them, told them about this thing called Christianity. while they were doing the most heinous things ever to them, and then told them that they were the problem once they got free, that they were lazy, that they were dirty, that they were all these things. The alien would be like, but it's not true. And history shows that everything, that they are the bad guys.
+00:27:17 Darius
+And be like, after the fact, after all of that, when it was time for them to vote, they were like, you can vote if you can guess how many beans are in this jar.
+00:27:24 Jordan
+Right.
+00:27:26 Darius
+They made you guess the beans. Yes, literally, the beans. Like if you showed them a literacy test to vote, you'd be like, this is, that's not true. Ranking from least likely to most likely, I have government conspiracy here. I don't believe MLK was having all them affairs. If they had the goods, they'd let us know.
+00:27:47 Jordan
+You think that was the CIA? I just I kind of I'm with you, but I think he was cheating. I don't think it was as rampant as they act like it was.
+00:27:56 Darius
+I mean, to the extent that any prominent, high social capital man is confined to cheat. Sure. But just why don't we have like, we would have the goods by now?
+00:28:10 Jordan
+We'd have the CIA photos and the.
+00:28:12 Darius
+Photos, the tapes, he was one of the most surveilled men on planet Earth.
+00:28:17 Jordan
+Yeah.
+00:28:17 Darius
+And we haven't seen anything. It just doesn't strike me as Like that's why habit is least because it's entirely believable that a very prominent high social capital man who traveled A lot.
+00:28:28 Jordan
+Traveled A lot.
+00:28:29 Darius
+It's like that's why it's least.
+00:28:30 Jordan
+There's no cell phones, you know, it's.
+00:28:33 Darius
+But if it came out that J. Edgar Hoover was just planting this **** I'd believe it too.
+00:28:37 Jordan
+Well, he's one of the worst humans of all time. So absolutely.
+00:28:41 Darius
+Second from the bottom, historical. Yeah, I got here. Yeah, historical mystery. It's called the Lost Colony of Roanoke, Virginia, but it's actually located in Outer Banks. It's basically this established settlement in the 1500s that just disappeared. And no one ever knows why. They said it was a settlement and then the people who came behind them went to them and like the whole settlement was taken down. And there was just like one word written on a tree, I guess, that said like Croatian, or at least by today's pronunciation, who knows what they actually meant. And it's never been explained. And it's like, it couldn't have been a fire. It couldn't have been a military occupation because there'd be dead bodies. There'd be nothing to that. And the working theory is that they just split up and assimilated into some native tribe. And they just, they just, you know, were lost to history. They just went and joined another tribe, which is entirely possible in the 1500s. So next up, unexplained disappearance. The most famous one in true crime is Maura Murray. Lady. I forget the city, but she was just driving in this remote area and in a 10 minute window. Well, she crashed her car and then she found someone and she called for help. And then 10 minutes later, she vanished without a trace. And no one ever is explaining that like it was snowing. And so like there's a couple of theories that maybe she just walked into the woods and got lost and hypothermia killed her. But 20 years later, we have no bod</t>
+  </si>
 </sst>
 </file>
 
@@ -10990,7 +11402,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11017,7 +11429,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -11034,6 +11445,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11353,7 +11768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -12207,7 +12622,7 @@
       <c r="D43" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="E43" t="s">
         <v>334</v>
       </c>
       <c r="F43" s="11" t="s">
@@ -12246,6 +12661,23 @@
       </c>
       <c r="F45" s="11" t="s">
         <v>331</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>335</v>
+      </c>
+      <c r="B46" t="s">
+        <v>336</v>
+      </c>
+      <c r="C46" s="10">
+        <v>46325</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -12260,7 +12692,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -12899,6 +13331,20 @@
         <v>333</v>
       </c>
     </row>
+    <row r="46" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>335</v>
+      </c>
+      <c r="B46" t="s">
+        <v>336</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D40" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
     <filterColumn colId="3">

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FF6478-0F5D-4CD3-BAC4-F64DEA242FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59AC0182-1F2A-4F86-AE9D-638BCCD46CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="30660" yWindow="16080" windowWidth="24240" windowHeight="13020" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="342">
   <si>
     <t>youtube_link</t>
   </si>
@@ -11313,6 +11313,9 @@
 00:28:41 Darius
 Second from the bottom, historical. Yeah, I got here. Yeah, historical mystery. It's called the Lost Colony of Roanoke, Virginia, but it's actually located in Outer Banks. It's basically this established settlement in the 1500s that just disappeared. And no one ever knows why. They said it was a settlement and then the people who came behind them went to them and like the whole settlement was taken down. And there was just like one word written on a tree, I guess, that said like Croatian, or at least by today's pronunciation, who knows what they actually meant. And it's never been explained. And it's like, it couldn't have been a fire. It couldn't have been a military occupation because there'd be dead bodies. There'd be nothing to that. And the working theory is that they just split up and assimilated into some native tribe. And they just, they just, you know, were lost to history. They just went and joined another tribe, which is entirely possible in the 1500s. So next up, unexplained disappearance. The most famous one in true crime is Maura Murray. Lady. I forget the city, but she was just driving in this remote area and in a 10 minute window. Well, she crashed her car and then she found someone and she called for help. And then 10 minutes later, she vanished without a trace. And no one ever is explaining that like it was snowing. And so like there's a couple of theories that maybe she just walked into the woods and got lost and hypothermia killed her. But 20 years later, we have no bod</t>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=FOrbaezcSh0&amp;t=27s</t>
+  </si>
 </sst>
 </file>
 
@@ -11402,7 +11405,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11429,6 +11432,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -11445,10 +11449,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12642,6 +12642,9 @@
       <c r="D44" s="4" t="s">
         <v>324</v>
       </c>
+      <c r="E44" s="12" t="s">
+        <v>341</v>
+      </c>
       <c r="F44" s="11" t="s">
         <v>325</v>
       </c>

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59AC0182-1F2A-4F86-AE9D-638BCCD46CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C860ED7A-6A1C-46B1-AB60-03539840C8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30660" yWindow="16080" windowWidth="24240" windowHeight="13020" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="343">
   <si>
     <t>youtube_link</t>
   </si>
@@ -11316,6 +11316,9 @@
   <si>
     <t>https://www.youtube.com/watch?v=FOrbaezcSh0&amp;t=27s</t>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=jWmkgXJXnDQ&amp;t=1s</t>
+  </si>
 </sst>
 </file>
 
@@ -12642,7 +12645,7 @@
       <c r="D44" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" t="s">
         <v>341</v>
       </c>
       <c r="F44" s="11" t="s">
@@ -12661,6 +12664,9 @@
       </c>
       <c r="D45" s="4" t="s">
         <v>330</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>342</v>
       </c>
       <c r="F45" s="11" t="s">
         <v>331</v>

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C860ED7A-6A1C-46B1-AB60-03539840C8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFD25D7-AE8E-4C81-99B7-AF557F1CAB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30660" yWindow="16080" windowWidth="24240" windowHeight="13020" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="353">
   <si>
     <t>youtube_link</t>
   </si>
@@ -11319,6 +11319,637 @@
   <si>
     <t>https://www.youtube.com/watch?v=jWmkgXJXnDQ&amp;t=1s</t>
   </si>
+  <si>
+    <t>Tourist Trap Scams, Mars Flexes, and Tupac Biographies</t>
+  </si>
+  <si>
+    <t>10.20.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transcript
+00:00:00 Jordan
+But I mean, I really thought about this and I've been seeing a lot of posts from black people about how they haven't always had great experiences being in Europe traveling and stuff. So I'm going to say **** it and go to Mars. I did some great pictures. It'll go really cool on my Instagram. That's definitely going to be my profile picture. I'm going to be vlogging up there.
+00:00:20 Darius
+Welcome to Out the Trunk with Jordan and Darius. My name is Darius. That's these all up in the area on all socials.
+00:00:26 Jordan
+And I'm Jordan. That's Jordan to be writing on all socials.
+00:00:28 Darius
+This is our segment we've titled What's On Our Mind, where we let you guys know, well, what's on our mind, what we saw on the internet, what, you know, the things that we want to discuss. And so I have one quick intro that I, so a lot of people did it and you did it to people. So the Thanksgiving thing on that's going on like this or that.
+00:00:52 Jordan
+Yeah, this or that, yeah.
+00:00:53 Darius
+Why do people struggle with instructions?
+00:00:57 Jordan
+First of all, because it's my phone, I do what the **** I want.
+00:01:01 Darius
+And I know it doesn't matter. It's some stupid internet thing. But of course we all want everything.
+00:01:05 Jordan
+If you're just going to pick them both, then I feel, I hear you. So I think my thinking was it's one of those things where like, I really truly love both. So that's why I do it with the select few of those.
+00:01:19 Darius
+Everyone did it though.
+00:01:21 Jordan
+I know. And I think, so I think the ones I selected, I think I selected both for cranberry sauce over cornbread. And I was like, I don't want people to think I don't love cornbread because that's anti-black. So I was like, let me select both.
+00:01:33 Darius
+Well, those people would not be able to read because it does not say choose which one you like. It says which one is better. And so it's entirely possible to like one food more than another and still like the other food.
+00:01:46 Jordan
+That is true. I think the thing too is because it was not specific in terms of which kind of given food. Like it was cranberry sauce, but it was like the berries as opposed to the congealed kind. I like both, but I mean, so there's that too. Like I prefer a cornbread casserole to cornbread, but I like cornbread also.
+00:02:06 Darius
+I am partial to cornbread dressing. I don't actually like just like, I mean, okay, I eat, I don't like bread like that. So I like cornbread, but within the bread family, it's fine. But just generally speaking, Really. It's like a vehicle for a sandwich is fine. Yeah. Or a vehicle for.
+00:02:26 Jordan
+So you don't like bread by itself is what you say?
+00:02:28 Darius
+Yeah, just like when you go to the restaurant and just put bread and butter on the table. I'm nibble at it, but I could live without it. It's not a big deal to me.
+00:02:34 Jordan
+Got you.
+00:02:34 Darius
+Okay, I hear you. But like if, you know, it's charcuterie board, you need something to put the meat and cheese on. You know, it's not that I don't like bread. It's just I don't just eat. I don't look forward to bread in that way. So.
+00:02:46 Jordan
+No, I get you.
+00:02:47 Darius
+You know, I know that makes me a little weird, but heading into a topic, I must I have a confession. All right. So I was recently in Philadelphia and I think I told my first Internet lie. Yeah. I went and got a tourist trap cheesesteak and I posted that this was good. It was not good.
+00:03:13 Jordan
+And you felt like a ******* hoe for mine, didn't you? Yeah, because I looked at it. I'm like, there's no way that's worth 100. There's no way you ate that and thought that's worth a pair of shoes.
+00:03:23 Darius
+I had four bites of it and politely asked for my check so I can go watch some basketball.
+00:03:30 Jordan
+And this is Mr. All restaurants suck.
+00:03:33 Darius
+I mean, they do, but I as far as restaurant food while I was there, I had good food, but it was always like during the day at a food hall or something like that. But my night reservations for dinner, 0 for three.
+00:03:48 Jordan
+That's crazy.
+00:03:49 Darius
+It's just restaurants, man. I don't know what's going on with them. These are places that I'd been before and that were good. Yeah. But yeah, I got it down or. Yeah, just I don't know. I went to a restaurant. I'm not going to name them just because I don't like doing that. But it was an Italian restaurant. It was an Italian restaurant and I went in 2019 and I literally ran back and it was phenomenal. I got a shrimp scampi and a Sunday gravy, which is Italian's way for saying spaghetti and meatballs, basically.
+00:04:23 Jordan
+Okay, got you.
+00:04:25 Darius
+And you know, the bread that you get for free with it. And what amazing meal in 2019, one of the best Italian restaurants I'd ever been to. This time, straight mid. The shrimp scampi straight out of the sea pack, like the freezer bag that's already peeled in devein that has no flavor. There was like no natural ocean seafood flavor in the shrimp. It was just straight up sea pack shrimp drowned in butter, garlic butter. And look, I'm not opposed to bland shrimp drowned in garlic butter, but that's not exactly what a shrimp scampi is supposed to be. And the spaghetti just tasted like Tuesday night at mom's house. it just was fine. Okay. Yeah. like your mom got off work and she had to put spaghetti, had to cook something. So she made spaghetti and that's what it tasted like. It was.
+00:05:13 Jordan
+You hear that, Miss Thomas?
+00:05:14 Darius
+Yeah, I mean, you know, there's nothing wrong with it. just tasted like weeknight spaghetti that you got to put up. You got to just, you got to some kids got to eat, got to put some on the table. And that's just what it tasted like. And, you know, so my question to you is, what is have you ever fallen for a tourist trap and what was it?
+00:05:41 Jordan
+Tourist trap, I'm trying to think, you know, okay. They almost got me in, I think I was in Jamaica. And so I don't know if you've been Jamaica on a cruise.
+00:05:53 Darius
+I was there for like six hours. You get off and you walk.
+00:05:55 Jordan
+Gotcha. Okay. the thing about when you see vendors, don't tell them your name because they'll carve your **** in there. And so I was, I knew that, but I was walking through the, and there's like people, you just try to say no to everybody really quickly. it's like, imagine, I mean, they're not homeless, but it's like the aggression is that of like a panhandler, you know? And so you're just like turning down panhandlers left and right metaphorically. And the guy was just like, oh, hey, like, how long are you going to be here? Or is this your first time here? Something like that. I answered like a simple question. Mom was like, no, don't say anything. And the funny part is she said my name when she said, no, don't say anything. So I'm like, could have actually carpeted right then and there and not have been screwed. But I think that's probably the closest I've been gotten, closest I've gotten to being got with a tourist trap.
+00:06:46 Darius
+Yeah, man, it's I have a beef with all the influence who said that sandwich was good. There's no way they were being paid to say it. There's no way they're being truthful in their assessment of that sandwich. Now I got some scallops that were phenomenal. Like some diver bay sea scallops. But and I had a shrimp cocktail, but like you can't **** that up. It's literally just shrimp and cocktail sauce. But I had a phenomenal Manhattan there. But all in all, a $230 tab, almost $300 after tax and tip. And it was a straight up scam. So that was the first lie I've ever told on Instagram when I said that steak was just okay.
+00:07:31 Jordan
+Got you. know what? I felt got this weekend actually. I went downtown Raleigh and I bar hopped. I had a friend in town. We had a couple people together. So we, you know, bar hopped and ****. And it just felt like the prices just kept going up. Like it was just like, what? Yeah, man, I don't know what happened. Actually, no, I was at UNCG's homecoming, their black party they do every year. Their bar automatically included 20% gratuity. Yeah. Well, they tell you when they do it, but you still kind of feel a little bit like, you know, taken aback by it, you know?
+00:08:07 Darius
+Yeah, I popped into a sports bar to watch, you know, it was an NBA opening weekend and I'm in a hotel, so I don't have I'm not, I don't have about apps, I don't have nothing. So nothing, yeah. Most of the games are on peacock and **** so you can't even watch them on the TV, TV. So I popped to a sports bar in Chinatown to watch one of the games, I forget the game, and I got a beer and a shot. Coors Light shot, and it was $24, which I thought, hi, but you're in Philadelphia, you're downtown. Didn't know it included gratuity. So then I put another 10 on top of that. So I ended up paying $34 for a beer and shot. And then when I, so I knew, I didn't, I was like, I felt like I got, but didn't know. And then when I, because I had tapped out, And I had started talking to somebody and decided to stay for an extra drink. And I got another beer. And he explicitly told me, like, there's a tip on this. I think he almost felt bad. He was like, just so you know, there's a tip on the tab already. It sort of gave me the permission structure to not tip a second time. And I appreciate him for that because I just, you know, he didn't have to do that.
+00:09:17 Jordan
+So you'd have paid 70 bucks for $10 worth of alcohol.
+00:09:23 Darius
+Traveling is got to have your bag right for that. That's not.
+00:09:27 Jordan
+Yes, yeah, for sure. Absolutely.
+00:09:30 Darius
+Even if it's like you think you can skimp it, but you can't because I mean, my morning life is $8. I went out for breakfast at a diner. Also like You're in downtown. So it's like you're playing going out prices for your whole day. Right. When you went downtown, you were just there. Your regular day was spent under normal expenses. So you ate normal expense. But I'm doing breakfast, lunch, dinner, coffee, snacks, all that on downtown pricing. And it'll run you.
+00:10:05 Jordan
+Yeah.
+00:10:06 Darius
+But yeah, man, I got got, but I had a good time in Philly, man. That was, as the kids say, Philly owes me nothing. I had a blast. The only down, the only thing was that scam, the Barclay, I'm going to name the restaurant, but the steakhouse I went to where I got the $150 cheese steak, there's only one of them. You can Google it. It's out in them, but it's a scam. I'm sure their regular steaks are great, but everything else I had there was good. But that menu item in and of itself is a scam.
+00:10:34 Jordan
+Yeah, if I'm going to pay that much for a cheese steak, I need to have gold in it, literally. Like there's that restaurant that has gold and gold flakes in their food.
+00:10:41 Darius
+I mean, it better have that. The ingredient list justifies the price point, but it just didn't taste good. And at the end of the day, that's what matters. Right. So let's go on to the next topic, man. This is on you blind spots.
+00:10:57 Jordan
+Oh yeah. So I was texting a friend like last week, maybe a week or two ago, I can't remember. And she was telling me how there's that Beach Boys song, about going on vacation. It was like Aruba, Jamaica. I want to take you to that song. And she was saying that when she was a kid, she thought it was taking to the Poconos, but it's actually Kokomo. I think it's like a beach place or something like a tropical location. And I was like, yeah, I thought it was Kokomo too, or that they alternated, you know, it's got me thinking of like **** that I thought was one thing that meant something totally different. Like the phrase show tunes. Like, women say like, or people in TV shows in the 90s would say like, that dude's probably gay because he liked show tunes or whatever. I always thought show tunes meant theme songs. So I was like, what's wrong with liking the Fresh Prince song? Like, I didn't, you know, I didn't get it. I didn't realize it meant songs from Broadway.
+00:11:46 Darius
+Oh, yeah. I kind of knew that was theater based. my one of my, I guess one of my famous ones. that Jamie Foxx twisted Kanye West song.
+00:12:00 Jordan
+Yeah. Slow jams.
+00:12:01 Darius
+Yeah. I thought it was a little a needle instead of a little Anita. Yeah.
+00:12:07 Jordan
+That was my heroin.
+00:12:10 Darius
+I guess I don't. It never made sense. And Anita Baker fits with the theme of it. But, you know, people is so. To stall us out. We, have Googled the lyrics on our phone. We didn't have Spotify with the lyrics.
+00:12:24 Jordan
+Yeah.
+00:12:25 Darius
+And I maintain that's cheating. Not learning the lyrics on your own and Googling them.
+00:12:30 Jordan
+Oh, well, yeah.
+00:12:30 Darius
+That's not, that's not how that, that's cheating. It's like doing the cliff notes on the book instead of reading the book.
+00:12:36 Jordan
+Yeah. I do use Shazam to find the name of the song so I can add it to my phone. I do that all the time with Siri and Alexa for sure. Yeah, I'm trying to think of like other like knowledge blind spots like that. Oh, like, you know, this is the phrase, have your cake and eat it too. Yeah. Apparently it's actually, you want to have your Kate and Edith too. Meaning two women, like their names.
+00:13:04 Darius
+I understand why they made that a little bit more generic. Get the same sentiment across, but I understand why they went with a more generic one. Another one a lot of people mess up is, what is it? Couldn't care less, which means you do care. Or it's I could care less, which means you do care, but it's actually couldn't care less. Correct. That's one that I cleaned up. I know for the longest I pronounce hyperbole, hyperbole, because I'd only ever read it. In the written text, yeah. I embarrassed myself quite famously by saying that word amongst, like just, I was in my early 20s and I said it and people were like, what the **** are you talking about? I was at a party. It was quite embarrassing. I still get **** about that. So do you have any other ones?
+00:14:01 Jordan
+Oh, for the longest time, I did not know Kansas City was in Missouri. Not for a long time. I think I was a teenager when I realized it. Like I was talking to somebody, I was working at a grocery store and somebody was talking about Kansas City or something like that, whatever. And had I ever been or whatever go. And I was like, what would I go to Kansas for? And they're like, you know, it's in Missouri, right? And I was like, get the **** out of here. And they're like, yeah, it's in Missouri. But so I didn't know that for until I was like 16 or 17. Yeah.
+00:14:25 Darius
+That's also pretty stupid though. Like why is it?
+00:14:28 Jordan
+That is dumb as hell. Why put that there?
+00:14:30 Darius
+I'm sure there's a historical reason.
+00:14:32 Jordan
+Yeah.
+00:14:33 Darius
+This is a bit obscure. Most people would, this isn't like something that most people had right. But it was not until Hamilton came out and the character in the first act, Marquita Lafayette. I didn't know every Lafayette St. was named after that dude. I just thought that was like, but he was a Revolutionary War figure from France and he, fought on our behalf and went back to France. And yeah, every Lafayette Street, I mean, probably not everyone, but when you see a lot, most of it's probably named after Marquita Lafayette, the you wouldn't know people would know him as the Hamilton character. So gotcha.
+00:15:08 Jordan
+Okay.
+00:15:09 Darius
+Yeah, that's. but that's one that like nobody knows I say yeah that's not a I don't feel bad about not people I'm sure mad.
+00:15:16 Jordan
+People thought like it was just a bunch of Creole that did a bunch of crazy ****.
+00:15:20 Darius
+I mean that might fit the bill French French war fighter might have been Creole crazy did you have any other ones?
+00:15:33 Jordan
+Trying to think no off the top of my head hmm Yeah, that's it. I think pretty much. Those are the two biggest two main ones that I had, at least from like growing up and **** Yeah, you got any more?
+00:15:51 Darius
+No, I did Google famous misheard lyrics and all the responses are like predominantly white bands. I don't even know what the **** is Eiffel 65. So.
+00:16:01 Jordan
+Is that a great band or a song?
+00:16:03 Darius
+That's the name of the band and the song is Blue. And it's misheard is I need a guy or I believe I will die. But it's actually I'm blue. Oh, I'm blue.
+00:16:17 Jordan
+Okay.
+00:16:18 Darius
+Yeah. You know, I went to an integrated school, so I heard a lot of these.
+00:16:21 Jordan
+Yeah, I just didn't know what they were.
+00:16:23 Darius
+So yeah. All right. We're going to head over into a random hypothetical. learn how to spell that. And so you win an all expense paid prize, right? You don't have to worry about a time, but you have to pick between one of them. You get to do 10 minutes walking on the surface of, we're gonna say Mars, because people have actually been on the moon. It only makes sense if you're going to some place no one's ever been, right? So 10 minutes walking on the surface of Mars or an entire living anywhere in Europe with a $2,000 monthly budget, stipend, whatever. Which would you choose?
+00:17:04 Jordan
+I mean, even with the currency exchange rate, I don't know how much like balling out I could do in Europe off 2 grand. But I mean, I really thought about this and I've been seeing a lot of posts from black people about how like they haven't always had great experiences being in Europe traveling and stuff. So I'm going to say **** it and go to Mars. I did some great pictures. It'll go really cool on my Instagram. That's definitely going to be my profile picture. I'm going to be vlogging up there.
+00:17:31 Darius
+You only get 10 minutes, but you can be like, what? Oh, you went to Thailand? I left the planet.
+00:17:36 Jordan
+Yeah, **** you.
+00:17:40 Darius
+I literally left the planet.
+00:17:42 Jordan
+What's that song? You see me? I'm on some out of town ****. Yeah.
+00:17:46 Darius
+Literally out of the planet.
+00:17:47 Jordan
+Yeah, that's beneath my pay grade. I don't even do that ******* earthly human ****.
+00:17:51 Darius
+You're traveling on a plane. I was on a spaceship.
+00:17:55 Jordan
+Yeah.
+00:17:57 Darius
+That's pretty dope, actually. That's an ultimate flex.
+00:18:00 Jordan
+No, I did ask. It's like, oh, you went to Vegas. Cool. I went to Mars.
+00:18:04 Darius
+Where I went, you literally cannot buy. It does not matter what you do for a living.
+00:18:09 Jordan
+Nothing.
+00:18:09 Darius
+I went someplace you cannot purchase.
+00:18:11 Jordan
+Correct.
+00:18:13 Darius
+I'm not that adventurous, man. I'm going to Europe. Although two grand a month is not actually very much.
+00:18:20 Jordan
+It's like lunch money.
+00:18:22 Darius
+Honestly, I think that's what you pay in food. But Yeah. I looked into doing a little overseas travel next year. And yeah, I don't know. It just, it's just that's what I would pick if I were choosing between the two, because while it is Timon is doing something no one else has ever done, I just I feel like I would just enjoy it more. Yeah. you know, just touring Europe for a month or a year, basically.
+00:18:54 Jordan
+Yeah, I was going to do a gap.
+00:18:55 Darius
+Different. You can do the different, you know, go to different countries and do different things. And that just sounds like more my speed, you know, so. All right. So we got you logged in as heading to Mars and you got me logged in as gallivanting across Europe on a shoestring budget. So we heading into your topic, man. It's kind of self-explanatory. So what you what you got?
+00:19:24 Jordan
+So I just finished there's a new show called Carrie on Amazon. It's a new adaptation retelling of the Stephen King novel called Carrie. It's really, really dope. They casted a lot of actors that at least I had never really seen before. I won't say like no names, but I hadn't seen any of their work before. Everybody bodied it. I think it's like 8 episodes. So it's pretty quick to get through. And it's I think now is kind of a perfect time for that kind of show because of the advent of social media and cyber bullying and just, there's a quote I heard where it's like, back in the day, when you were a bully, you had to see like the look on somebody's face when you like hurt their feelings or just did something really bad to them, or abuse them or whatever the case may be. Whereas now you can just type and go on about your day and you know, who knows how that impacts somebody, whatever, you know. So I thought that was a really cool twist. Quick interjection.
+00:20:18 Darius
+Cyberbullying is fake. Just turn your phone off. Like it's when you were bullied at school, you couldn't leave school. Like you were constrained, like, but cyberbullying is 100% fake. You could literally just log off.
+00:20:30 Jordan
+Well, true. But so in this situation, whether they all go to school, it's a small town that everybody knows each other. So it's, you know, if I spread this rumor about you, everybody knows it and they all like, it's just a little more.
+00:20:42 Darius
+Well, that's not just that's not cyber bullying. That's no, I know.
+00:20:45 Jordan
+But I'm saying you can initiate the rumor via the Internet goes out quicker and then it spreads to the town via word of mouth.
+00:20:55 Darius
+Fair. But generally speaking, cyber bullying is fake. Log off. Once you once you put your phone in your pocket, it doesn't even exist anymore. You could just go about the world and doesn't matter. So sorry for interrupting you, though.
+00:21:09 Jordan
+And so also it's a have you seen the movie Chronicle?
+00:21:13 Darius
+I have not, no.
+00:21:13 Jordan
+Okay, so it's really, really good. It's got a kind of a feel of that where the Carrie is telekinetic. So you have her learning her powers and kind of coming into terms with herself and standing up to the, you know, people that do her harm, which is the payoff is so great because the **** they do like in the movie, the original movies in the books, they do bad **** of course, but Christian was at the prom scene. In this show, the prom scene is just like the needle in the haystack, not to spoil anything, but like the **** that this one kid does to her is like otherworldly evil. You know what I mean? Like on some, like I can't even think, like if Darth Vader was a teenager type **** like that's kind of the type of stuff she does. I want to give it away, you know, for the audience. But so that was really cool. It's also a lot about like parenthood and the way that parents try to protect their kids and the positive and negative effects of that, which I think is really dope because you don't always see the cons to that in film and television these days. Yeah, it's just a really good show. It's there's no filler episodes. There's no like ********. There's no, oh, we're going to put two episodes here just to get to the finale. Correct. Exactly. Like it's a great way of breaking down each character, showing their family life and how they got the way they are, you know, in a way that's not like a cheap villain backstory. You see in some movies sometimes, you know, yeah, really good show. Definitely recommend it for sure. And it's again, the message of the show is not to take the high road, so to speak, which I really like.
+00:22:49 Darius
+Nice, nice, nice. Have not been watching much TV at all outside of sports just because yeah, just not a time for it. But I have been reading You know, as you know, I've been offline for two plus weeks now and it's amazing how quickly, how much, how quickly you get productive again. But I was recently in Philadelphia and I wasn't going out while I was there. I was, you know, in the room by 11 ish. And so I'd have plans at like 10 that morning. And so I wake up at six, 630, go get some breakfast and then either eat breakfast or come back to my room and I'd have like two hours, sorry, I'd have like two hours of time before I had to, whatever ticket I had that day, the museum or whatever. So I would just read a book on the Kindle and I finished two books, 2 Jeff Perlman books, his Tupac book and his book on the Kobe Lakers, the first one, the Kobe Shaq Lakers. And so... Do you read circus? Yes, Yeah, that one's good.
+00:23:50 Jordan
+I read that one. Yeah.
+00:23:51 Darius
+And so the Tupac book, only God can judge me. was the one that was I enjoyed that one a lot. You know, it's it starts slow because he is a reporter. So he does like an exhaustive trip through his childhood. And like, you know, how many more stories, how many stories of his mom's a crackhead, you know, he had to move out. Right. But once you get into adulthood, it's it's one of the few Tupac accounts that isn't hagiography. He doesn't like he focus on his personal shortcomings.
+00:24:26 Jordan
+Yeah.
+00:24:28 Darius
+As an adult reading it is interesting because almost all of Tupac's erratic behavior can be explained by the fact that he was just drunk and high. He was 23. Yeah. No, he was just drunk. He was a drunk. Oh my God. There's the reason he mentioned Hennessy that many times.
+00:24:42 Jordan
+I mean, rest in peace, of course. But you know.
+00:24:44 Darius
+Oh my goodness. And it's just like, I don't know, man, as an adult, I'm like, I would have hated this dude. Like, He would show up to sets hours late and he would just improvise lines. Almost everyone who actually had to work with him was just like, oh my God. It was like, also he was just like pretty stupid. He would just like **** ** things all the time and just make terrible decisions. He got himself killed because he decided to punch some gang member in Vegas for no reason. He's just like, people have all these grand theories about what got him killed and what happened was him and Sug were affiliated with one gang and then someone from his crew pointed out Orlando, another dude, Orlando Anderson, who was walking through the casino of an arrival gang. And he walked up to him, he punched him and they jumped him and he shot and killed him later. And it's like, you just not done that. That was stupid.
+00:25:35 Jordan
+And his fiance, Kadada Jones, literally told him, like, just stay home tonight. Stay in tonight. Don't go out. Similar to Cesar's wife, ironically, although granted one was betrayed when just did some **** ****.
+00:25:49 Darius
+He also like, he got the thug life tattoo in the middle of filming Poetic Justice, which caused all sorts of continuity issues.
+00:25:56 Jordan
+Yeah.
+00:25:56 Darius
+It's just like just doing stupid **** stupid, unprofessional. Oh my God, I hated them at the end of that book. It's like, imagine you're John Singleton and you're trying to film a movie and your ******* lead male actor goes and gets a tattoo in the middle of it.
+00:26:12 Jordan
+Right.
+00:26:13 Darius
+And no, people don't film movies in chronological order. Like it's.
+00:26:15 Jordan
+No. And his budget probably wasn't crazy enough to have a bunch of makeup and all that, you know?
+00:26:20 Darius
+And he had to like, he's like, he was so ****** because he had, they still hadn't shot the love scenes yet. So he had to like work around that. And it's just, you know, Yeah, he, his womanizing was, I mean, he was a rich rapper in his early 20s. The womanizing is pretty par for the course, but we do sort of like yada yada past the whole fact that he went to jail for rape.
+00:26:45 Jordan
+Yeah.
+00:26:45 Darius
+It's people just think and choose when this stuff. We do.
+00:26:48 Jordan
+We do.
+00:26:50 Darius
+Yeah, we do. His biggest song, California Love, his first verse is, I don't bail fresh out.
+00:26:55 Jordan
+Of jail, California Dream.
+00:26:56 Darius
+I don't bail for what, sir. I thought we went through a whole reckoning where this stuff's supposed to matter now.
+00:27:07 Jordan
+Do you think he did it?
+00:27:08 Darius
+Yeah, 100%. There's no way given his behavior and given his propensity for substance abuse. And when you compare it to when the context of his sexual behavior in other places like Jeff Pearlman, he's a journalist, so he can't say it outright, but.
+00:27:28 Jordan
+Right.
+00:27:30 Darius
+One of Tupac's friends from the Outlaws, I think, walked in on him in at some sex party in Vegas, and he was with two French models. And I'll spare people the details, but yeah, basically tried to pawn the French model off on his friend who walked in it. His friend's like, I'm good. He's like, no. And the French model is like, no, we're just here for you. And his friend sensing it was not a good look, was like, hey, I'm good. I'm just here, like, say what's up, whatever, whatever. And there was another woman who a year earlier accused him of something similar, but the police just kind of botched the investigation. There's no doubt in my mind he did that. Not even close. And, you know, it's again, when people pick and choose when these things are supposed to matter. But no, Tupac, great rapper, probably a terrible human being. But that's why I don't like this new trend of biographies and documentaries where the subject has control over it. Because it's fake. So I straight up am like boycotting. If I find out, I mean, I've said this on the pod before, but like I find out any sort of piece of biography or documentary has signed off from the subject. I'm not watching it. Right. Because I just I don't have any interest in that. But no, I mean, it wasn't all bad. Like he they talk about his like is like his acting talent was almost more than his rapping talent. He just was like, yes, he people just And when you, I went back and watched the movie, and he was only in five movies, I think. Juice, Poetic Justice, Gridlock, Above the Rim, and something else I'm forgetting.
+00:29:12 Jordan
+Yeah.
+00:29:13 Darius
+And he is magnetic. And you know, it's like, who, which director at the end was like, we had to film all of his close-ups during the morning session because afternoon he would just get so stoned. He'd be too high. He'd be so red if he couldn't zoom in on his face anymore. And it's just like, it's someone who I try to think about the fact that he's 23 and, he died when he was 25, but thinking about it as a 38 year old who like thinking about how much of A logistical nightmare had been to plan around this dude. It's just like, yeah. But no, read it. Jeff Perlman's only guy can judge me. It's a quick read. He's a really good writer. Five and six hours. I went and bought I read his Kobe, his three ring circus book. And then I went and bought his book on Barry Bonds and the Yankees and all of that. And it's in the queue. And so been getting a lot of reading done, man. I'm compiling a list of all, like every morning I just open up, I got subscribed to like 5 or 6 news sites. And every morning I open them up and read, you know, what looks interesting. And I've been compiling a list of the things that I found interesting that I read throughout the week. And I'm going to try to structure them in like shorter pieces, middle pieces, longer pieces, and just share them. I don't know how to share it, but share them later. But just to highlight a few that I've recently read, there's the New York Times had a new like lead on the OJ case. Apparently some mob member was alleged to have been at the basically alleging that OJ had helped that night.
+00:30:51 Jordan
+I do believe that.
+00:30:52 Darius
+Yeah. his bloody clothes are never found, the murder weapon was never found. And I got to the end of the piece about 30 minutes. It's a good read. And I got to the end of the piece. I feel like they never found the smoking gun. They just kind of, it's a lot of hearsay, but it's still an interesting piece. It's still an interesting thing to read. And as we get further away from it, all the principles of the case are dead. So it's kind of, you know, and then I read something interesting about how AI translator, you know how translations You can translate something word for word and you can still lose the kind of the meaning. Right.
+00:31:26 Jordan
+Yeah.
+00:31:27 Darius
+You know, this is English for English, but like the famous Louisiana case where the defendant said, I want a lawyer dog. And so he's like, there's no such thing as a lawyer dog, but like me, you would know what that means. Right. And so AI translation in medical settings is causing issues because certain words can mean different things. They're trying to, I read a piece in Slate, I think, and it's just like, should we, add more regulation to it? And I'm kind of 50-50 on it. But that was pretty good. And then in the least surprising news of the day, I've read another piece about how, you know, because the </t>
+  </si>
+  <si>
+    <t>NBA Predictions, Coddled Superstars, and the Self-Awareness Audit</t>
+  </si>
+  <si>
+    <t>10.27.26</t>
+  </si>
+  <si>
+    <t>Transcript
+00:00:00 Darius
+So remember when they traded him and Brian Curtis, one of my favorite media reporters, has this thing called the Now They Tell Us report, like when some coach gets fired or some player gets traded, the beat reporters just sort of empty the notebook. Right. they said some things about Jalen Brown. He thinks he's the smartest person in the room, da da da da. And the Twitterati was like, that's coded language. Da da da da da. And like, I believe everything they said. It's funny because Tatum said it.
+00:00:32 Jordan
+Tatum did say that this summer. I don't know if you heard that clip or not.
+00:00:36 Darius
+Jalen Brown reminds me of the most annoying co-worker anyone's ever had ever. And so I believe out the trunk with Jordan and Darius. My name is Darius. That's Steve's all up in the area on all socials.
+00:00:47 Jordan
+And I'm Jordan that's going to be riding on all socials.
+00:00:50 Darius
+This is our segment we've titled What's On Our Mind. We let you guys know what's on our mind, what we've seen on the internet, things we'd like to discuss. You know a team is in a good mood when the social account gets the players to do goofy ****. So I'm totally stealing this idea from the Vikings Instagram account. And so the lady walked around the locker room and had all the players list, you know the bottom of your phone has the four apps. So what are the bottom 4 apps on your home screen?
+00:01:19 Jordan
+So I actually have three. I took one off.
+00:01:21 Darius
+Okay.
+00:01:22 Jordan
+But I got my phone, the phone app, Safari, and my music app.
+00:01:28 Darius
+Interesting.
+00:01:29 Jordan
+Oh wait, I'm tripping. On my home screen, I'm tripping. I thought you meant the little bar at the bottom.
+00:01:36 Darius
+I did mean the bottle. She means the bottle. Oh yeah, okay.
+00:01:38 Jordan
+Yeah, got you. Yeah, I got three. Yeah, music, safari, and my phone.
+00:01:42 Darius
+No texting. All right.
+00:01:44 Jordan
+Yeah, I moved that because I felt like I just wake up and then you're like, oh, who did I hear from or who do I got to hit back? And it's supposed to take a few minutes to yourself during the day or in the morning. So I kind of, that's a way I force myself to do that.
+00:01:57 Darius
+I do that by having my phone be dry. cleansing mechanism there. I got the phone app, Google Messages, Google Chrome, and the camera. Okay. So it's, yeah, I mean, that kind of, I think that's actually the stock. But the one I use the least is the camera. Maybe not. It's probably Google Safari because I do a lot of my internet reading on my laptop or desktop. So yeah. So what would you say is your most used app? don't actually you don't have to actually look it up and verify just guess.
+00:02:32 Jordan
+Yeah uh either YouTube my music app or probably yeah probably YouTube in my music app maybe TikTok is probably right there too but those two for sure YouTube and music I do a lot uh either Twitter.
+00:02:58 Darius
+And now it would be honestly Google Gemini because I'm in there looking up **** all the time. So I don't have conversations with AI, but like I'm always researching something, trying to program something, you know, editing something, doing things like that. So yeah, easily before recently, up until recently, it was Twitter for sure. And then after that, it would be Google Gemini and then maybe Instagram. I don't know. I kind of Instagram is kind of washed, but that would probably be. Yeah.
+00:03:30 Jordan
+If I don't have any notifications, I'm not really on there. I mean, I'm on there scrolling just, you know, real ownership. Other than that, I'm not really on there too much.
+00:03:38 Darius
+We're not going to beat the dead horse, but the reels are so unoriginal. Like it's just, oh my God.
+00:03:44 Jordan
+And I saw him on TikTok 3 weeks ago. So does that.
+00:03:47 Darius
+Oh my goodness, man. How many of the. Waking up on November 1st, leaving Halloween costume ones. Have you seen?
+00:03:54 Jordan
+Oh yeah, leaving your, yeah, the one night stand, yeah.
+00:03:57 Darius
+Dude, you know you're the 50th person to do this today. You know, so all right, the next one is pretty straightforward. NBA season is, at this point when you hear this, it'll be in good swing. But it's not too early to get our NBA award predictions out there. So top line award MVP, who do you have?
+00:04:21 Jordan
+My MVP pick this year, I'm going with, you know what? I'm not a fan of this player, but given the injuries that could potentially derail a season, I think they're going to still do well. I'm going to say Shea wins a third MVP this year after losing Jaylen Williams and Cason Wallace.
+00:04:44 Darius
+I don't think the voters will give them three in a row. They just They don't really. They don't. They're real stingy about that third one.
+00:04:53 Jordan
+They're for Bird. Yeah, they won't never **** with Larry Bird's legacy for whatever reason.
+00:04:58 Darius
+And so. I will say Wimby, but Ant is my dark horse for Anthony, which is my dark horse for outside shot. You know, if. If Whimmy doesn't play 65 and Joker looks kind of a little slower and the Nuggets suck.
+00:05:22 Jordan
+Yeah, they saying it's they saying he's might be washed.
+00:05:26 Darius
+No, he's certainly not washed. It's just that the Nuggets aren't probably won't be good enough. And Giannis looks a little washed. And you know, he's going out like they want to give it to an American. So I got him as my dark horse.
+00:05:39 Jordan
+Yeah, that's a good, that's a good pick too. Him and LaMelo, they're hooping. They're fun to watch. I mean, it's early, so we'll see what they actually look like in, you know, in 2030 games from now. But yeah.
+00:05:49 Darius
+Finally, my rediscovering my joy of the NBA regular season by just following one team. And so I'm going to try to watch every T-Wolves game. Obviously, I won't because there's so there's 80 of them and like, you know, I'm not going to not go out to dinner with friends because the 56th T-Wolves game is on TV. You know, but if I'm home and it's I'm going to watch it and just try to follow a team. Just try to follow one team day-to-day that way. And so that's how I'm trying to re-fall in love with the NBA regular season. So rookie of the year, the big four, Cam Boozer, Caleb Wilson, Darren Peterson and AJ Debansa. Which one you got?
+00:06:31 Jordan
+I got Caleb Wilson. He's ******* hooping right now. He's putting up crazy numbers every night. They're not going to win a lot because of Chicago, unfortunately. But yeah, he's my rookie of the year pick. I also think he's going to be the best of that draft. And ironically, I actually met someone today at a leasing office who used to work at UNC with the athletic program, and they're actually really cool. So we were talking about him. Had a good conversation. Yeah, my pick is Caleb Wilson.
+00:06:58 Darius
+I agree because AJ DeVance is already hurt. So who even knows if he's going to hit 65? Darren Peterson, there's just so many mouths to feed in Utah. And he's a, he's, that's going to be a tough, his learning curve is steep. I'll put it that way.
+00:07:15 Jordan
+Yeah. And he's a weird guy to figure out. I don't know if he loves basketball or not. It's kind of given like Ben Simmons.
+00:07:21 Darius
+Yeah. Caleb Wilson is the, I think Cam Boozer will be the best player of the four, but Caleb Wilson is like the perfect blend of skill and opportunity. And I mean, it's just him. He's crazy in Chicago. So he's going to get up 25 shots tonight. And you know, I think you don't want young players to slip into bad habits on bad team, but I do think it's good to be able to spread your wings a little bit. And so, yeah, so that's where I'm going with that one. DPOI, Defensive Player of the Year, who, well, let's non-Wimby edition. If Wimby doesn't win, the only way he doesn't win is if he doesn't play 65 games.
+00:08:01 Jordan
+Yeah, so I'm trying to think.
+00:08:04 Darius
+Want me to go first?
+00:08:07 Jordan
+Yeah, you go first. Yeah.
+00:08:09 Darius
+I've got one of the Thompson twins. That **** was crazy. And no 6 foot seven person **** already to block Wimby.
+00:08:19 Jordan
+Seriously, what the ****?
+00:08:21 Darius
+I think with Fred Van Vleet back, he doesn't really have to handle the ball anymore. And he can just play defense and miss jumpers like he's born to do, you know? So it's not a test all around player award.
+00:08:35 Jordan
+Yeah, it reminds me of a, remember that Charles Barkley quote about DeAndre Jordan? If you locked him in the gym overnight and said no dunk, he'd have six points.
+00:08:46 Darius
+Yeah, I think the Asar has whichever one more offensive skills. I'm in Houston. I'll use the rocket one is what I'm talking about. He has a bit more on ball. We'll call it dexterity. Yeah, but the one in Detroit, man, he might as well have come back up the court, stay back, play four or five. You just stay down there.
+00:09:10 Jordan
+And be an alien on defense, man.
+00:09:12 Darius
+That's it. We really don't need you on this side of the ball.
+00:09:15 Jordan
+Yeah, they need hockey rule. They need hockey substitutions for him on defense and offense.
+00:09:21 Darius
+It's rough. But it's funny though, because both of his parents, both of their parents are short. And like, what are the odds? Yeah, I don't understand that. Would birth 6 foot 7 freakishly athletic twins. I don't get it.
+00:09:33 Jordan
+I don't understand.
+00:09:34 Darius
+Genetics are weird, man.
+00:09:35 Jordan
+Yeah, like KD, how? That doesn't make any sense.
+00:09:40 Darius
+Yeah, man, I'm just trying to, for a couple of years I was out on the NBA regular season. I always been around for the playoffs, but it's just, I bought the league pass this year and it's just kind of cool to, you know, tanking's kind of been legislated out and so teams are trying and, you know, talk to me again in February, see how I feel about it. But so far, so good. Yeah, so I was really all I got for that one. Do you have any other ones?
+00:10:06 Jordan
+Yeah, the Thompson twin is it's a good pick. I'd That'd be my pick too, but I don't want to like copycat. I'd say I'm trying to think. It feels like the day the day of like the defensive big is kind of over. Is it just me or?
+00:10:24 Darius
+It usually goes to a big, but you know, it's just it depends.
+00:10:30 Jordan
+I mean, maybe like.
+00:10:35 Darius
+If they could.
+00:10:39 Jordan
+I thought that too. Yeah, you know, so yeah, I really do. Honestly, the reason I feel like because someone made a point they were like, I feel like it feels like no one cares about the Miami trade. It's like, yeah, because Johannes waited five years to do to make the decision. It's kind of over now.
+00:10:56 Darius
+Yeah, and just he waited too long. He's, in his early 30s and there's nothing left on the team and it's like, correct. how much am I supposed to care about this? He hasn't, right. He hasn't. Since right since he won a championship.
+00:11:16 Jordan
+That was it. Yeah.
+00:11:17 Darius
+That was Joe Biden's president, you know, like.
+00:11:20 Jordan
+Yeah, man, like really.
+00:11:21 Darius
+Not long ago, you know, we didn't even know each other with last time. Like, well, we met each other that time.
+00:11:26 Jordan
+We met during that playoff round.
+00:11:27 Darius
+But like, it's just, that's how long it's been. So like, dude, get out of the first round and check back on me before I start getting invested into you again.
+00:11:36 Jordan
+Yeah.
+00:11:37 Darius
+Speaking of people who have fallen. Your topic, self-awareness. I don't have a good transition for that one. I was trying to tie it into Giannis, but couldn't figure out a way to do it.
+00:11:47 Jordan
+No, it's all good. So this topic is actually coming from a personal situation that happened recently. I was at work, making a visit for work, and I was dropping some stuff off to a property, and they were like, hey, do you have any pens or anything like that? I get merchant stuff to give to people. And I was like, let me check. I was like, no, I don't have any of those, but I do have some stuff I can give you. So I went back to the car and I grabbed a couple of little, items, whatever, cool nifty things that people in the office would use. And then I had like a couple goodie bags that I had pre-made, whatever. And so I give them both to the ladies in the office. And there's in my work line of work, there's you can kind of read the dynamics of an office pretty quickly. There's not a good cop, bad cop, but there's the one that's like the personality that the residents love and all that. And then there's a other person and you're just like, I guess you're probably just really good at your job, maybe. I don't know, I assume. And so I'm there and I hand him the goodie bags and the nice, the nice girl is like, oh, see, I told you he was really nice. Implying that they had some conversation where the other person like thought I wasn't nice. And I'm like, nothing. Yeah, right. And it's also like, lady, nothing about you gives off like inviting or friendly or anything. And it's like, yo, do you see how you come off to people at all? So it just got me thinking about like self-awareness because it's just really funny because I was unaware that I came off to that way, you know, so that's on me too, I guess. But also like, I know why I didn't overly engage with that person because of their demeanor. They just had the RBF and I've been in that office multiple times. No, smile and wave, no speaking, no just head down at work. Like, you know what I mean? So just really funny to me, like just a complete lack of awareness as to why someone would maybe not want to talk to you.
+00:13:42 Darius
+Yeah, it's one of those things where if you ever have somebody that you kind of like you're your friends with and then they talk to you about something and you're like, man, that sounds crazy. And then they talk to you about something else. You're like, that sounds crazy. And about the three or fourth one, you're like, all right, how do you keep? I had to have it today. Like you're falling out with a new person every three business days. Why? How does this keep? I haven't fallen out with somebody in years. How do you keep, you know? Yeah, it's. Everyone else is the problem is usually, as the kids say, a giant red flag. Because ultimately, if you can't, even if it's just like the falling out, if you can't just like exit a friendship amiably, then that's also like you don't have to. You don't have to. Everything's a crash out block. Don't talk to me again. Right. That's quite immature. Like sometimes things, you know, people, you just don't talk to them anymore. But it's right. Yeah, people know. I mean, it I'm amazed at how little self-awareness people have. And it's like socials are making it worse because, you know, it's all you. Someone made the point. It was like it used to be the case that you'd watch TV and in between stuff you'd get an ad and now everything is just an ad. And so like everything you see on Instagram is an ad. And so it is tailored specifically to you and to you kind of Yeah, it kind of colors how people view the world. And, you know, it makes a lot of self-indulgent people who lack self-awareness. So let me ask you this. Has there ever been a time where you had you lacked self-awareness and then it was brought to you and you were like, okay, this is what I should change that or something of that sort?
+00:15:41 Jordan
+Yeah, for sure. Yeah. A couple of times. I remember, It was a job I had years ago and it was a call to the job, so it was just beep, beep, beep, calls from back-to-back to back. So I'm just very much tunnel vision when it comes to my work and things. I'm focused on getting done. And we had somebody like new who was chatting with another person in my little pod area. And I just didn't have time to talk because I was working, you know? And I mean, I think I turned around and said hello, my name or whatever. I mean, I probably could have spoken more. But they were like, they normally actually became really good friends. And they were like, when I first met you, I thought you were rude or stuck up, whatever. And I was like, why? And she was like, because she didn't talk to me. And I was like, okay, do you get it now though? And she's like, I absolutely understand now. But I still would like, I guess I probably could have still, looking back, I could have been more, sacrificed a little more of my work time to ingratiate myself with the person. I think another example was, trying to think, This was like really young. I was like in my early 20s, so still trying to figure out like how to talk to girls and stuff like that. And someone just kind of pulled me to the side and was like, hey, you need to like temper your delivery a little bit. You can be a little too direct, I guess. And I was like, they were like, you're not being offensive, but they can take it that way because they don't know you. And I was like, okay, yeah, I got what you're saying. So that was definitely an eye opener for sure.
+00:17:08 Darius
+The most glaring example for me is I used to I used to be the ******* atheist guy. Yeah. And I'm just not there anymore. I was listening to a crack.com podcast with Jason Pargins, and he was talking about I think it was about the loneliest epidemic. It was like five or six years ago. And he just mentioned like, you know, people, people who don't regularly attend church don't realize that, like, the religious part is almost, it's beside the fact it's just like, those are the people you call when your car breaks down. Those are the people you call when you're sick and shut in. Those are the people who you, know, ask to borrow money if something goes wrong. Those are the people who, those are your friends. That's the people who go attend the bing hall. And it just made me think about what the church means to my parents. And it is, you know, their primary social function. And Who am I to say that's bad? That's great, whatever, a lot of us younger, I ain't young anymore, elder millennials and coastal people, we sort of, we live an irreligious life. And that's not to say you have to go to church, but we didn't replace it with anything. And so I see the good in what regular church attendance does to my parents and my family members and things like that. And it may not be for me, but I'm not gonna, I just stopped being * **** ***** it because, it's. I don't know, so it's like who we're all just guessing. And so, that kind of, that's one thing I just stopped being like the ******* atheist person. Everyone knows the ******* atheist. And so, generally speaking, I just. I am a lot nicer than I used to be in the sense that I just let people cook. I don't really do a lot of correct. I used to just be the guy who was correcting people or actually this and actually that, but especially in social settings, man, I'm just, I'm just like the good times where I let people cook. And so that was something that I had to get some self-awareness and change about myself. And it was like, Would you enjoy hanging out with you? And for the most part, I would say, yeah. But there were times where I was just like, there are things I would do now. Or the things I used to do that I remember. So I was when I was in Charlotte last April or May or April or March. And I took my sister out to lunch on that Sunday. And we was at Longhorn Steakhouse and we ordered steaks or whatever. And she was just telling me about the time that I was just like, we I used to be elitist about what temperature you ordered your steak. And she was just like, remember that? And I just, I just thought, man, I really was being * ****. Who cares how someone else orders their steak?
+00:20:09 Jordan
+Yeah, people didn't really get away about that. Yeah.
+00:20:12 Darius
+I just, I just remember, I just looked at her and I was like, man, I just, I don't know why I cared so much about that. I was like, she was like, you've scaled it back a lot. Like you've calmed down a lot. And I was just like, Yeah. I just think about like, who the **** cares? Someone gets a steak well done. Well, how does it make me better that I ordered a steak a different, it's just, so yeah, I guess my answer to that would be I just, I'm a lot more mellow these days, a lot less. Being right only matters, you know, what doesn't Bill Wither sign? It don't do no good to do all that talking if no one's listening. So I'm much more judicious about when I interject and set the record straight about things or the things that I decide to go on crusades about and different things like that. It's just, yeah, discretion, I guess, would be kind of where I'm at with it.
+00:20:59 Jordan
+So for sure. Yeah, that's a good one, too. I think I think for me is I. I used to really be like that, too, not so much with like, being correct. Well, yeah, sometimes about being correct, too. Then also for me, it would be like, when I just didn't understand the way people reacted to certain things, like emotionally or things in life and circumstances. Like, I just didn't understand it. So I just was like, well, you're weak. Like, you're just, you're, you're, you're, you're not strong enough to handle whatever you're going through. You're immature, you're whatever. When in reality, it's like, I don't know their life story, their journey before they got to that point. So how do I know why that thing affected them that way? You know what I mean? I didn't walk in their shoes, so I can't say whether or not they had blisters before they stepped on that thumbtack. You know what I'm saying? So it's like, I definitely had to learn a little bit more understanding and empathy for people and also just like, because it doesn't look the same way. is the way I would carry it doesn't mean that they're carrying it the wrong way, and vice versa too, because I've been in situations where I'm a very, animated and passionate person and some people find that off-putting and I it made me feel like I needed to like not be that way, so it cuts both ways.
+00:22:21 Darius
+Yeah, I just I remember someone made the good point, this is a video of some lady like having a meltdown on some fast food worker. And she was obviously being a ***** about it. But it was like, you saw 30 seconds of her day. Like you have, you are. Judging, you saw 30 seconds of her day. And maybe she is just a terrible person, but keep in mind, you saw 30 seconds of her day.
+00:22:50 Jordan
+Right.
+00:22:50 Darius
+That's real.
+00:22:51 Jordan
+That's real.
+00:22:53 Darius
+She lived a whole day before that. You don't know what day she had at work. You don't know what?
+00:22:58 Jordan
+She could have tripped and fell and busted a tire.
+00:23:01 Darius
+And you don't know what bill just hit her inbox. Yeah, you know, her car got jacked. Her kids report car was back. You don't you saw 30 seconds of her day and it was a meltdown on a fast food worker. And that's Look, there's no justification for that in the sense that those fast food workers didn't do it. But just keep in mind, you're seeing 30 seconds of that person's day.
+00:23:21 Jordan
+No, that's real ****. Cause I remember I used to work in a movie theater and they were doing like reconstruction on the roof. So it'd be like loud noise at different points throughout the course of the day. And this one lady was like complaining about it. We were like, this ***** won't shut the **** **. Like, you know, and we're like, what a ******* Karen. So we were like making fun of her and we were like, oh, it's so much noise. You know, whatever. And she like heard us. And she was like, I was a soldier in Iraq. This is actually really traumatizing for me.
+00:23:48 Darius
+It's just, And we feel awful. it was just like when similar people dig up old tweets and I just feel like that's so holier than doubt. What was it? The reporter or the play that play analyst for the Trail Blazers. He's like 29 years old and he got the job before the season started. The same day they announced his job, some ******** searched his old tweets and they found tweets from 2012. The kid would have been 15, yeah. We don't even hold people responsible for crimes they committed at 15. Right. But you're going to lose your job for tweets when you were 15.
+00:24:25 Jordan
+Yeah, I get it. No, right. Yeah. That **** does get out of control.
+00:24:30 Darius
+It's just, we, if people are like, well, he should have scrubbed his past, scrubbed his internet. And okay, sure, fine. I agree. But That can't be some. That can't be the answer. The answer should be no one should care about things you tweeted when you were 15 years old. Like it just does not. Yeah, we again, if he was at 15 years old, he like busted someone's car with a rock. Yeah, we wouldn't like no one would he wouldn't be charged as an adult for that. Like so this idea that.
+00:25:04 Jordan
+Yeah.
+00:25:06 Darius
+Again, just move it a little bit more grace because your day could be next. when people were doing all the cancellations and when they're in peak woke, I remember sitting there like, you guys know the other side gets to win, gets to, he's going to win one day too, right? Friday, exactly. And so now when I won't say his name, so I don't want to deal with the pod, but like some guy got killed last year, right? prominent political figure, right-wing political figure. And people were losing their jobs for tweets about it.
+00:25:38 Jordan
+And I'm like, yeah, and this dude did nothing in the world. You know, like it's crazy.
+00:25:41 Darius
+But they set that standard though.
+00:25:44 Jordan
+Right. To a good point. Good point. Yeah.
+00:25:45 Darius
+You set the standard that some kids said something racist on his Twitter account 15 years ago. That's fireable. You have to know the other side gets to, it's gonna be like, you have to play. If you're If your plan has no answer for when the other side gets to govern, it's a, you have to understand that, like, they get to, it's two sides. So I never, I didn't feel bad for any of those people, because that's the state that everyone set, that tweets are fair games are being fired.
+00:26:11 Jordan
+Now what I will say, yeah, and now what I will say is like, so there's a singer now who canceled her tour because of like a flood of her tweets came out from when she was like a teenager, I guess, but it was like crazy **** like some the Bosa Brothers type ****. And then, but then they, and I was like, it's bad. I get it. I wouldn't go to the concert. Obviously, I'll never listen to her music, you know, whatever supporter. And I would hope other people don't, you know, I'm keeping a buck. But also like, then there was a tweet from like four years ago when she was an adult and was like, looking back at those tweets, man, I was so funny. Cancel her. Like, that's, that's fine with me. Like, you know what I'm saying?
+00:26:46 Darius
+I'm, I guess I'm an evangelical about it. I just don't think tweets are cancellable or fireable.
+00:26:52 Jordan
+Sorry, not cancelled, but I'm saying like.
+00:26:54 Darius
+Now, you can't force nobody to buy a ticket to your concert. Like, if you don't want to go, like, there's no you can't force the government to make you people buy concert tickets. But right now, man, it's just you have to be careful about that stuff because what's what's considered out of bounds today could change tomorrow. And that is true. You you don't when the whoever is in charge gets to make those rules. And that's why, you know, you know, it's You don't want to set the standard where, because it never gets to be just the things you don't like are fireable on Twitter.
+00:27:31 Jordan
+Right.
+00:27:32 Darius
+You don't get to always control what is or isn't things that you like. And so, you know, it's just moving a little bit more grace.
+00:27:39 Jordan
+But yeah, and I also think people should not, I think tweets should not be treated more harshly than like actual crimes. You know what I'm saying? Like, there's a guy who has a really prominent job in a really prominent house in this country. And he's done way worse **** than people have tweeted and he's still working. You know what I'm saying? Like there's things we need to, we need to take care of before that.
+00:28:03 Darius
+It's just, you know, keep in mind when you watch that viral video of someone having a tantrum that you're watching 30 seconds of their day.
+00:28:10 Jordan
+No, that's true. Yeah, because sometimes it, like we had a situation like that when I worked at a fast food restaurant. We were like, what the **** is her problem? And she actually was diabetic and her sugar was running low. So it was an urgent situation. So we didn't know that. And we weren't doctors, you know, she told us later on, you know. So, yeah, you just never know.
+00:28:31 Darius
+Fair enough. Speaking a lack of self-awareness, you want to talk about two basketball players?
+00:28:36 Jordan
+Yeah. So how did somebody asked? Oh, yeah. So Jason Tatum, he had a clip of on a YouTube channel about his reaction to the Brown, Jalen Brown trade when he got traded to Philly this summer. And he said, basically, he was like, oh man, like, **** that sucks, dude, like ****. And then they were like, where did he, where did he trade him to, trade him to Philly? And he was like, oh man, I traded him down the street, damn it, you know, whatever.
+00:29:02 Darius
+Oh, it sucks.
+00:29:03 Jordan
+Yeah, it was like that Drake meme when Katie tore his **** in the final, he's like, I actually believe Drake was genuine. It just, I know, but it just looks so over the top. I mean, he's an actor. That is true. He's a crazy actor. Yeah. And so Jalen Brown put cap under the comment in the comment section. They asked Tatum about it. He was like, we won together. I won the best for him, so on and so forth. His response was very peaceful. You know, I reached out to him, haven't heard back yet, but everybody processed things differently. Then they asked Jalen Brown, and he's like, yeah, I heard what he said, some of what he said, didn't see the whole clip. He said, I heard you say it, it's no beef, and he's right. It should never be beef because it's just basketball. But it is lamb chops and some gravy. But he kept saying it because he thought it was going to hit like the more times he said it, which was hilarious. And if you watch the clip back, one of the reporters, there's a zoom in on his face. And as he says it again, it crashes and burns. The reporter's just like, and he was like, then he said, then he went on to say, he comes from a great family. What else did he say? He's got a great PR team, so on and so forth. So it's like he basically just saying, all taking all these Dinleyville shots at Tatum. I mean, for those who don't know, In that situation where someone doesn't like you says you come from a great family. He's trying to call you a ***** essentially. He's got a great PR team. Yeah, he's calling you right. He's called. You got a great PR team. He's a snake. So yeah, I just want to get your take on that. And then there's some layers to the I have a couple questions that I want to address with them too.
+00:30:41 Darius
+So remember when they traded him? And Brian Curtis, one of my favorite media reporters, has this thing called the Now They Tell Us report, like when some coach gets fired or some player gets traded, the beat reporters just sort of empty the notebook. Right. And they say some things about Jalen Brown. He thinks he's the smartest person in the room, da da da da. And the Twitterati was like, that's coded language. Da da da da da. And like, I believe everything they said. It's funny because Tatum said it.
+00:31:13 Jordan
+Tatum did say that this summer. I don't know if you heard that clip or not.
+00:31:16 Darius
+I Jalen Brown reminds me of the most annoying co-worker anyone's ever had ever. And so I believe every word of everything they said about him when he left. I saw a clip of him. He was like, someone asked him how much money he made that year. And he said it because it means public information. He wasn't, he wasn't right. He just literally answered the question. But he said something was like, it's not about how much money is in your account. It's about your investments. And it's just like the most vapid. Yeah. Podcaster, financial information. Elitist, yeah. You pay your financial advisor more than both of our salaries combined, and you don't know. Correct. He, a professional, you don't know what you're talking about. It's like, yes, what he said was just so stupid. And it was just like, he just clearly, you're talking to somebody who went on Wikipedia for an hour and thinks they're an expert on the topic. And he's just a reminder of that person. He's just the guy wh</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Topics Covered&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Social media 'this or that' food polls and internet inability to follow binary voting rules.&lt;/li&gt;
+    &lt;li&gt;Holiday side dishes: cranberry sauce consistency, cornbread dressing vs. standard bread baskets.&lt;/li&gt;
+    &lt;li&gt;Tourist trap gastronomy: the infamous $150 wagyu cheesesteak at Barclay Prime in Philadelphia.&lt;/li&gt;
+    &lt;li&gt;Restaurant quality regression: post-2019 declines in Italian dining, frozen scampi, and weeknight spaghetti standards.&lt;/li&gt;
+    &lt;li&gt;Travel dining markups: downtown all-day pricing vs. local routine living expenses.&lt;/li&gt;
+    &lt;li&gt;Bar tab ambush: automatic 20% gratuity additions, hidden fees, and tipping etiquette on $34 beer-and-shot combos.&lt;/li&gt;
+    &lt;li&gt;Aggressive vendor hustles in tourist cruise ports (Jamaica woodcarvers, personal names, and panhandler parallels).&lt;/li&gt;
+    &lt;li&gt;Cultural and linguistic blind spots: misheard Beach Boys lyrics ('Kokomo' vs. 'Poconos'), 'show tunes' vs. TV themes, and Slow Jamz verses.&lt;/li&gt;
+    &lt;li&gt;Linguistic idioms and pronunciation traps: 'could care less' vs. 'couldn't care less', and reading vs. speaking 'hyperbole'.&lt;/li&gt;
+    &lt;li&gt;Geography and historical naming conventions: Kansas City, Missouri and Lafayette Street's Revolutionary War namesake.&lt;/li&gt;
+    &lt;li&gt;The Mars vs. Europe hypothetical: ultimate extraterrestrial social flex vs. grounded cultural travel on a $2k monthly stipend.&lt;/li&gt;
+    &lt;li&gt;Television critique: Amazon Prime's 8-episode Carrie adaptation, Stephen King themes, telekinesis, and youth bullying.&lt;/li&gt;
+    &lt;li&gt;The cyberbullying controversy: online harassment mechanisms vs. the power of putting the phone down.&lt;/li&gt;
+    &lt;li&gt;Unsanitized sports and music journalism: Jeff Pearlman's biographies on Tupac Shakur and the Kobe-Shaq Lakers.&lt;/li&gt;
+    &lt;li&gt;Celebrity hagiography vs. truth: why estate-approved and subject-authorized documentaries produce fabricated narratives.&lt;/li&gt;
+    &lt;li&gt;The logistics of film sets: Tupac's erratic behavior, onset substance abuse, and spontaneous tattoos during Poetic Justice.&lt;/li&gt;
+    &lt;li&gt;Weekly long-form journalism: the OJ Simpson mob lead, medical AI translation risks, and Texas school policing data.&lt;/li&gt;
+    &lt;li&gt;Film critique: A24's Prime Time starring Robert Pattinson, examining the lack of central conflict, antagonist, or narrative arc.&lt;/li&gt;
+    &lt;li&gt;Sports trivia and economics: NFL Super Bowl referees receiving championship rings for high-paying part-time schedules.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Questions&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Why do social media users struggle to adhere to binary 'this or that' polling rules?&lt;/li&gt;
+    &lt;li&gt;At what price point does an elevated comfort food (like a $150 cheesesteak) become an outright scam rather than a luxury experience?&lt;/li&gt;
+    &lt;li&gt;Are downtown dining and nightlife establishments weaponizing automatic gratuity to exploit distracted patrons?&lt;/li&gt;
+    &lt;li&gt;Why do childhood cultural misunderstandings and misheard lyrics persist well into adult life?&lt;/li&gt;
+    &lt;li&gt;Would the unmatched historical clout of walking on Mars outweigh the sustained lifestyle experience of a year in Europe?&lt;/li&gt;
+    &lt;li&gt;Is cyberbullying an inescapable social trauma or an avoidable problem solved by logging off?&lt;/li&gt;
+    &lt;li&gt;Why are audiences increasingly accepting sanitized, subject-controlled celebrity documentaries over independent journalism?&lt;/li&gt;
+    &lt;li&gt;Can a film with elite acting (like Robert Pattinson in Prime Time) succeed without an active antagonist or narrative conflict?&lt;/li&gt;
+    &lt;li&gt;How does the part-time compensation and championship ring prestige of NFL officiating compare to standard executive side gigs?&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Observations&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Vacation expenses compound invisibly because travelers incur peak downtown pricing across every meal, coffee, and snack, unlike residents operating on fixed grocery baselines.&lt;/li&gt;
+    &lt;li&gt;Automatic gratuities on high-priced urban bar tabs frequently trick patrons into double-tipping unless service staff deliberately disclose the surcharge.&lt;/li&gt;
+    &lt;li&gt;The ultimate modern social media flex is no longer luxury travel, but access to experiences that cannot be purchased with money, like leaving Earth entirely.&lt;/li&gt;
+    &lt;li&gt;Reading words exclusively in print creates pronunciation blind spots that only surface through awkward social exposure.&lt;/li&gt;
+    &lt;li&gt;Sanitized, subject-approved documentaries and biographies rob historical figures of their humanity by eliminating their flaws, erratic choices, and genuine personal struggles.&lt;/li&gt;
+    &lt;li&gt;Independent reporting like Jeff Pearlman's reveals that historical chaos is often caused by simple human immaturity, substance abuse, and bad impulses rather than masterminded conspiracies.&lt;/li&gt;
+    &lt;li&gt;Cinematic character studies without narrative stakes, legal tension, or central conflict feel like empty calories, regardless of lead acting talent.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Debate&lt;/h3&gt;
+  &lt;p&gt;The Mars Walk vs. European Residency Hypothetical: Darius presented an all-expenses-paid dilemma between spending 10 minutes walking on the surface of Mars versus living anywhere in Europe for a full year with a $2,000 monthly stipend. Jordan chose Mars, arguing that setting foot where no ordinary human can ever purchase access represents the ultimate life experience, Instagram profile flex, and social media content. Darius countered by selecting Europe, noting that while Mars offers a singular flex, a year of authentic European cultural exploration, travel, and personal lifestyle immersion provides far greater sustained enjoyment than a 10-minute spacewalk, even on a modest $2,000 monthly budget.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Consumer Culture &amp;amp; Tourist Traps&lt;/li&gt;
+      &lt;li&gt;Travel Economics &amp;amp; Inflation&lt;/li&gt;
+      &lt;li&gt;Cultural Blind Spots &amp;amp; Idioms&lt;/li&gt;
+      &lt;li&gt;Hypothetical Choices &amp;amp; Status Flexes&lt;/li&gt;
+      &lt;li&gt;Media Critique &amp;amp; Narrative Structure&lt;/li&gt;
+      &lt;li&gt;Literary Nonfiction &amp;amp; Uncensored Biographies&lt;/li&gt;
+      &lt;li&gt;Documentary Ethics &amp;amp; Subject Control&lt;/li&gt;
+      &lt;li&gt;Substance Abuse &amp;amp; Celebrity Downfalls&lt;/li&gt;
+      &lt;li&gt;Digital Detox &amp;amp; Personal Productivity&lt;/li&gt;
+      &lt;li&gt;Sports Economics &amp;amp; Officiating Trivia&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Topics Covered&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Phone home screen dock layouts: managing morning boundaries by removing text messaging apps vs. desktop browsing preference.&lt;/li&gt;
+    &lt;li&gt;Algorithm fatigue: creative repetition in Instagram Reels and early cross-posting migration from TikTok.&lt;/li&gt;
+    &lt;li&gt;2026–27 NBA award predictions: Shai Gilgeous-Alexander's 3-peat MVP odds vs. Victor Wembanyama and Anthony Edwards.&lt;/li&gt;
+    &lt;li&gt;2026 Rookie of the Year class dynamics: Caleb Wilson's opportunity in Chicago vs. Cam Boozer, Darren Peterson, and AJ Dybantsa.&lt;/li&gt;
+    &lt;li&gt;Defensive Player of the Year candidates: non-Wembanyama contingency picks, Ausar and Amen Thompson's athletic ceiling, and parental genetics.&lt;/li&gt;
+    &lt;li&gt;Fan engagement strategies: rediscovering joy in the 82-game regular season by anchoring to a single franchise (Minnesota Timberwolves).&lt;/li&gt;
+    &lt;li&gt;Giannis Antetokounmpo and Miami Heat trade aftermath: star fatigue and dwindling public investment after extended playoff droughts.&lt;/li&gt;
+    &lt;li&gt;Interpersonal self-awareness: workplace goodie bag dynamics, resting facial expressions, and misinterpreting professional focus as aloofness.&lt;/li&gt;
+    &lt;li&gt;Personal maturity arcs: shedding reactionary atheism, appreciating church as a community safety net, and dropping elitism around steak temperatures.&lt;/li&gt;
+    &lt;li&gt;The 30-second video empathy rule: judging viral public meltdowns without understanding invisible stressors, financial panic, or medical crises.&lt;/li&gt;
+    &lt;li&gt;Retrospective social media policing: Trail Blazers analyst tweet excavation, holding adults accountable for teenage posts, and setting reciprocal cancellation rules.&lt;/li&gt;
+    &lt;li&gt;The Jayson Tatum vs. Jaylen Brown dynamic: the 'Now They Tell Us' beat reporter dump, passive-aggressive media jabs ('lamb chops and gravy'), and the Scottie Pippen 'Robin' complex.&lt;/li&gt;
+    &lt;li&gt;Athlete coddling in modern basketball: max-contract entitlement, locker room sensitivity, and the inability to accept shared hierarchy during title contention.&lt;/li&gt;
+    &lt;li&gt;Purchases genuinely worth the money: multi-room high-fidelity sound systems, uninterrupted ad-free streaming subscriptions (YouTube Premium), and NFL Sunday Ticket multi-view.&lt;/li&gt;
+    &lt;li&gt;Sneaker culture market philosophy: bypassing sneaker-app artificial scarcity by paying secondary resale markups on must-have retro kicks.&lt;/li&gt;
+    &lt;li&gt;Etymological evolution: animal group nomenclature (a cackle of hyenas), brain energy expenditure, and the modern semantic drift of 'raw dogging.'&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Questions&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Why are NBA superstars seemingly more sensitive to media hierarchy and public credit than athletes in other team sports?&lt;/li&gt;
+    &lt;li&gt;Does winning a championship temporarily heal underlying locker room dysfunction, or merely suppress it until catastrophic collapse?&lt;/li&gt;
+    &lt;li&gt;Why do social media algorithms incentivize creators to copy viral joke formats identically within 24 hours?&lt;/li&gt;
+    &lt;li&gt;How much grace should the public extend to individuals captured having a public meltdown in a 30-second viral snippet?&lt;/li&gt;
+    &lt;li&gt;Is it reasonable to evaluate a 29-year-old professional's character based on tweets posted when they were 15?&lt;/li&gt;
+    &lt;li&gt;At what point in personal maturity does the desire to correct others become recognized as insecurity rather than helpfulness?&lt;/li&gt;
+    &lt;li&gt;Why do elite athletes on supermax contracts resent being viewed as the 'second option' on historically dominant championship teams?&lt;/li&gt;
+    &lt;li&gt;What separates an overpriced consumer convenience from an essential lifestyle upgrade that provides daily peace of mind?&lt;/li&gt;
+    &lt;li&gt;How does linguistic slang transition from crude vulgarity to universally accepted everyday idiom?&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Observations&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Judging someone based on a viral 30-second conflict strips away the entire context of their day, from medical emergencies to financial distress.&lt;/li&gt;
+    &lt;li&gt;Supermax contracts and individual accolades cannot satisfy superstar egos if their primary insecurity is how independent podcasters and fans distribute credit.&lt;/li&gt;
+    &lt;li&gt;When organizations and societies establish zero-tolerance cancellation precedents for old comments, they rarely plan for when their political or cultural opponents take power and enforce the exact same standard.&lt;/li&gt;
+    &lt;li&gt;Maturity is realizing that being technically correct in social settings rarely matters if your interjection alienates everyone around you.&lt;/li&gt;
+    &lt;li&gt;Removing high-stimulus communication apps like iMessage from phone docks forces healthy morning reflection before absorbing other people's emergencies.&lt;/li&gt;
+    &lt;li&gt;Independent sports beat reporters rarely publish critical locker room truths until a player is officially traded or a coach is terminated, creating the 'Now They Tell Us' media cycle.&lt;/li&gt;
+    &lt;li&gt;Subscriptions that remove digital advertising or offer multi-screen sports feeds are not financial splurges; they are investments in preserving personal time and sanity.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Debate&lt;/h3&gt;
+  &lt;p&gt;The Coddled Superstar Epidemic &amp;amp; The 'Robin' Complex (Tatum vs. Jaylen Brown): Jordan and Darius examined the media tension between Jayson Tatum and Jaylen Brown following Brown's trade. Jordan highlighted how organizational favoritism, draft pedigree, and injury rehabilitation create legitimate psychological resentment when one star feels undervalued. Darius pushed back forcefully, arguing that NBA superstars on historic supermax deals are the most coddled, temperamental figures in professional sports. He emphasized that being the second-best player on a championship team—with Finals MVP honors and max money—should satisfy any mature adult, rejecting the premise that professional franchises exist to soothe player insecurities instead of competing for wins on Tuesday night.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;NBA Culture &amp;amp; Superstar Psychology&lt;/li&gt;
+      &lt;li&gt;Athlete Empowerment vs. Entitlement&lt;/li&gt;
+      &lt;li&gt;Locker Room Politics &amp;amp; Media Leaks&lt;/li&gt;
+      &lt;li&gt;Interpersonal Self-Awareness &amp;amp; Maturity&lt;/li&gt;
+      &lt;li&gt;Empathy in the Digital Age&lt;/li&gt;
+      &lt;li&gt;Cancel Culture &amp;amp; Historical Standards&lt;/li&gt;
+      &lt;li&gt;Screen Time &amp;amp; Digital Boundaries&lt;/li&gt;
+      &lt;li&gt;Consumer Value &amp;amp; Subscription Economics&lt;/li&gt;
+      &lt;li&gt;Sneaker Culture &amp;amp; Secondary Markets&lt;/li&gt;
+      &lt;li&gt;Linguistic Evolution &amp;amp; Slang&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>Food &amp; Lifestyle, Money &amp; Class, Movies &amp; Cinema, Technology &amp; Internet Culture</t>
+  </si>
+  <si>
+    <t>Sports &amp; Athletics, Technology &amp; Internet Culture, Aging &amp; Personal Growth, Social Norms &amp; Etiquette</t>
+  </si>
 </sst>
 </file>
 
@@ -11408,7 +12039,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11435,7 +12066,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -11452,6 +12082,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11771,7 +12405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -12665,7 +13299,7 @@
       <c r="D45" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="E45" s="12" t="s">
+      <c r="E45" t="s">
         <v>342</v>
       </c>
       <c r="F45" s="11" t="s">
@@ -12687,6 +13321,40 @@
       </c>
       <c r="F46" s="11" t="s">
         <v>338</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>343</v>
+      </c>
+      <c r="B47" t="s">
+        <v>344</v>
+      </c>
+      <c r="C47" s="10">
+        <v>46332</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>346</v>
+      </c>
+      <c r="B48" t="s">
+        <v>347</v>
+      </c>
+      <c r="C48" s="10">
+        <v>46339</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -12701,7 +13369,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -13354,6 +14022,34 @@
         <v>340</v>
       </c>
     </row>
+    <row r="47" spans="1:4" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>343</v>
+      </c>
+      <c r="B47" t="s">
+        <v>344</v>
+      </c>
+      <c r="C47" s="9">
+        <v>46332</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>346</v>
+      </c>
+      <c r="B48" t="s">
+        <v>347</v>
+      </c>
+      <c r="C48" s="9">
+        <v>46339</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D40" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
     <filterColumn colId="3">
